--- a/Morphometrics/morphology_bu_species_for_taxonomic_treatment.xlsx
+++ b/Morphometrics/morphology_bu_species_for_taxonomic_treatment.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Documents/GitHub/Heuchera-americana-group-species-manuscript/Morphometrics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{C937AE9E-96B8-BB4C-8BEC-E05E6A5A9DF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{9EC80054-4136-A943-B7EB-FD14B7A65CF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{37DF62A1-309C-2E49-B246-2BDE6342D869}"/>
   </bookViews>
   <sheets>
-    <sheet name="Averages &amp; Ranges" sheetId="10" r:id="rId1"/>
+    <sheet name="Median &amp; Ranges" sheetId="10" r:id="rId1"/>
     <sheet name="morphometric_data_final" sheetId="1" r:id="rId2"/>
     <sheet name="Hispida" sheetId="9" r:id="rId3"/>
     <sheet name="Hirsuticaulis" sheetId="8" r:id="rId4"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3708" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3715" uniqueCount="234">
   <si>
     <t>Species</t>
   </si>
@@ -744,6 +744,27 @@
   <si>
     <t>Metric</t>
   </si>
+  <si>
+    <t>Americana:</t>
+  </si>
+  <si>
+    <t>Calycosa:</t>
+  </si>
+  <si>
+    <t>Fumosimontana:</t>
+  </si>
+  <si>
+    <t>Grayana:</t>
+  </si>
+  <si>
+    <t>Richardsonii:</t>
+  </si>
+  <si>
+    <t>Hirsuticaulis:</t>
+  </si>
+  <si>
+    <t>Hispida:</t>
+  </si>
 </sst>
 </file>
 
@@ -1245,10 +1266,11 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1624,7 +1646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3386285D-3D13-374B-A6F3-51FAF5916581}">
-  <dimension ref="A1:P73"/>
+  <dimension ref="A1:P102"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="37.6640625" bestFit="1" customWidth="1"/>
@@ -2210,61 +2232,61 @@
       <c r="B10" t="s">
         <v>216</v>
       </c>
-      <c r="C10" t="str" cm="1">
-        <f t="array" ref="C10">"(" &amp; MIN(_xlfn._xlws.FILTER(Americana!E$2:E1000,Americana!E$2:E1000&lt;&gt;"" )) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Americana!E$2:E1000,(Americana!E$2:E1000&lt;&gt;"" )*(Americana!E$2:E1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!E$2:E1000,Americana!E$2:E1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!E$2:E1000,Americana!E$2:E1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!E$2:E1000,Americana!E$2:E1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Americana!E$2:E1000,(Americana!E$2:E1000&lt;&gt;"" )*(Americana!E$2:E1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!E$2:E1000,Americana!E$2:E1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!E$2:E1000,Americana!E$2:E1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!E$2:E1000,Americana!E$2:E1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Americana!E$2:E1000,Americana!E$2:E1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(0) 0–0 (2.874) mm</v>
-      </c>
-      <c r="D10" t="str" cm="1">
-        <f t="array" ref="D10">"(" &amp; MIN(_xlfn._xlws.FILTER(Americana!F$2:F1000,Americana!F$2:F1000&lt;&gt;"" )) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Americana!F$2:F1000,(Americana!F$2:F1000&lt;&gt;"" )*(Americana!F$2:F1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!F$2:F1000,Americana!F$2:F1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!F$2:F1000,Americana!F$2:F1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!F$2:F1000,Americana!F$2:F1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Americana!F$2:F1000,(Americana!F$2:F1000&lt;&gt;"" )*(Americana!F$2:F1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!F$2:F1000,Americana!F$2:F1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!F$2:F1000,Americana!F$2:F1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!F$2:F1000,Americana!F$2:F1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Americana!F$2:F1000,Americana!F$2:F1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(0) 0–0 (0.504) mm</v>
-      </c>
-      <c r="E10" t="str" cm="1">
-        <f t="array" ref="E10">"(" &amp; MIN(_xlfn._xlws.FILTER(Americana!G$2:G1000,Americana!G$2:G1000&lt;&gt;"" )) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Americana!G$2:G1000,(Americana!G$2:G1000&lt;&gt;"" )*(Americana!G$2:G1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!G$2:G1000,Americana!G$2:G1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!G$2:G1000,Americana!G$2:G1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!G$2:G1000,Americana!G$2:G1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Americana!G$2:G1000,(Americana!G$2:G1000&lt;&gt;"" )*(Americana!G$2:G1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!G$2:G1000,Americana!G$2:G1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!G$2:G1000,Americana!G$2:G1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!G$2:G1000,Americana!G$2:G1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Americana!G$2:G1000,Americana!G$2:G1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(0) 0–0 (0) mm</v>
-      </c>
-      <c r="F10" t="str" cm="1">
-        <f t="array" ref="F10">"(" &amp; MIN(_xlfn._xlws.FILTER(Americana!H$2:H1000,Americana!H$2:H1000&lt;&gt;"" )) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Americana!H$2:H1000,(Americana!H$2:H1000&lt;&gt;"" )*(Americana!H$2:H1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!H$2:H1000,Americana!H$2:H1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!H$2:H1000,Americana!H$2:H1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!H$2:H1000,Americana!H$2:H1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Americana!H$2:H1000,(Americana!H$2:H1000&lt;&gt;"" )*(Americana!H$2:H1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!H$2:H1000,Americana!H$2:H1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!H$2:H1000,Americana!H$2:H1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!H$2:H1000,Americana!H$2:H1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Americana!H$2:H1000,Americana!H$2:H1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(2.147) 2.147–8.625 (8.625) mm</v>
-      </c>
-      <c r="G10" t="str" cm="1">
-        <f t="array" ref="G10">"(" &amp; MIN(_xlfn._xlws.FILTER(Americana!I$2:I1000,Americana!I$2:I1000&lt;&gt;"" )) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Americana!I$2:I1000,(Americana!I$2:I1000&lt;&gt;"" )*(Americana!I$2:I1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!I$2:I1000,Americana!I$2:I1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!I$2:I1000,Americana!I$2:I1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!I$2:I1000,Americana!I$2:I1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Americana!I$2:I1000,(Americana!I$2:I1000&lt;&gt;"" )*(Americana!I$2:I1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!I$2:I1000,Americana!I$2:I1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!I$2:I1000,Americana!I$2:I1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!I$2:I1000,Americana!I$2:I1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Americana!I$2:I1000,Americana!I$2:I1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(0.378) 0.378–3.299 (3.299) mm</v>
-      </c>
-      <c r="H10" t="str" cm="1">
-        <f t="array" ref="H10">"(" &amp; MIN(_xlfn._xlws.FILTER(Americana!J$2:J1000,Americana!J$2:J1000&lt;&gt;"" )) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Americana!J$2:J1000,(Americana!J$2:J1000&lt;&gt;"" )*(Americana!J$2:J1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!J$2:J1000,Americana!J$2:J1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!J$2:J1000,Americana!J$2:J1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!J$2:J1000,Americana!J$2:J1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Americana!J$2:J1000,(Americana!J$2:J1000&lt;&gt;"" )*(Americana!J$2:J1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!J$2:J1000,Americana!J$2:J1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!J$2:J1000,Americana!J$2:J1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!J$2:J1000,Americana!J$2:J1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Americana!J$2:J1000,Americana!J$2:J1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(2.299) 2.299–4.997 (4.997) mm</v>
-      </c>
-      <c r="I10" t="str" cm="1">
-        <f t="array" ref="I10">"(" &amp; MIN(_xlfn._xlws.FILTER(Americana!K$2:K1000,Americana!K$2:K1000&lt;&gt;"" )) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Americana!K$2:K1000,(Americana!K$2:K1000&lt;&gt;"" )*(Americana!K$2:K1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!K$2:K1000,Americana!K$2:K1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!K$2:K1000,Americana!K$2:K1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!K$2:K1000,Americana!K$2:K1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Americana!K$2:K1000,(Americana!K$2:K1000&lt;&gt;"" )*(Americana!K$2:K1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!K$2:K1000,Americana!K$2:K1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!K$2:K1000,Americana!K$2:K1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!K$2:K1000,Americana!K$2:K1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Americana!K$2:K1000,Americana!K$2:K1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(0.778) 0.867–1.999 (1.999) mm</v>
-      </c>
-      <c r="J10" t="str" cm="1">
-        <f t="array" ref="J10">"(" &amp; MIN(_xlfn._xlws.FILTER(Americana!L$2:L1000,Americana!L$2:L1000&lt;&gt;"" )) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Americana!L$2:L1000,(Americana!L$2:L1000&lt;&gt;"" )*(Americana!L$2:L1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!L$2:L1000,Americana!L$2:L1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!L$2:L1000,Americana!L$2:L1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!L$2:L1000,Americana!L$2:L1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Americana!L$2:L1000,(Americana!L$2:L1000&lt;&gt;"" )*(Americana!L$2:L1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!L$2:L1000,Americana!L$2:L1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!L$2:L1000,Americana!L$2:L1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!L$2:L1000,Americana!L$2:L1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Americana!L$2:L1000,Americana!L$2:L1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(0.375) 0.764–1.865 (1.865) mm</v>
-      </c>
-      <c r="K10" t="str" cm="1">
-        <f t="array" ref="K10">"(" &amp; MIN(_xlfn._xlws.FILTER(Americana!M$2:M1000,Americana!M$2:M1000&lt;&gt;"" )) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Americana!M$2:M1000,(Americana!M$2:M1000&lt;&gt;"" )*(Americana!M$2:M1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!M$2:M1000,Americana!M$2:M1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!M$2:M1000,Americana!M$2:M1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!M$2:M1000,Americana!M$2:M1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Americana!M$2:M1000,(Americana!M$2:M1000&lt;&gt;"" )*(Americana!M$2:M1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!M$2:M1000,Americana!M$2:M1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!M$2:M1000,Americana!M$2:M1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!M$2:M1000,Americana!M$2:M1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Americana!M$2:M1000,Americana!M$2:M1000&lt;&gt;"" )) &amp; ") mm"</f>
+      <c r="C10" t="str">
+        <f>"(" &amp; IF(MIN(Americana!E$2:E$1000)&lt;_xlfn.QUARTILE.INC(Americana!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Americana!E$2:E$1000,1)),MIN(Americana!E$2:E$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Americana!E$2:E$1000, Americana!E$2:E$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Americana!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Americana!E$2:E$1000,1)), Americana!E$2:E$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Americana!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Americana!E$2:E$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Americana!E$2:E$1000, Americana!E$2:E$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Americana!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Americana!E$2:E$1000,1)), Americana!E$2:E$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Americana!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Americana!E$2:E$1000,1))) &amp; " (" &amp; IF(MAX(Americana!E$2:E$1000)&gt;_xlfn.QUARTILE.INC(Americana!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Americana!E$2:E$1000,1)),MAX(Americana!E$2:E$1000),"") &amp; ") mm"</f>
+        <v>() 0–0 (2.874) mm</v>
+      </c>
+      <c r="D10" t="str">
+        <f>"(" &amp; IF(MIN(Americana!F$2:F$1000)&lt;_xlfn.QUARTILE.INC(Americana!F$2:F$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Americana!F$2:F$1000,1)),MIN(Americana!F$2:F$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Americana!F$2:F$1000, Americana!F$2:F$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Americana!F$2:F$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Americana!F$2:F$1000,1)), Americana!F$2:F$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Americana!F$2:F$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Americana!F$2:F$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Americana!F$2:F$1000, Americana!F$2:F$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Americana!F$2:F$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Americana!F$2:F$1000,1)), Americana!F$2:F$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Americana!F$2:F$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Americana!F$2:F$1000,1))) &amp; " (" &amp; IF(MAX(Americana!F$2:F$1000)&gt;_xlfn.QUARTILE.INC(Americana!F$2:F$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Americana!F$2:F$1000,1)),MAX(Americana!F$2:F$1000),"") &amp; ") mm"</f>
+        <v>() 0–0 (0.504) mm</v>
+      </c>
+      <c r="E10" t="str">
+        <f>"(" &amp; IF(MIN(Americana!G$2:G$1000)&lt;_xlfn.QUARTILE.INC(Americana!G$2:G$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Americana!G$2:G$1000,1)),MIN(Americana!G$2:G$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Americana!G$2:G$1000, Americana!G$2:G$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Americana!G$2:G$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Americana!G$2:G$1000,1)), Americana!G$2:G$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Americana!G$2:G$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Americana!G$2:G$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Americana!G$2:G$1000, Americana!G$2:G$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Americana!G$2:G$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Americana!G$2:G$1000,1)), Americana!G$2:G$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Americana!G$2:G$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Americana!G$2:G$1000,1))) &amp; " (" &amp; IF(MAX(Americana!G$2:G$1000)&gt;_xlfn.QUARTILE.INC(Americana!G$2:G$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Americana!G$2:G$1000,1)),MAX(Americana!G$2:G$1000),"") &amp; ") mm"</f>
+        <v>() 0–0 () mm</v>
+      </c>
+      <c r="F10" t="str">
+        <f>"(" &amp; IF(MIN(Americana!H$2:H$1000)&lt;_xlfn.QUARTILE.INC(Americana!H$2:H$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Americana!H$2:H$1000,1)),MIN(Americana!H$2:H$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Americana!H$2:H$1000, Americana!H$2:H$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Americana!H$2:H$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Americana!H$2:H$1000,1)), Americana!H$2:H$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Americana!H$2:H$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Americana!H$2:H$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Americana!H$2:H$1000, Americana!H$2:H$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Americana!H$2:H$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Americana!H$2:H$1000,1)), Americana!H$2:H$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Americana!H$2:H$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Americana!H$2:H$1000,1))) &amp; " (" &amp; IF(MAX(Americana!H$2:H$1000)&gt;_xlfn.QUARTILE.INC(Americana!H$2:H$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Americana!H$2:H$1000,1)),MAX(Americana!H$2:H$1000),"") &amp; ") mm"</f>
+        <v>() 2.147–8.625 () mm</v>
+      </c>
+      <c r="G10" t="str">
+        <f>"(" &amp; IF(MIN(Americana!I$2:I$1000)&lt;_xlfn.QUARTILE.INC(Americana!I$2:I$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Americana!I$2:I$1000,1)),MIN(Americana!I$2:I$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Americana!I$2:I$1000, Americana!I$2:I$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Americana!I$2:I$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Americana!I$2:I$1000,1)), Americana!I$2:I$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Americana!I$2:I$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Americana!I$2:I$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Americana!I$2:I$1000, Americana!I$2:I$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Americana!I$2:I$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Americana!I$2:I$1000,1)), Americana!I$2:I$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Americana!I$2:I$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Americana!I$2:I$1000,1))) &amp; " (" &amp; IF(MAX(Americana!I$2:I$1000)&gt;_xlfn.QUARTILE.INC(Americana!I$2:I$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Americana!I$2:I$1000,1)),MAX(Americana!I$2:I$1000),"") &amp; ") mm"</f>
+        <v>() 0.378–3.299 () mm</v>
+      </c>
+      <c r="H10" t="str">
+        <f>"(" &amp; IF(MIN(Americana!J$2:J$1000)&lt;_xlfn.QUARTILE.INC(Americana!J$2:J$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Americana!J$2:J$1000,1)),MIN(Americana!J$2:J$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Americana!J$2:J$1000, Americana!J$2:J$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Americana!J$2:J$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Americana!J$2:J$1000,1)), Americana!J$2:J$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Americana!J$2:J$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Americana!J$2:J$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Americana!J$2:J$1000, Americana!J$2:J$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Americana!J$2:J$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Americana!J$2:J$1000,1)), Americana!J$2:J$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Americana!J$2:J$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Americana!J$2:J$1000,1))) &amp; " (" &amp; IF(MAX(Americana!J$2:J$1000)&gt;_xlfn.QUARTILE.INC(Americana!J$2:J$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Americana!J$2:J$1000,1)),MAX(Americana!J$2:J$1000),"") &amp; ") mm"</f>
+        <v>() 2.299–4.997 () mm</v>
+      </c>
+      <c r="I10" t="str">
+        <f>"(" &amp; IF(MIN(Americana!K$2:K$1000)&lt;_xlfn.QUARTILE.INC(Americana!K$2:K$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Americana!K$2:K$1000,1)),MIN(Americana!K$2:K$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Americana!K$2:K$1000, Americana!K$2:K$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Americana!K$2:K$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Americana!K$2:K$1000,1)), Americana!K$2:K$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Americana!K$2:K$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Americana!K$2:K$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Americana!K$2:K$1000, Americana!K$2:K$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Americana!K$2:K$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Americana!K$2:K$1000,1)), Americana!K$2:K$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Americana!K$2:K$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Americana!K$2:K$1000,1))) &amp; " (" &amp; IF(MAX(Americana!K$2:K$1000)&gt;_xlfn.QUARTILE.INC(Americana!K$2:K$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Americana!K$2:K$1000,1)),MAX(Americana!K$2:K$1000),"") &amp; ") mm"</f>
+        <v>(0.778) 0.867–1.999 () mm</v>
+      </c>
+      <c r="J10" t="str">
+        <f>"(" &amp; IF(MIN(Americana!L$2:L$1000)&lt;_xlfn.QUARTILE.INC(Americana!L$2:L$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Americana!L$2:L$1000,1)),MIN(Americana!L$2:L$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Americana!L$2:L$1000, Americana!L$2:L$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Americana!L$2:L$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Americana!L$2:L$1000,1)), Americana!L$2:L$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Americana!L$2:L$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Americana!L$2:L$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Americana!L$2:L$1000, Americana!L$2:L$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Americana!L$2:L$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Americana!L$2:L$1000,1)), Americana!L$2:L$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Americana!L$2:L$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Americana!L$2:L$1000,1))) &amp; " (" &amp; IF(MAX(Americana!L$2:L$1000)&gt;_xlfn.QUARTILE.INC(Americana!L$2:L$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Americana!L$2:L$1000,1)),MAX(Americana!L$2:L$1000),"") &amp; ") mm"</f>
+        <v>(0.375) 0.764–1.865 () mm</v>
+      </c>
+      <c r="K10" t="str">
+        <f>"(" &amp; IF(MIN(Americana!M$2:M$1000)&lt;_xlfn.QUARTILE.INC(Americana!M$2:M$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Americana!M$2:M$1000,1)),MIN(Americana!M$2:M$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Americana!M$2:M$1000, Americana!M$2:M$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Americana!M$2:M$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Americana!M$2:M$1000,1)), Americana!M$2:M$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Americana!M$2:M$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Americana!M$2:M$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Americana!M$2:M$1000, Americana!M$2:M$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Americana!M$2:M$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Americana!M$2:M$1000,1)), Americana!M$2:M$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Americana!M$2:M$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Americana!M$2:M$1000,1))) &amp; " (" &amp; IF(MAX(Americana!M$2:M$1000)&gt;_xlfn.QUARTILE.INC(Americana!M$2:M$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Americana!M$2:M$1000,1)),MAX(Americana!M$2:M$1000),"") &amp; ") mm"</f>
         <v>(1.21) 1.57–3.162 (3.75) mm</v>
       </c>
-      <c r="L10" t="str" cm="1">
-        <f t="array" ref="L10">"(" &amp; MIN(_xlfn._xlws.FILTER(Americana!N$2:N1000,Americana!N$2:N1000&lt;&gt;"" )) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Americana!N$2:N1000,(Americana!N$2:N1000&lt;&gt;"" )*(Americana!N$2:N1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!N$2:N1000,Americana!N$2:N1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!N$2:N1000,Americana!N$2:N1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!N$2:N1000,Americana!N$2:N1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Americana!N$2:N1000,(Americana!N$2:N1000&lt;&gt;"" )*(Americana!N$2:N1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!N$2:N1000,Americana!N$2:N1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!N$2:N1000,Americana!N$2:N1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!N$2:N1000,Americana!N$2:N1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Americana!N$2:N1000,Americana!N$2:N1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(2.682) 2.682–4.936 (4.936) mm</v>
-      </c>
-      <c r="M10" t="str" cm="1">
-        <f t="array" ref="M10">"(" &amp; MIN(_xlfn._xlws.FILTER(Americana!O$2:O1000,Americana!O$2:O1000&lt;&gt;"" )) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Americana!O$2:O1000,(Americana!O$2:O1000&lt;&gt;"" )*(Americana!O$2:O1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!O$2:O1000,Americana!O$2:O1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!O$2:O1000,Americana!O$2:O1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!O$2:O1000,Americana!O$2:O1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Americana!O$2:O1000,(Americana!O$2:O1000&lt;&gt;"" )*(Americana!O$2:O1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!O$2:O1000,Americana!O$2:O1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!O$2:O1000,Americana!O$2:O1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!O$2:O1000,Americana!O$2:O1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Americana!O$2:O1000,Americana!O$2:O1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(2.797) 2.797–4.624 (4.624) mm</v>
-      </c>
-      <c r="N10" t="str" cm="1">
-        <f t="array" ref="N10">"(" &amp; MIN(_xlfn._xlws.FILTER(Americana!P$2:P1000,Americana!P$2:P1000&lt;&gt;"" )) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Americana!P$2:P1000,(Americana!P$2:P1000&lt;&gt;"" )*(Americana!P$2:P1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!P$2:P1000,Americana!P$2:P1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!P$2:P1000,Americana!P$2:P1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!P$2:P1000,Americana!P$2:P1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Americana!P$2:P1000,(Americana!P$2:P1000&lt;&gt;"" )*(Americana!P$2:P1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!P$2:P1000,Americana!P$2:P1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!P$2:P1000,Americana!P$2:P1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!P$2:P1000,Americana!P$2:P1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Americana!P$2:P1000,Americana!P$2:P1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(2.284) 2.284–8.485 (11.193) mm</v>
-      </c>
-      <c r="O10" t="str" cm="1">
-        <f t="array" ref="O10">"(" &amp; MIN(_xlfn._xlws.FILTER(Americana!Q$2:Q1000,Americana!Q$2:Q1000&lt;&gt;"" )) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Americana!Q$2:Q1000,(Americana!Q$2:Q1000&lt;&gt;"" )*(Americana!Q$2:Q1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!Q$2:Q1000,Americana!Q$2:Q1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!Q$2:Q1000,Americana!Q$2:Q1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!Q$2:Q1000,Americana!Q$2:Q1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Americana!Q$2:Q1000,(Americana!Q$2:Q1000&lt;&gt;"" )*(Americana!Q$2:Q1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!Q$2:Q1000,Americana!Q$2:Q1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!Q$2:Q1000,Americana!Q$2:Q1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!Q$2:Q1000,Americana!Q$2:Q1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Americana!Q$2:Q1000,Americana!Q$2:Q1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(9.219) 9.219–37.631 (42.961) mm</v>
-      </c>
-      <c r="P10" t="str" cm="1">
-        <f t="array" ref="P10">"(" &amp; MIN(_xlfn._xlws.FILTER(Americana!R$2:R1000,Americana!R$2:R1000&lt;&gt;"" )) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Americana!R$2:R1000,(Americana!R$2:R1000&lt;&gt;"" )*(Americana!R$2:R1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!R$2:R1000,Americana!R$2:R1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!R$2:R1000,Americana!R$2:R1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!R$2:R1000,Americana!R$2:R1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Americana!R$2:R1000,(Americana!R$2:R1000&lt;&gt;"" )*(Americana!R$2:R1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!R$2:R1000,Americana!R$2:R1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!R$2:R1000,Americana!R$2:R1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Americana!R$2:R1000,Americana!R$2:R1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Americana!R$2:R1000,Americana!R$2:R1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(436.43) 436.43–945.758 (945.758) mm</v>
+      <c r="L10" t="str">
+        <f>"(" &amp; IF(MIN(Americana!N$2:N$1000)&lt;_xlfn.QUARTILE.INC(Americana!N$2:N$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Americana!N$2:N$1000,1)),MIN(Americana!N$2:N$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Americana!N$2:N$1000, Americana!N$2:N$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Americana!N$2:N$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Americana!N$2:N$1000,1)), Americana!N$2:N$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Americana!N$2:N$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Americana!N$2:N$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Americana!N$2:N$1000, Americana!N$2:N$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Americana!N$2:N$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Americana!N$2:N$1000,1)), Americana!N$2:N$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Americana!N$2:N$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Americana!N$2:N$1000,1))) &amp; " (" &amp; IF(MAX(Americana!N$2:N$1000)&gt;_xlfn.QUARTILE.INC(Americana!N$2:N$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Americana!N$2:N$1000,1)),MAX(Americana!N$2:N$1000),"") &amp; ") mm"</f>
+        <v>() 2.682–4.936 () mm</v>
+      </c>
+      <c r="M10" t="str">
+        <f>"(" &amp; IF(MIN(Americana!O$2:O$1000)&lt;_xlfn.QUARTILE.INC(Americana!O$2:O$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Americana!O$2:O$1000,1)),MIN(Americana!O$2:O$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Americana!O$2:O$1000, Americana!O$2:O$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Americana!O$2:O$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Americana!O$2:O$1000,1)), Americana!O$2:O$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Americana!O$2:O$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Americana!O$2:O$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Americana!O$2:O$1000, Americana!O$2:O$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Americana!O$2:O$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Americana!O$2:O$1000,1)), Americana!O$2:O$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Americana!O$2:O$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Americana!O$2:O$1000,1))) &amp; " (" &amp; IF(MAX(Americana!O$2:O$1000)&gt;_xlfn.QUARTILE.INC(Americana!O$2:O$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Americana!O$2:O$1000,1)),MAX(Americana!O$2:O$1000),"") &amp; ") mm"</f>
+        <v>() 2.797–4.624 () mm</v>
+      </c>
+      <c r="N10" t="str">
+        <f>"(" &amp; IF(MIN(Americana!P$2:P$1000)&lt;_xlfn.QUARTILE.INC(Americana!P$2:P$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Americana!P$2:P$1000,1)),MIN(Americana!P$2:P$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Americana!P$2:P$1000, Americana!P$2:P$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Americana!P$2:P$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Americana!P$2:P$1000,1)), Americana!P$2:P$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Americana!P$2:P$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Americana!P$2:P$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Americana!P$2:P$1000, Americana!P$2:P$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Americana!P$2:P$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Americana!P$2:P$1000,1)), Americana!P$2:P$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Americana!P$2:P$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Americana!P$2:P$1000,1))) &amp; " (" &amp; IF(MAX(Americana!P$2:P$1000)&gt;_xlfn.QUARTILE.INC(Americana!P$2:P$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Americana!P$2:P$1000,1)),MAX(Americana!P$2:P$1000),"") &amp; ") mm"</f>
+        <v>() 2.284–8.485 (11.193) mm</v>
+      </c>
+      <c r="O10" t="str">
+        <f>"(" &amp; IF(MIN(Americana!Q$2:Q$1000)&lt;_xlfn.QUARTILE.INC(Americana!Q$2:Q$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Americana!Q$2:Q$1000,1)),MIN(Americana!Q$2:Q$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Americana!Q$2:Q$1000, Americana!Q$2:Q$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Americana!Q$2:Q$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Americana!Q$2:Q$1000,1)), Americana!Q$2:Q$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Americana!Q$2:Q$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Americana!Q$2:Q$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Americana!Q$2:Q$1000, Americana!Q$2:Q$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Americana!Q$2:Q$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Americana!Q$2:Q$1000,1)), Americana!Q$2:Q$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Americana!Q$2:Q$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Americana!Q$2:Q$1000,1))) &amp; " (" &amp; IF(MAX(Americana!Q$2:Q$1000)&gt;_xlfn.QUARTILE.INC(Americana!Q$2:Q$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Americana!Q$2:Q$1000,1)),MAX(Americana!Q$2:Q$1000),"") &amp; ") mm"</f>
+        <v>() 9.219–37.631 (42.961) mm</v>
+      </c>
+      <c r="P10" t="str">
+        <f>"(" &amp; IF(MIN(Americana!R$2:R$1000)&lt;_xlfn.QUARTILE.INC(Americana!R$2:R$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Americana!R$2:R$1000,1)),MIN(Americana!R$2:R$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Americana!R$2:R$1000, Americana!R$2:R$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Americana!R$2:R$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Americana!R$2:R$1000,1)), Americana!R$2:R$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Americana!R$2:R$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Americana!R$2:R$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Americana!R$2:R$1000, Americana!R$2:R$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Americana!R$2:R$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Americana!R$2:R$1000,1)), Americana!R$2:R$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Americana!R$2:R$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Americana!R$2:R$1000,1))) &amp; " (" &amp; IF(MAX(Americana!R$2:R$1000)&gt;_xlfn.QUARTILE.INC(Americana!R$2:R$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Americana!R$2:R$1000,1)),MAX(Americana!R$2:R$1000),"") &amp; ") mm"</f>
+        <v>() 436.43–945.758 () mm</v>
       </c>
     </row>
     <row r="11" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3306,61 +3328,61 @@
       <c r="B28" t="s">
         <v>215</v>
       </c>
-      <c r="C28" t="str" cm="1">
-        <f t="array" ref="C28">"(" &amp; MIN(_xlfn._xlws.FILTER(Calycosa!E$2:E1000,Calycosa!E$2:E1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Calycosa!E$2:E1000,(Calycosa!E$2:E1000&lt;&gt;"")*(Calycosa!E$2:E1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!E$2:E1000,Calycosa!E$2:E1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!E$2:E1000,Calycosa!E$2:E1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!E$2:E1000,Calycosa!E$2:E1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Calycosa!E$2:E1000,(Calycosa!E$2:E1000&lt;&gt;"")*(Calycosa!E$2:E1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!E$2:E1000,Calycosa!E$2:E1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!E$2:E1000,Calycosa!E$2:E1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!E$2:E1000,Calycosa!E$2:E1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Calycosa!E$2:E1000,Calycosa!E$2:E1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(0) 0–0 (0.871) mm</v>
-      </c>
-      <c r="D28" t="str" cm="1">
-        <f t="array" ref="D28">"(" &amp; MIN(_xlfn._xlws.FILTER(Calycosa!F$2:F1000,Calycosa!F$2:F1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Calycosa!F$2:F1000,(Calycosa!F$2:F1000&lt;&gt;"")*(Calycosa!F$2:F1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!F$2:F1000,Calycosa!F$2:F1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!F$2:F1000,Calycosa!F$2:F1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!F$2:F1000,Calycosa!F$2:F1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Calycosa!F$2:F1000,(Calycosa!F$2:F1000&lt;&gt;"")*(Calycosa!F$2:F1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!F$2:F1000,Calycosa!F$2:F1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!F$2:F1000,Calycosa!F$2:F1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!F$2:F1000,Calycosa!F$2:F1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Calycosa!F$2:F1000,Calycosa!F$2:F1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(0) 0–0 (0.479) mm</v>
-      </c>
-      <c r="E28" t="str" cm="1">
-        <f t="array" ref="E28">"(" &amp; MIN(_xlfn._xlws.FILTER(Calycosa!G$2:G1000,Calycosa!G$2:G1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Calycosa!G$2:G1000,(Calycosa!G$2:G1000&lt;&gt;"")*(Calycosa!G$2:G1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!G$2:G1000,Calycosa!G$2:G1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!G$2:G1000,Calycosa!G$2:G1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!G$2:G1000,Calycosa!G$2:G1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Calycosa!G$2:G1000,(Calycosa!G$2:G1000&lt;&gt;"")*(Calycosa!G$2:G1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!G$2:G1000,Calycosa!G$2:G1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!G$2:G1000,Calycosa!G$2:G1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!G$2:G1000,Calycosa!G$2:G1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Calycosa!G$2:G1000,Calycosa!G$2:G1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(0) 0–0 (1.42) mm</v>
-      </c>
-      <c r="F28" t="str" cm="1">
-        <f t="array" ref="F28">"(" &amp; MIN(_xlfn._xlws.FILTER(Calycosa!H$2:H1000,Calycosa!H$2:H1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Calycosa!H$2:H1000,(Calycosa!H$2:H1000&lt;&gt;"")*(Calycosa!H$2:H1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!H$2:H1000,Calycosa!H$2:H1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!H$2:H1000,Calycosa!H$2:H1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!H$2:H1000,Calycosa!H$2:H1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Calycosa!H$2:H1000,(Calycosa!H$2:H1000&lt;&gt;"")*(Calycosa!H$2:H1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!H$2:H1000,Calycosa!H$2:H1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!H$2:H1000,Calycosa!H$2:H1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!H$2:H1000,Calycosa!H$2:H1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Calycosa!H$2:H1000,Calycosa!H$2:H1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(2.441) 2.441–5.684 (8.919) mm</v>
-      </c>
-      <c r="G28" t="str" cm="1">
-        <f t="array" ref="G28">"(" &amp; MIN(_xlfn._xlws.FILTER(Calycosa!I$2:I1000,Calycosa!I$2:I1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Calycosa!I$2:I1000,(Calycosa!I$2:I1000&lt;&gt;"")*(Calycosa!I$2:I1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!I$2:I1000,Calycosa!I$2:I1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!I$2:I1000,Calycosa!I$2:I1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!I$2:I1000,Calycosa!I$2:I1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Calycosa!I$2:I1000,(Calycosa!I$2:I1000&lt;&gt;"")*(Calycosa!I$2:I1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!I$2:I1000,Calycosa!I$2:I1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!I$2:I1000,Calycosa!I$2:I1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!I$2:I1000,Calycosa!I$2:I1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Calycosa!I$2:I1000,Calycosa!I$2:I1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(0.532) 0.532–2.55 (2.55) mm</v>
-      </c>
-      <c r="H28" t="str" cm="1">
-        <f t="array" ref="H28">"(" &amp; MIN(_xlfn._xlws.FILTER(Calycosa!J$2:J1000,Calycosa!J$2:J1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Calycosa!J$2:J1000,(Calycosa!J$2:J1000&lt;&gt;"")*(Calycosa!J$2:J1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!J$2:J1000,Calycosa!J$2:J1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!J$2:J1000,Calycosa!J$2:J1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!J$2:J1000,Calycosa!J$2:J1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Calycosa!J$2:J1000,(Calycosa!J$2:J1000&lt;&gt;"")*(Calycosa!J$2:J1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!J$2:J1000,Calycosa!J$2:J1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!J$2:J1000,Calycosa!J$2:J1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!J$2:J1000,Calycosa!J$2:J1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Calycosa!J$2:J1000,Calycosa!J$2:J1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(2.143) 2.143–4.258 (4.258) mm</v>
-      </c>
-      <c r="I28" t="str" cm="1">
-        <f t="array" ref="I28">"(" &amp; MIN(_xlfn._xlws.FILTER(Calycosa!K$2:K1000,Calycosa!K$2:K1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Calycosa!K$2:K1000,(Calycosa!K$2:K1000&lt;&gt;"")*(Calycosa!K$2:K1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!K$2:K1000,Calycosa!K$2:K1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!K$2:K1000,Calycosa!K$2:K1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!K$2:K1000,Calycosa!K$2:K1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Calycosa!K$2:K1000,(Calycosa!K$2:K1000&lt;&gt;"")*(Calycosa!K$2:K1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!K$2:K1000,Calycosa!K$2:K1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!K$2:K1000,Calycosa!K$2:K1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!K$2:K1000,Calycosa!K$2:K1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Calycosa!K$2:K1000,Calycosa!K$2:K1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(0.494) 0.494–1.651 (1.651) mm</v>
-      </c>
-      <c r="J28" t="str" cm="1">
-        <f t="array" ref="J28">"(" &amp; MIN(_xlfn._xlws.FILTER(Calycosa!L$2:L1000,Calycosa!L$2:L1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Calycosa!L$2:L1000,(Calycosa!L$2:L1000&lt;&gt;"")*(Calycosa!L$2:L1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!L$2:L1000,Calycosa!L$2:L1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!L$2:L1000,Calycosa!L$2:L1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!L$2:L1000,Calycosa!L$2:L1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Calycosa!L$2:L1000,(Calycosa!L$2:L1000&lt;&gt;"")*(Calycosa!L$2:L1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!L$2:L1000,Calycosa!L$2:L1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!L$2:L1000,Calycosa!L$2:L1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!L$2:L1000,Calycosa!L$2:L1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Calycosa!L$2:L1000,Calycosa!L$2:L1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(0.474) 0.474–1.612 (1.612) mm</v>
-      </c>
-      <c r="K28" t="str" cm="1">
-        <f t="array" ref="K28">"(" &amp; MIN(_xlfn._xlws.FILTER(Calycosa!M$2:M1000,Calycosa!M$2:M1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Calycosa!M$2:M1000,(Calycosa!M$2:M1000&lt;&gt;"")*(Calycosa!M$2:M1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!M$2:M1000,Calycosa!M$2:M1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!M$2:M1000,Calycosa!M$2:M1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!M$2:M1000,Calycosa!M$2:M1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Calycosa!M$2:M1000,(Calycosa!M$2:M1000&lt;&gt;"")*(Calycosa!M$2:M1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!M$2:M1000,Calycosa!M$2:M1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!M$2:M1000,Calycosa!M$2:M1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!M$2:M1000,Calycosa!M$2:M1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Calycosa!M$2:M1000,Calycosa!M$2:M1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(1.086) 1.086–3.118 (3.118) mm</v>
-      </c>
-      <c r="L28" t="str" cm="1">
-        <f t="array" ref="L28">"(" &amp; MIN(_xlfn._xlws.FILTER(Calycosa!N$2:N1000,Calycosa!N$2:N1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Calycosa!N$2:N1000,(Calycosa!N$2:N1000&lt;&gt;"")*(Calycosa!N$2:N1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!N$2:N1000,Calycosa!N$2:N1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!N$2:N1000,Calycosa!N$2:N1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!N$2:N1000,Calycosa!N$2:N1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Calycosa!N$2:N1000,(Calycosa!N$2:N1000&lt;&gt;"")*(Calycosa!N$2:N1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!N$2:N1000,Calycosa!N$2:N1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!N$2:N1000,Calycosa!N$2:N1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!N$2:N1000,Calycosa!N$2:N1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Calycosa!N$2:N1000,Calycosa!N$2:N1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(2.088) 2.088–4.284 (4.284) mm</v>
-      </c>
-      <c r="M28" t="str" cm="1">
-        <f t="array" ref="M28">"(" &amp; MIN(_xlfn._xlws.FILTER(Calycosa!O$2:O1000,Calycosa!O$2:O1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Calycosa!O$2:O1000,(Calycosa!O$2:O1000&lt;&gt;"")*(Calycosa!O$2:O1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!O$2:O1000,Calycosa!O$2:O1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!O$2:O1000,Calycosa!O$2:O1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!O$2:O1000,Calycosa!O$2:O1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Calycosa!O$2:O1000,(Calycosa!O$2:O1000&lt;&gt;"")*(Calycosa!O$2:O1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!O$2:O1000,Calycosa!O$2:O1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!O$2:O1000,Calycosa!O$2:O1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!O$2:O1000,Calycosa!O$2:O1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Calycosa!O$2:O1000,Calycosa!O$2:O1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(2.05) 2.05–4.275 (4.275) mm</v>
-      </c>
-      <c r="N28" t="str" cm="1">
-        <f t="array" ref="N28">"(" &amp; MIN(_xlfn._xlws.FILTER(Calycosa!P$2:P1000,Calycosa!P$2:P1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Calycosa!P$2:P1000,(Calycosa!P$2:P1000&lt;&gt;"")*(Calycosa!P$2:P1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!P$2:P1000,Calycosa!P$2:P1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!P$2:P1000,Calycosa!P$2:P1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!P$2:P1000,Calycosa!P$2:P1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Calycosa!P$2:P1000,(Calycosa!P$2:P1000&lt;&gt;"")*(Calycosa!P$2:P1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!P$2:P1000,Calycosa!P$2:P1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!P$2:P1000,Calycosa!P$2:P1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!P$2:P1000,Calycosa!P$2:P1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Calycosa!P$2:P1000,Calycosa!P$2:P1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(1.644) 1.644–6.625 (6.625) mm</v>
-      </c>
-      <c r="O28" t="str" cm="1">
-        <f t="array" ref="O28">"(" &amp; MIN(_xlfn._xlws.FILTER(Calycosa!Q$2:Q1000,Calycosa!Q$2:Q1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Calycosa!Q$2:Q1000,(Calycosa!Q$2:Q1000&lt;&gt;"")*(Calycosa!Q$2:Q1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!Q$2:Q1000,Calycosa!Q$2:Q1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!Q$2:Q1000,Calycosa!Q$2:Q1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!Q$2:Q1000,Calycosa!Q$2:Q1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Calycosa!Q$2:Q1000,(Calycosa!Q$2:Q1000&lt;&gt;"")*(Calycosa!Q$2:Q1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!Q$2:Q1000,Calycosa!Q$2:Q1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!Q$2:Q1000,Calycosa!Q$2:Q1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!Q$2:Q1000,Calycosa!Q$2:Q1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Calycosa!Q$2:Q1000,Calycosa!Q$2:Q1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(10.217) 10.217–30.727 (30.727) mm</v>
-      </c>
-      <c r="P28" t="str" cm="1">
-        <f t="array" ref="P28">"(" &amp; MIN(_xlfn._xlws.FILTER(Calycosa!R$2:R1000,Calycosa!R$2:R1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Calycosa!R$2:R1000,(Calycosa!R$2:R1000&lt;&gt;"")*(Calycosa!R$2:R1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!R$2:R1000,Calycosa!R$2:R1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!R$2:R1000,Calycosa!R$2:R1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!R$2:R1000,Calycosa!R$2:R1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Calycosa!R$2:R1000,(Calycosa!R$2:R1000&lt;&gt;"")*(Calycosa!R$2:R1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!R$2:R1000,Calycosa!R$2:R1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!R$2:R1000,Calycosa!R$2:R1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Calycosa!R$2:R1000,Calycosa!R$2:R1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Calycosa!R$2:R1000,Calycosa!R$2:R1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(481.688) 481.688–961.619 (961.619) mm</v>
+      <c r="C28" t="str">
+        <f>"(" &amp; IF(MIN(Calycosa!E$2:E$1000)&lt;_xlfn.QUARTILE.INC(Calycosa!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Calycosa!E$2:E$1000,1)),MIN(Calycosa!E$2:E$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Calycosa!E$2:E$1000, Calycosa!E$2:E$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Calycosa!E$2:E$1000,1)), Calycosa!E$2:E$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Calycosa!E$2:E$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Calycosa!E$2:E$1000, Calycosa!E$2:E$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Calycosa!E$2:E$1000,1)), Calycosa!E$2:E$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Calycosa!E$2:E$1000,1))) &amp; " (" &amp; IF(MAX(Calycosa!E$2:E$1000)&gt;_xlfn.QUARTILE.INC(Calycosa!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Calycosa!E$2:E$1000,1)),MAX(Calycosa!E$2:E$1000),"") &amp; ") mm"</f>
+        <v>() 0–0 (0.871) mm</v>
+      </c>
+      <c r="D28" t="str">
+        <f>"(" &amp; IF(MIN(Calycosa!F$2:F$1000)&lt;_xlfn.QUARTILE.INC(Calycosa!F$2:F$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Calycosa!F$2:F$1000,1)),MIN(Calycosa!F$2:F$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Calycosa!F$2:F$1000, Calycosa!F$2:F$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!F$2:F$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Calycosa!F$2:F$1000,1)), Calycosa!F$2:F$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!F$2:F$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Calycosa!F$2:F$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Calycosa!F$2:F$1000, Calycosa!F$2:F$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!F$2:F$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Calycosa!F$2:F$1000,1)), Calycosa!F$2:F$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!F$2:F$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Calycosa!F$2:F$1000,1))) &amp; " (" &amp; IF(MAX(Calycosa!F$2:F$1000)&gt;_xlfn.QUARTILE.INC(Calycosa!F$2:F$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Calycosa!F$2:F$1000,1)),MAX(Calycosa!F$2:F$1000),"") &amp; ") mm"</f>
+        <v>() 0–0 (0.479) mm</v>
+      </c>
+      <c r="E28" t="str">
+        <f>"(" &amp; IF(MIN(Calycosa!G$2:G$1000)&lt;_xlfn.QUARTILE.INC(Calycosa!G$2:G$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Calycosa!G$2:G$1000,1)),MIN(Calycosa!G$2:G$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Calycosa!G$2:G$1000, Calycosa!G$2:G$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!G$2:G$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Calycosa!G$2:G$1000,1)), Calycosa!G$2:G$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!G$2:G$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Calycosa!G$2:G$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Calycosa!G$2:G$1000, Calycosa!G$2:G$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!G$2:G$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Calycosa!G$2:G$1000,1)), Calycosa!G$2:G$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!G$2:G$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Calycosa!G$2:G$1000,1))) &amp; " (" &amp; IF(MAX(Calycosa!G$2:G$1000)&gt;_xlfn.QUARTILE.INC(Calycosa!G$2:G$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Calycosa!G$2:G$1000,1)),MAX(Calycosa!G$2:G$1000),"") &amp; ") mm"</f>
+        <v>() 0–0 (1.42) mm</v>
+      </c>
+      <c r="F28" t="str">
+        <f>"(" &amp; IF(MIN(Calycosa!H$2:H$1000)&lt;_xlfn.QUARTILE.INC(Calycosa!H$2:H$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Calycosa!H$2:H$1000,1)),MIN(Calycosa!H$2:H$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Calycosa!H$2:H$1000, Calycosa!H$2:H$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!H$2:H$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Calycosa!H$2:H$1000,1)), Calycosa!H$2:H$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!H$2:H$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Calycosa!H$2:H$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Calycosa!H$2:H$1000, Calycosa!H$2:H$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!H$2:H$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Calycosa!H$2:H$1000,1)), Calycosa!H$2:H$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!H$2:H$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Calycosa!H$2:H$1000,1))) &amp; " (" &amp; IF(MAX(Calycosa!H$2:H$1000)&gt;_xlfn.QUARTILE.INC(Calycosa!H$2:H$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Calycosa!H$2:H$1000,1)),MAX(Calycosa!H$2:H$1000),"") &amp; ") mm"</f>
+        <v>() 2.441–5.684 (8.919) mm</v>
+      </c>
+      <c r="G28" t="str">
+        <f>"(" &amp; IF(MIN(Calycosa!I$2:I$1000)&lt;_xlfn.QUARTILE.INC(Calycosa!I$2:I$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Calycosa!I$2:I$1000,1)),MIN(Calycosa!I$2:I$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Calycosa!I$2:I$1000, Calycosa!I$2:I$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!I$2:I$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Calycosa!I$2:I$1000,1)), Calycosa!I$2:I$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!I$2:I$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Calycosa!I$2:I$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Calycosa!I$2:I$1000, Calycosa!I$2:I$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!I$2:I$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Calycosa!I$2:I$1000,1)), Calycosa!I$2:I$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!I$2:I$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Calycosa!I$2:I$1000,1))) &amp; " (" &amp; IF(MAX(Calycosa!I$2:I$1000)&gt;_xlfn.QUARTILE.INC(Calycosa!I$2:I$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Calycosa!I$2:I$1000,1)),MAX(Calycosa!I$2:I$1000),"") &amp; ") mm"</f>
+        <v>() 0.532–2.55 () mm</v>
+      </c>
+      <c r="H28" t="str">
+        <f>"(" &amp; IF(MIN(Calycosa!J$2:J$1000)&lt;_xlfn.QUARTILE.INC(Calycosa!J$2:J$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Calycosa!J$2:J$1000,1)),MIN(Calycosa!J$2:J$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Calycosa!J$2:J$1000, Calycosa!J$2:J$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!J$2:J$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Calycosa!J$2:J$1000,1)), Calycosa!J$2:J$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!J$2:J$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Calycosa!J$2:J$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Calycosa!J$2:J$1000, Calycosa!J$2:J$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!J$2:J$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Calycosa!J$2:J$1000,1)), Calycosa!J$2:J$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!J$2:J$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Calycosa!J$2:J$1000,1))) &amp; " (" &amp; IF(MAX(Calycosa!J$2:J$1000)&gt;_xlfn.QUARTILE.INC(Calycosa!J$2:J$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Calycosa!J$2:J$1000,1)),MAX(Calycosa!J$2:J$1000),"") &amp; ") mm"</f>
+        <v>() 2.143–4.258 () mm</v>
+      </c>
+      <c r="I28" t="str">
+        <f>"(" &amp; IF(MIN(Calycosa!K$2:K$1000)&lt;_xlfn.QUARTILE.INC(Calycosa!K$2:K$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Calycosa!K$2:K$1000,1)),MIN(Calycosa!K$2:K$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Calycosa!K$2:K$1000, Calycosa!K$2:K$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!K$2:K$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Calycosa!K$2:K$1000,1)), Calycosa!K$2:K$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!K$2:K$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Calycosa!K$2:K$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Calycosa!K$2:K$1000, Calycosa!K$2:K$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!K$2:K$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Calycosa!K$2:K$1000,1)), Calycosa!K$2:K$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!K$2:K$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Calycosa!K$2:K$1000,1))) &amp; " (" &amp; IF(MAX(Calycosa!K$2:K$1000)&gt;_xlfn.QUARTILE.INC(Calycosa!K$2:K$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Calycosa!K$2:K$1000,1)),MAX(Calycosa!K$2:K$1000),"") &amp; ") mm"</f>
+        <v>() 0.494–1.651 () mm</v>
+      </c>
+      <c r="J28" t="str">
+        <f>"(" &amp; IF(MIN(Calycosa!L$2:L$1000)&lt;_xlfn.QUARTILE.INC(Calycosa!L$2:L$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Calycosa!L$2:L$1000,1)),MIN(Calycosa!L$2:L$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Calycosa!L$2:L$1000, Calycosa!L$2:L$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!L$2:L$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Calycosa!L$2:L$1000,1)), Calycosa!L$2:L$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!L$2:L$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Calycosa!L$2:L$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Calycosa!L$2:L$1000, Calycosa!L$2:L$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!L$2:L$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Calycosa!L$2:L$1000,1)), Calycosa!L$2:L$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!L$2:L$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Calycosa!L$2:L$1000,1))) &amp; " (" &amp; IF(MAX(Calycosa!L$2:L$1000)&gt;_xlfn.QUARTILE.INC(Calycosa!L$2:L$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Calycosa!L$2:L$1000,1)),MAX(Calycosa!L$2:L$1000),"") &amp; ") mm"</f>
+        <v>() 0.474–1.612 () mm</v>
+      </c>
+      <c r="K28" t="str">
+        <f>"(" &amp; IF(MIN(Calycosa!M$2:M$1000)&lt;_xlfn.QUARTILE.INC(Calycosa!M$2:M$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Calycosa!M$2:M$1000,1)),MIN(Calycosa!M$2:M$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Calycosa!M$2:M$1000, Calycosa!M$2:M$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!M$2:M$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Calycosa!M$2:M$1000,1)), Calycosa!M$2:M$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!M$2:M$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Calycosa!M$2:M$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Calycosa!M$2:M$1000, Calycosa!M$2:M$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!M$2:M$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Calycosa!M$2:M$1000,1)), Calycosa!M$2:M$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!M$2:M$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Calycosa!M$2:M$1000,1))) &amp; " (" &amp; IF(MAX(Calycosa!M$2:M$1000)&gt;_xlfn.QUARTILE.INC(Calycosa!M$2:M$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Calycosa!M$2:M$1000,1)),MAX(Calycosa!M$2:M$1000),"") &amp; ") mm"</f>
+        <v>() 1.086–3.118 () mm</v>
+      </c>
+      <c r="L28" t="str">
+        <f>"(" &amp; IF(MIN(Calycosa!N$2:N$1000)&lt;_xlfn.QUARTILE.INC(Calycosa!N$2:N$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Calycosa!N$2:N$1000,1)),MIN(Calycosa!N$2:N$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Calycosa!N$2:N$1000, Calycosa!N$2:N$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!N$2:N$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Calycosa!N$2:N$1000,1)), Calycosa!N$2:N$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!N$2:N$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Calycosa!N$2:N$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Calycosa!N$2:N$1000, Calycosa!N$2:N$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!N$2:N$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Calycosa!N$2:N$1000,1)), Calycosa!N$2:N$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!N$2:N$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Calycosa!N$2:N$1000,1))) &amp; " (" &amp; IF(MAX(Calycosa!N$2:N$1000)&gt;_xlfn.QUARTILE.INC(Calycosa!N$2:N$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Calycosa!N$2:N$1000,1)),MAX(Calycosa!N$2:N$1000),"") &amp; ") mm"</f>
+        <v>() 2.088–4.284 () mm</v>
+      </c>
+      <c r="M28" t="str">
+        <f>"(" &amp; IF(MIN(Calycosa!O$2:O$1000)&lt;_xlfn.QUARTILE.INC(Calycosa!O$2:O$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Calycosa!O$2:O$1000,1)),MIN(Calycosa!O$2:O$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Calycosa!O$2:O$1000, Calycosa!O$2:O$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!O$2:O$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Calycosa!O$2:O$1000,1)), Calycosa!O$2:O$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!O$2:O$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Calycosa!O$2:O$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Calycosa!O$2:O$1000, Calycosa!O$2:O$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!O$2:O$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Calycosa!O$2:O$1000,1)), Calycosa!O$2:O$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!O$2:O$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Calycosa!O$2:O$1000,1))) &amp; " (" &amp; IF(MAX(Calycosa!O$2:O$1000)&gt;_xlfn.QUARTILE.INC(Calycosa!O$2:O$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Calycosa!O$2:O$1000,1)),MAX(Calycosa!O$2:O$1000),"") &amp; ") mm"</f>
+        <v>() 2.05–4.275 () mm</v>
+      </c>
+      <c r="N28" t="str">
+        <f>"(" &amp; IF(MIN(Calycosa!P$2:P$1000)&lt;_xlfn.QUARTILE.INC(Calycosa!P$2:P$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Calycosa!P$2:P$1000,1)),MIN(Calycosa!P$2:P$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Calycosa!P$2:P$1000, Calycosa!P$2:P$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!P$2:P$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Calycosa!P$2:P$1000,1)), Calycosa!P$2:P$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!P$2:P$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Calycosa!P$2:P$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Calycosa!P$2:P$1000, Calycosa!P$2:P$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!P$2:P$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Calycosa!P$2:P$1000,1)), Calycosa!P$2:P$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!P$2:P$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Calycosa!P$2:P$1000,1))) &amp; " (" &amp; IF(MAX(Calycosa!P$2:P$1000)&gt;_xlfn.QUARTILE.INC(Calycosa!P$2:P$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Calycosa!P$2:P$1000,1)),MAX(Calycosa!P$2:P$1000),"") &amp; ") mm"</f>
+        <v>() 1.644–6.625 () mm</v>
+      </c>
+      <c r="O28" t="str">
+        <f>"(" &amp; IF(MIN(Calycosa!Q$2:Q$1000)&lt;_xlfn.QUARTILE.INC(Calycosa!Q$2:Q$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Calycosa!Q$2:Q$1000,1)),MIN(Calycosa!Q$2:Q$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Calycosa!Q$2:Q$1000, Calycosa!Q$2:Q$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!Q$2:Q$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Calycosa!Q$2:Q$1000,1)), Calycosa!Q$2:Q$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!Q$2:Q$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Calycosa!Q$2:Q$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Calycosa!Q$2:Q$1000, Calycosa!Q$2:Q$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!Q$2:Q$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Calycosa!Q$2:Q$1000,1)), Calycosa!Q$2:Q$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!Q$2:Q$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Calycosa!Q$2:Q$1000,1))) &amp; " (" &amp; IF(MAX(Calycosa!Q$2:Q$1000)&gt;_xlfn.QUARTILE.INC(Calycosa!Q$2:Q$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Calycosa!Q$2:Q$1000,1)),MAX(Calycosa!Q$2:Q$1000),"") &amp; ") mm"</f>
+        <v>() 10.217–30.727 () mm</v>
+      </c>
+      <c r="P28" t="str">
+        <f>"(" &amp; IF(MIN(Calycosa!R$2:R$1000)&lt;_xlfn.QUARTILE.INC(Calycosa!R$2:R$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Calycosa!R$2:R$1000,1)),MIN(Calycosa!R$2:R$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Calycosa!R$2:R$1000, Calycosa!R$2:R$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!R$2:R$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Calycosa!R$2:R$1000,1)), Calycosa!R$2:R$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!R$2:R$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Calycosa!R$2:R$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Calycosa!R$2:R$1000, Calycosa!R$2:R$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!R$2:R$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Calycosa!R$2:R$1000,1)), Calycosa!R$2:R$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!R$2:R$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Calycosa!R$2:R$1000,1))) &amp; " (" &amp; IF(MAX(Calycosa!R$2:R$1000)&gt;_xlfn.QUARTILE.INC(Calycosa!R$2:R$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Calycosa!R$2:R$1000,1)),MAX(Calycosa!R$2:R$1000),"") &amp; ") mm"</f>
+        <v>() 481.688–961.619 () mm</v>
       </c>
     </row>
     <row r="29" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3882,61 +3904,61 @@
       <c r="B37" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C37" s="2" t="str" cm="1">
-        <f t="array" ref="C37">"(" &amp; MIN(_xlfn._xlws.FILTER(Fumosimontana!E$2:E1000,Fumosimontana!E$2:E1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Fumosimontana!E$2:E1000,(Fumosimontana!E$2:E1000&lt;&gt;"")*(Fumosimontana!E$2:E1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!E$2:E1000,Fumosimontana!E$2:E1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!E$2:E1000,Fumosimontana!E$2:E1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!E$2:E1000,Fumosimontana!E$2:E1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Fumosimontana!E$2:E1000,(Fumosimontana!E$2:E1000&lt;&gt;"")*(Fumosimontana!E$2:E1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!E$2:E1000,Fumosimontana!E$2:E1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!E$2:E1000,Fumosimontana!E$2:E1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!E$2:E1000,Fumosimontana!E$2:E1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Fumosimontana!E$2:E1000,Fumosimontana!E$2:E1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(0.98) 0.98–2.76 (2.76) mm</v>
-      </c>
-      <c r="D37" s="2" t="str" cm="1">
-        <f t="array" ref="D37">"(" &amp; MIN(_xlfn._xlws.FILTER(Fumosimontana!F$2:F1000,Fumosimontana!F$2:F1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Fumosimontana!F$2:F1000,(Fumosimontana!F$2:F1000&lt;&gt;"")*(Fumosimontana!F$2:F1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!F$2:F1000,Fumosimontana!F$2:F1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!F$2:F1000,Fumosimontana!F$2:F1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!F$2:F1000,Fumosimontana!F$2:F1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Fumosimontana!F$2:F1000,(Fumosimontana!F$2:F1000&lt;&gt;"")*(Fumosimontana!F$2:F1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!F$2:F1000,Fumosimontana!F$2:F1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!F$2:F1000,Fumosimontana!F$2:F1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!F$2:F1000,Fumosimontana!F$2:F1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Fumosimontana!F$2:F1000,Fumosimontana!F$2:F1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(0.41) 0.41–1.04 (1.04) mm</v>
-      </c>
-      <c r="E37" s="2" t="str" cm="1">
-        <f t="array" ref="E37">"(" &amp; MIN(_xlfn._xlws.FILTER(Fumosimontana!G$2:G1000,Fumosimontana!G$2:G1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Fumosimontana!G$2:G1000,(Fumosimontana!G$2:G1000&lt;&gt;"")*(Fumosimontana!G$2:G1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!G$2:G1000,Fumosimontana!G$2:G1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!G$2:G1000,Fumosimontana!G$2:G1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!G$2:G1000,Fumosimontana!G$2:G1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Fumosimontana!G$2:G1000,(Fumosimontana!G$2:G1000&lt;&gt;"")*(Fumosimontana!G$2:G1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!G$2:G1000,Fumosimontana!G$2:G1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!G$2:G1000,Fumosimontana!G$2:G1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!G$2:G1000,Fumosimontana!G$2:G1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Fumosimontana!G$2:G1000,Fumosimontana!G$2:G1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(0.4) 0.4–1.28 (1.28) mm</v>
-      </c>
-      <c r="F37" s="2" t="str" cm="1">
-        <f t="array" ref="F37">"(" &amp; MIN(_xlfn._xlws.FILTER(Fumosimontana!H$2:H1000,Fumosimontana!H$2:H1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Fumosimontana!H$2:H1000,(Fumosimontana!H$2:H1000&lt;&gt;"")*(Fumosimontana!H$2:H1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!H$2:H1000,Fumosimontana!H$2:H1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!H$2:H1000,Fumosimontana!H$2:H1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!H$2:H1000,Fumosimontana!H$2:H1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Fumosimontana!H$2:H1000,(Fumosimontana!H$2:H1000&lt;&gt;"")*(Fumosimontana!H$2:H1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!H$2:H1000,Fumosimontana!H$2:H1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!H$2:H1000,Fumosimontana!H$2:H1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!H$2:H1000,Fumosimontana!H$2:H1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Fumosimontana!H$2:H1000,Fumosimontana!H$2:H1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(0.88) 0.88–3.73 (3.73) mm</v>
-      </c>
-      <c r="G37" s="2" t="str" cm="1">
-        <f t="array" ref="G37">"(" &amp; MIN(_xlfn._xlws.FILTER(Fumosimontana!I$2:I1000,Fumosimontana!I$2:I1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Fumosimontana!I$2:I1000,(Fumosimontana!I$2:I1000&lt;&gt;"")*(Fumosimontana!I$2:I1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!I$2:I1000,Fumosimontana!I$2:I1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!I$2:I1000,Fumosimontana!I$2:I1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!I$2:I1000,Fumosimontana!I$2:I1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Fumosimontana!I$2:I1000,(Fumosimontana!I$2:I1000&lt;&gt;"")*(Fumosimontana!I$2:I1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!I$2:I1000,Fumosimontana!I$2:I1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!I$2:I1000,Fumosimontana!I$2:I1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!I$2:I1000,Fumosimontana!I$2:I1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Fumosimontana!I$2:I1000,Fumosimontana!I$2:I1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(2.52) 2.52–6.66 (6.66) mm</v>
-      </c>
-      <c r="H37" s="2" t="str" cm="1">
-        <f t="array" ref="H37">"(" &amp; MIN(_xlfn._xlws.FILTER(Fumosimontana!J$2:J1000,Fumosimontana!J$2:J1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Fumosimontana!J$2:J1000,(Fumosimontana!J$2:J1000&lt;&gt;"")*(Fumosimontana!J$2:J1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!J$2:J1000,Fumosimontana!J$2:J1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!J$2:J1000,Fumosimontana!J$2:J1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!J$2:J1000,Fumosimontana!J$2:J1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Fumosimontana!J$2:J1000,(Fumosimontana!J$2:J1000&lt;&gt;"")*(Fumosimontana!J$2:J1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!J$2:J1000,Fumosimontana!J$2:J1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!J$2:J1000,Fumosimontana!J$2:J1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!J$2:J1000,Fumosimontana!J$2:J1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Fumosimontana!J$2:J1000,Fumosimontana!J$2:J1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(2.67) 3.32–3.91 (3.91) mm</v>
-      </c>
-      <c r="I37" s="2" t="str" cm="1">
-        <f t="array" ref="I37">"(" &amp; MIN(_xlfn._xlws.FILTER(Fumosimontana!K$2:K1000,Fumosimontana!K$2:K1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Fumosimontana!K$2:K1000,(Fumosimontana!K$2:K1000&lt;&gt;"")*(Fumosimontana!K$2:K1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!K$2:K1000,Fumosimontana!K$2:K1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!K$2:K1000,Fumosimontana!K$2:K1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!K$2:K1000,Fumosimontana!K$2:K1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Fumosimontana!K$2:K1000,(Fumosimontana!K$2:K1000&lt;&gt;"")*(Fumosimontana!K$2:K1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!K$2:K1000,Fumosimontana!K$2:K1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!K$2:K1000,Fumosimontana!K$2:K1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!K$2:K1000,Fumosimontana!K$2:K1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Fumosimontana!K$2:K1000,Fumosimontana!K$2:K1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(0.76) 0.76–1.75 (1.75) mm</v>
-      </c>
-      <c r="J37" s="2" t="str" cm="1">
-        <f t="array" ref="J37">"(" &amp; MIN(_xlfn._xlws.FILTER(Fumosimontana!L$2:L1000,Fumosimontana!L$2:L1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Fumosimontana!L$2:L1000,(Fumosimontana!L$2:L1000&lt;&gt;"")*(Fumosimontana!L$2:L1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!L$2:L1000,Fumosimontana!L$2:L1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!L$2:L1000,Fumosimontana!L$2:L1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!L$2:L1000,Fumosimontana!L$2:L1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Fumosimontana!L$2:L1000,(Fumosimontana!L$2:L1000&lt;&gt;"")*(Fumosimontana!L$2:L1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!L$2:L1000,Fumosimontana!L$2:L1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!L$2:L1000,Fumosimontana!L$2:L1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!L$2:L1000,Fumosimontana!L$2:L1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Fumosimontana!L$2:L1000,Fumosimontana!L$2:L1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(0.51) 0.51–1.35 (1.35) mm</v>
-      </c>
-      <c r="K37" s="2" t="str" cm="1">
-        <f t="array" ref="K37">"(" &amp; MIN(_xlfn._xlws.FILTER(Fumosimontana!M$2:M1000,Fumosimontana!M$2:M1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Fumosimontana!M$2:M1000,(Fumosimontana!M$2:M1000&lt;&gt;"")*(Fumosimontana!M$2:M1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!M$2:M1000,Fumosimontana!M$2:M1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!M$2:M1000,Fumosimontana!M$2:M1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!M$2:M1000,Fumosimontana!M$2:M1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Fumosimontana!M$2:M1000,(Fumosimontana!M$2:M1000&lt;&gt;"")*(Fumosimontana!M$2:M1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!M$2:M1000,Fumosimontana!M$2:M1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!M$2:M1000,Fumosimontana!M$2:M1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!M$2:M1000,Fumosimontana!M$2:M1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Fumosimontana!M$2:M1000,Fumosimontana!M$2:M1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(1.72) 1.72–3.35 (3.35) mm</v>
-      </c>
-      <c r="L37" s="2" t="str" cm="1">
-        <f t="array" ref="L37">"(" &amp; MIN(_xlfn._xlws.FILTER(Fumosimontana!N$2:N1000,Fumosimontana!N$2:N1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Fumosimontana!N$2:N1000,(Fumosimontana!N$2:N1000&lt;&gt;"")*(Fumosimontana!N$2:N1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!N$2:N1000,Fumosimontana!N$2:N1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!N$2:N1000,Fumosimontana!N$2:N1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!N$2:N1000,Fumosimontana!N$2:N1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Fumosimontana!N$2:N1000,(Fumosimontana!N$2:N1000&lt;&gt;"")*(Fumosimontana!N$2:N1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!N$2:N1000,Fumosimontana!N$2:N1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!N$2:N1000,Fumosimontana!N$2:N1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!N$2:N1000,Fumosimontana!N$2:N1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Fumosimontana!N$2:N1000,Fumosimontana!N$2:N1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(2.99) 3.43–4.36 (4.36) mm</v>
-      </c>
-      <c r="M37" s="2" t="str" cm="1">
-        <f t="array" ref="M37">"(" &amp; MIN(_xlfn._xlws.FILTER(Fumosimontana!O$2:O1000,Fumosimontana!O$2:O1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Fumosimontana!O$2:O1000,(Fumosimontana!O$2:O1000&lt;&gt;"")*(Fumosimontana!O$2:O1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!O$2:O1000,Fumosimontana!O$2:O1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!O$2:O1000,Fumosimontana!O$2:O1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!O$2:O1000,Fumosimontana!O$2:O1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Fumosimontana!O$2:O1000,(Fumosimontana!O$2:O1000&lt;&gt;"")*(Fumosimontana!O$2:O1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!O$2:O1000,Fumosimontana!O$2:O1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!O$2:O1000,Fumosimontana!O$2:O1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!O$2:O1000,Fumosimontana!O$2:O1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Fumosimontana!O$2:O1000,Fumosimontana!O$2:O1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(2.74) 2.74–5.59 (5.59) mm</v>
-      </c>
-      <c r="N37" s="2" t="str" cm="1">
-        <f t="array" ref="N37">"(" &amp; MIN(_xlfn._xlws.FILTER(Fumosimontana!P$2:P1000,Fumosimontana!P$2:P1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Fumosimontana!P$2:P1000,(Fumosimontana!P$2:P1000&lt;&gt;"")*(Fumosimontana!P$2:P1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!P$2:P1000,Fumosimontana!P$2:P1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!P$2:P1000,Fumosimontana!P$2:P1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!P$2:P1000,Fumosimontana!P$2:P1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Fumosimontana!P$2:P1000,(Fumosimontana!P$2:P1000&lt;&gt;"")*(Fumosimontana!P$2:P1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!P$2:P1000,Fumosimontana!P$2:P1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!P$2:P1000,Fumosimontana!P$2:P1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!P$2:P1000,Fumosimontana!P$2:P1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Fumosimontana!P$2:P1000,Fumosimontana!P$2:P1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(1.21) 1.21–4.98 (4.98) mm</v>
-      </c>
-      <c r="O37" s="2" t="str" cm="1">
-        <f t="array" ref="O37">"(" &amp; MIN(_xlfn._xlws.FILTER(Fumosimontana!Q$2:Q1000,Fumosimontana!Q$2:Q1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Fumosimontana!Q$2:Q1000,(Fumosimontana!Q$2:Q1000&lt;&gt;"")*(Fumosimontana!Q$2:Q1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!Q$2:Q1000,Fumosimontana!Q$2:Q1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!Q$2:Q1000,Fumosimontana!Q$2:Q1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!Q$2:Q1000,Fumosimontana!Q$2:Q1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Fumosimontana!Q$2:Q1000,(Fumosimontana!Q$2:Q1000&lt;&gt;"")*(Fumosimontana!Q$2:Q1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!Q$2:Q1000,Fumosimontana!Q$2:Q1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!Q$2:Q1000,Fumosimontana!Q$2:Q1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!Q$2:Q1000,Fumosimontana!Q$2:Q1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Fumosimontana!Q$2:Q1000,Fumosimontana!Q$2:Q1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(8.34) 8.34–35.14 (35.14) mm</v>
-      </c>
-      <c r="P37" s="2" t="str" cm="1">
-        <f t="array" ref="P37">"(" &amp; MIN(_xlfn._xlws.FILTER(Fumosimontana!R$2:R1000,Fumosimontana!R$2:R1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Fumosimontana!R$2:R1000,(Fumosimontana!R$2:R1000&lt;&gt;"")*(Fumosimontana!R$2:R1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!R$2:R1000,Fumosimontana!R$2:R1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!R$2:R1000,Fumosimontana!R$2:R1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!R$2:R1000,Fumosimontana!R$2:R1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Fumosimontana!R$2:R1000,(Fumosimontana!R$2:R1000&lt;&gt;"")*(Fumosimontana!R$2:R1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!R$2:R1000,Fumosimontana!R$2:R1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!R$2:R1000,Fumosimontana!R$2:R1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Fumosimontana!R$2:R1000,Fumosimontana!R$2:R1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Fumosimontana!R$2:R1000,Fumosimontana!R$2:R1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(66.7) 66.7–84.596 (84.596) mm</v>
+      <c r="C37" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Fumosimontana!E$2:E$1000)&lt;_xlfn.QUARTILE.INC(Fumosimontana!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!E$2:E$1000,1)),MIN(Fumosimontana!E$2:E$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Fumosimontana!E$2:E$1000, Fumosimontana!E$2:E$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!E$2:E$1000,1)), Fumosimontana!E$2:E$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!E$2:E$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Fumosimontana!E$2:E$1000, Fumosimontana!E$2:E$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!E$2:E$1000,1)), Fumosimontana!E$2:E$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!E$2:E$1000,1))) &amp; " (" &amp; IF(MAX(Fumosimontana!E$2:E$1000)&gt;_xlfn.QUARTILE.INC(Fumosimontana!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!E$2:E$1000,1)),MAX(Fumosimontana!E$2:E$1000),"") &amp; ") mm"</f>
+        <v>() 0.98–2.76 () mm</v>
+      </c>
+      <c r="D37" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Fumosimontana!F$2:F$1000)&lt;_xlfn.QUARTILE.INC(Fumosimontana!F$2:F$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!F$2:F$1000,1)),MIN(Fumosimontana!F$2:F$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Fumosimontana!F$2:F$1000, Fumosimontana!F$2:F$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!F$2:F$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!F$2:F$1000,1)), Fumosimontana!F$2:F$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!F$2:F$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!F$2:F$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Fumosimontana!F$2:F$1000, Fumosimontana!F$2:F$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!F$2:F$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!F$2:F$1000,1)), Fumosimontana!F$2:F$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!F$2:F$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!F$2:F$1000,1))) &amp; " (" &amp; IF(MAX(Fumosimontana!F$2:F$1000)&gt;_xlfn.QUARTILE.INC(Fumosimontana!F$2:F$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!F$2:F$1000,1)),MAX(Fumosimontana!F$2:F$1000),"") &amp; ") mm"</f>
+        <v>() 0.41–1.04 () mm</v>
+      </c>
+      <c r="E37" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Fumosimontana!G$2:G$1000)&lt;_xlfn.QUARTILE.INC(Fumosimontana!G$2:G$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!G$2:G$1000,1)),MIN(Fumosimontana!G$2:G$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Fumosimontana!G$2:G$1000, Fumosimontana!G$2:G$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!G$2:G$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!G$2:G$1000,1)), Fumosimontana!G$2:G$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!G$2:G$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!G$2:G$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Fumosimontana!G$2:G$1000, Fumosimontana!G$2:G$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!G$2:G$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!G$2:G$1000,1)), Fumosimontana!G$2:G$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!G$2:G$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!G$2:G$1000,1))) &amp; " (" &amp; IF(MAX(Fumosimontana!G$2:G$1000)&gt;_xlfn.QUARTILE.INC(Fumosimontana!G$2:G$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!G$2:G$1000,1)),MAX(Fumosimontana!G$2:G$1000),"") &amp; ") mm"</f>
+        <v>() 0.4–1.28 () mm</v>
+      </c>
+      <c r="F37" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Fumosimontana!H$2:H$1000)&lt;_xlfn.QUARTILE.INC(Fumosimontana!H$2:H$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!H$2:H$1000,1)),MIN(Fumosimontana!H$2:H$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Fumosimontana!H$2:H$1000, Fumosimontana!H$2:H$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!H$2:H$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!H$2:H$1000,1)), Fumosimontana!H$2:H$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!H$2:H$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!H$2:H$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Fumosimontana!H$2:H$1000, Fumosimontana!H$2:H$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!H$2:H$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!H$2:H$1000,1)), Fumosimontana!H$2:H$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!H$2:H$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!H$2:H$1000,1))) &amp; " (" &amp; IF(MAX(Fumosimontana!H$2:H$1000)&gt;_xlfn.QUARTILE.INC(Fumosimontana!H$2:H$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!H$2:H$1000,1)),MAX(Fumosimontana!H$2:H$1000),"") &amp; ") mm"</f>
+        <v>() 0.88–3.73 () mm</v>
+      </c>
+      <c r="G37" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Fumosimontana!I$2:I$1000)&lt;_xlfn.QUARTILE.INC(Fumosimontana!I$2:I$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!I$2:I$1000,1)),MIN(Fumosimontana!I$2:I$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Fumosimontana!I$2:I$1000, Fumosimontana!I$2:I$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!I$2:I$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!I$2:I$1000,1)), Fumosimontana!I$2:I$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!I$2:I$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!I$2:I$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Fumosimontana!I$2:I$1000, Fumosimontana!I$2:I$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!I$2:I$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!I$2:I$1000,1)), Fumosimontana!I$2:I$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!I$2:I$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!I$2:I$1000,1))) &amp; " (" &amp; IF(MAX(Fumosimontana!I$2:I$1000)&gt;_xlfn.QUARTILE.INC(Fumosimontana!I$2:I$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!I$2:I$1000,1)),MAX(Fumosimontana!I$2:I$1000),"") &amp; ") mm"</f>
+        <v>() 2.52–6.66 () mm</v>
+      </c>
+      <c r="H37" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Fumosimontana!J$2:J$1000)&lt;_xlfn.QUARTILE.INC(Fumosimontana!J$2:J$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!J$2:J$1000,1)),MIN(Fumosimontana!J$2:J$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Fumosimontana!J$2:J$1000, Fumosimontana!J$2:J$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!J$2:J$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!J$2:J$1000,1)), Fumosimontana!J$2:J$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!J$2:J$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!J$2:J$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Fumosimontana!J$2:J$1000, Fumosimontana!J$2:J$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!J$2:J$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!J$2:J$1000,1)), Fumosimontana!J$2:J$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!J$2:J$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!J$2:J$1000,1))) &amp; " (" &amp; IF(MAX(Fumosimontana!J$2:J$1000)&gt;_xlfn.QUARTILE.INC(Fumosimontana!J$2:J$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!J$2:J$1000,1)),MAX(Fumosimontana!J$2:J$1000),"") &amp; ") mm"</f>
+        <v>(2.67) 3.32–3.91 () mm</v>
+      </c>
+      <c r="I37" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Fumosimontana!K$2:K$1000)&lt;_xlfn.QUARTILE.INC(Fumosimontana!K$2:K$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!K$2:K$1000,1)),MIN(Fumosimontana!K$2:K$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Fumosimontana!K$2:K$1000, Fumosimontana!K$2:K$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!K$2:K$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!K$2:K$1000,1)), Fumosimontana!K$2:K$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!K$2:K$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!K$2:K$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Fumosimontana!K$2:K$1000, Fumosimontana!K$2:K$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!K$2:K$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!K$2:K$1000,1)), Fumosimontana!K$2:K$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!K$2:K$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!K$2:K$1000,1))) &amp; " (" &amp; IF(MAX(Fumosimontana!K$2:K$1000)&gt;_xlfn.QUARTILE.INC(Fumosimontana!K$2:K$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!K$2:K$1000,1)),MAX(Fumosimontana!K$2:K$1000),"") &amp; ") mm"</f>
+        <v>() 0.76–1.75 () mm</v>
+      </c>
+      <c r="J37" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Fumosimontana!L$2:L$1000)&lt;_xlfn.QUARTILE.INC(Fumosimontana!L$2:L$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!L$2:L$1000,1)),MIN(Fumosimontana!L$2:L$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Fumosimontana!L$2:L$1000, Fumosimontana!L$2:L$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!L$2:L$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!L$2:L$1000,1)), Fumosimontana!L$2:L$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!L$2:L$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!L$2:L$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Fumosimontana!L$2:L$1000, Fumosimontana!L$2:L$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!L$2:L$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!L$2:L$1000,1)), Fumosimontana!L$2:L$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!L$2:L$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!L$2:L$1000,1))) &amp; " (" &amp; IF(MAX(Fumosimontana!L$2:L$1000)&gt;_xlfn.QUARTILE.INC(Fumosimontana!L$2:L$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!L$2:L$1000,1)),MAX(Fumosimontana!L$2:L$1000),"") &amp; ") mm"</f>
+        <v>() 0.51–1.35 () mm</v>
+      </c>
+      <c r="K37" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Fumosimontana!M$2:M$1000)&lt;_xlfn.QUARTILE.INC(Fumosimontana!M$2:M$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!M$2:M$1000,1)),MIN(Fumosimontana!M$2:M$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Fumosimontana!M$2:M$1000, Fumosimontana!M$2:M$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!M$2:M$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!M$2:M$1000,1)), Fumosimontana!M$2:M$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!M$2:M$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!M$2:M$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Fumosimontana!M$2:M$1000, Fumosimontana!M$2:M$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!M$2:M$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!M$2:M$1000,1)), Fumosimontana!M$2:M$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!M$2:M$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!M$2:M$1000,1))) &amp; " (" &amp; IF(MAX(Fumosimontana!M$2:M$1000)&gt;_xlfn.QUARTILE.INC(Fumosimontana!M$2:M$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!M$2:M$1000,1)),MAX(Fumosimontana!M$2:M$1000),"") &amp; ") mm"</f>
+        <v>() 1.72–3.35 () mm</v>
+      </c>
+      <c r="L37" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Fumosimontana!N$2:N$1000)&lt;_xlfn.QUARTILE.INC(Fumosimontana!N$2:N$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!N$2:N$1000,1)),MIN(Fumosimontana!N$2:N$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Fumosimontana!N$2:N$1000, Fumosimontana!N$2:N$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!N$2:N$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!N$2:N$1000,1)), Fumosimontana!N$2:N$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!N$2:N$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!N$2:N$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Fumosimontana!N$2:N$1000, Fumosimontana!N$2:N$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!N$2:N$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!N$2:N$1000,1)), Fumosimontana!N$2:N$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!N$2:N$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!N$2:N$1000,1))) &amp; " (" &amp; IF(MAX(Fumosimontana!N$2:N$1000)&gt;_xlfn.QUARTILE.INC(Fumosimontana!N$2:N$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!N$2:N$1000,1)),MAX(Fumosimontana!N$2:N$1000),"") &amp; ") mm"</f>
+        <v>(2.99) 3.43–4.36 () mm</v>
+      </c>
+      <c r="M37" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Fumosimontana!O$2:O$1000)&lt;_xlfn.QUARTILE.INC(Fumosimontana!O$2:O$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!O$2:O$1000,1)),MIN(Fumosimontana!O$2:O$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Fumosimontana!O$2:O$1000, Fumosimontana!O$2:O$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!O$2:O$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!O$2:O$1000,1)), Fumosimontana!O$2:O$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!O$2:O$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!O$2:O$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Fumosimontana!O$2:O$1000, Fumosimontana!O$2:O$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!O$2:O$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!O$2:O$1000,1)), Fumosimontana!O$2:O$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!O$2:O$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!O$2:O$1000,1))) &amp; " (" &amp; IF(MAX(Fumosimontana!O$2:O$1000)&gt;_xlfn.QUARTILE.INC(Fumosimontana!O$2:O$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!O$2:O$1000,1)),MAX(Fumosimontana!O$2:O$1000),"") &amp; ") mm"</f>
+        <v>() 2.74–5.59 () mm</v>
+      </c>
+      <c r="N37" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Fumosimontana!P$2:P$1000)&lt;_xlfn.QUARTILE.INC(Fumosimontana!P$2:P$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!P$2:P$1000,1)),MIN(Fumosimontana!P$2:P$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Fumosimontana!P$2:P$1000, Fumosimontana!P$2:P$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!P$2:P$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!P$2:P$1000,1)), Fumosimontana!P$2:P$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!P$2:P$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!P$2:P$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Fumosimontana!P$2:P$1000, Fumosimontana!P$2:P$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!P$2:P$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!P$2:P$1000,1)), Fumosimontana!P$2:P$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!P$2:P$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!P$2:P$1000,1))) &amp; " (" &amp; IF(MAX(Fumosimontana!P$2:P$1000)&gt;_xlfn.QUARTILE.INC(Fumosimontana!P$2:P$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!P$2:P$1000,1)),MAX(Fumosimontana!P$2:P$1000),"") &amp; ") mm"</f>
+        <v>() 1.21–4.98 () mm</v>
+      </c>
+      <c r="O37" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Fumosimontana!Q$2:Q$1000)&lt;_xlfn.QUARTILE.INC(Fumosimontana!Q$2:Q$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!Q$2:Q$1000,1)),MIN(Fumosimontana!Q$2:Q$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Fumosimontana!Q$2:Q$1000, Fumosimontana!Q$2:Q$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!Q$2:Q$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!Q$2:Q$1000,1)), Fumosimontana!Q$2:Q$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!Q$2:Q$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!Q$2:Q$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Fumosimontana!Q$2:Q$1000, Fumosimontana!Q$2:Q$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!Q$2:Q$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!Q$2:Q$1000,1)), Fumosimontana!Q$2:Q$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!Q$2:Q$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!Q$2:Q$1000,1))) &amp; " (" &amp; IF(MAX(Fumosimontana!Q$2:Q$1000)&gt;_xlfn.QUARTILE.INC(Fumosimontana!Q$2:Q$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!Q$2:Q$1000,1)),MAX(Fumosimontana!Q$2:Q$1000),"") &amp; ") mm"</f>
+        <v>() 8.34–35.14 () mm</v>
+      </c>
+      <c r="P37" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Fumosimontana!R$2:R$1000)&lt;_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,1)),MIN(Fumosimontana!R$2:R$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Fumosimontana!R$2:R$1000, Fumosimontana!R$2:R$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,1)), Fumosimontana!R$2:R$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Fumosimontana!R$2:R$1000, Fumosimontana!R$2:R$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,1)), Fumosimontana!R$2:R$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,1))) &amp; " (" &amp; IF(MAX(Fumosimontana!R$2:R$1000)&gt;_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!R$2:R$1000,1)),MAX(Fumosimontana!R$2:R$1000),"") &amp; ") mm"</f>
+        <v>() 66.7–84.596 () mm</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.2">
@@ -4458,61 +4480,61 @@
       <c r="B46" t="s">
         <v>104</v>
       </c>
-      <c r="C46" t="str" cm="1">
-        <f t="array" ref="C46">"(" &amp; MIN(_xlfn._xlws.FILTER(Grayana!E$2:E1000,Grayana!E$2:E1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Grayana!E$2:E1000,(Grayana!E$2:E1000&lt;&gt;"")*(Grayana!E$2:E1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!E$2:E1000,Grayana!E$2:E1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!E$2:E1000,Grayana!E$2:E1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!E$2:E1000,Grayana!E$2:E1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Grayana!E$2:E1000,(Grayana!E$2:E1000&lt;&gt;"")*(Grayana!E$2:E1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!E$2:E1000,Grayana!E$2:E1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!E$2:E1000,Grayana!E$2:E1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!E$2:E1000,Grayana!E$2:E1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Grayana!E$2:E1000,Grayana!E$2:E1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(0.804) 0.804–2.26 (2.361) mm</v>
-      </c>
-      <c r="D46" t="str" cm="1">
-        <f t="array" ref="D46">"(" &amp; MIN(_xlfn._xlws.FILTER(Grayana!F$2:F1000,Grayana!F$2:F1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Grayana!F$2:F1000,(Grayana!F$2:F1000&lt;&gt;"")*(Grayana!F$2:F1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!F$2:F1000,Grayana!F$2:F1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!F$2:F1000,Grayana!F$2:F1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!F$2:F1000,Grayana!F$2:F1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Grayana!F$2:F1000,(Grayana!F$2:F1000&lt;&gt;"")*(Grayana!F$2:F1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!F$2:F1000,Grayana!F$2:F1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!F$2:F1000,Grayana!F$2:F1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!F$2:F1000,Grayana!F$2:F1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Grayana!F$2:F1000,Grayana!F$2:F1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(0.514) 0.514–1.19 (1.245) mm</v>
-      </c>
-      <c r="E46" t="str" cm="1">
-        <f t="array" ref="E46">"(" &amp; MIN(_xlfn._xlws.FILTER(Grayana!G$2:G1000,Grayana!G$2:G1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Grayana!G$2:G1000,(Grayana!G$2:G1000&lt;&gt;"")*(Grayana!G$2:G1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!G$2:G1000,Grayana!G$2:G1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!G$2:G1000,Grayana!G$2:G1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!G$2:G1000,Grayana!G$2:G1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Grayana!G$2:G1000,(Grayana!G$2:G1000&lt;&gt;"")*(Grayana!G$2:G1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!G$2:G1000,Grayana!G$2:G1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!G$2:G1000,Grayana!G$2:G1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!G$2:G1000,Grayana!G$2:G1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Grayana!G$2:G1000,Grayana!G$2:G1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(0) 0–0 (0) mm</v>
-      </c>
-      <c r="F46" t="str" cm="1">
-        <f t="array" ref="F46">"(" &amp; MIN(_xlfn._xlws.FILTER(Grayana!H$2:H1000,Grayana!H$2:H1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Grayana!H$2:H1000,(Grayana!H$2:H1000&lt;&gt;"")*(Grayana!H$2:H1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!H$2:H1000,Grayana!H$2:H1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!H$2:H1000,Grayana!H$2:H1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!H$2:H1000,Grayana!H$2:H1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Grayana!H$2:H1000,(Grayana!H$2:H1000&lt;&gt;"")*(Grayana!H$2:H1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!H$2:H1000,Grayana!H$2:H1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!H$2:H1000,Grayana!H$2:H1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!H$2:H1000,Grayana!H$2:H1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Grayana!H$2:H1000,Grayana!H$2:H1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(2.483) 2.483–9.211 (9.87) mm</v>
-      </c>
-      <c r="G46" t="str" cm="1">
-        <f t="array" ref="G46">"(" &amp; MIN(_xlfn._xlws.FILTER(Grayana!I$2:I1000,Grayana!I$2:I1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Grayana!I$2:I1000,(Grayana!I$2:I1000&lt;&gt;"")*(Grayana!I$2:I1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!I$2:I1000,Grayana!I$2:I1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!I$2:I1000,Grayana!I$2:I1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!I$2:I1000,Grayana!I$2:I1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Grayana!I$2:I1000,(Grayana!I$2:I1000&lt;&gt;"")*(Grayana!I$2:I1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!I$2:I1000,Grayana!I$2:I1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!I$2:I1000,Grayana!I$2:I1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!I$2:I1000,Grayana!I$2:I1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Grayana!I$2:I1000,Grayana!I$2:I1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(0.338) 0.338–3.441 (6.625) mm</v>
-      </c>
-      <c r="H46" t="str" cm="1">
-        <f t="array" ref="H46">"(" &amp; MIN(_xlfn._xlws.FILTER(Grayana!J$2:J1000,Grayana!J$2:J1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Grayana!J$2:J1000,(Grayana!J$2:J1000&lt;&gt;"")*(Grayana!J$2:J1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!J$2:J1000,Grayana!J$2:J1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!J$2:J1000,Grayana!J$2:J1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!J$2:J1000,Grayana!J$2:J1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Grayana!J$2:J1000,(Grayana!J$2:J1000&lt;&gt;"")*(Grayana!J$2:J1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!J$2:J1000,Grayana!J$2:J1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!J$2:J1000,Grayana!J$2:J1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!J$2:J1000,Grayana!J$2:J1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Grayana!J$2:J1000,Grayana!J$2:J1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(4.171) 4.171–9.812 (9.812) mm</v>
-      </c>
-      <c r="I46" t="str" cm="1">
-        <f t="array" ref="I46">"(" &amp; MIN(_xlfn._xlws.FILTER(Grayana!K$2:K1000,Grayana!K$2:K1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Grayana!K$2:K1000,(Grayana!K$2:K1000&lt;&gt;"")*(Grayana!K$2:K1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!K$2:K1000,Grayana!K$2:K1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!K$2:K1000,Grayana!K$2:K1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!K$2:K1000,Grayana!K$2:K1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Grayana!K$2:K1000,(Grayana!K$2:K1000&lt;&gt;"")*(Grayana!K$2:K1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!K$2:K1000,Grayana!K$2:K1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!K$2:K1000,Grayana!K$2:K1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!K$2:K1000,Grayana!K$2:K1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Grayana!K$2:K1000,Grayana!K$2:K1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(1.853) 1.853–4.833 (4.833) mm</v>
-      </c>
-      <c r="J46" t="str" cm="1">
-        <f t="array" ref="J46">"(" &amp; MIN(_xlfn._xlws.FILTER(Grayana!L$2:L1000,Grayana!L$2:L1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Grayana!L$2:L1000,(Grayana!L$2:L1000&lt;&gt;"")*(Grayana!L$2:L1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!L$2:L1000,Grayana!L$2:L1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!L$2:L1000,Grayana!L$2:L1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!L$2:L1000,Grayana!L$2:L1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Grayana!L$2:L1000,(Grayana!L$2:L1000&lt;&gt;"")*(Grayana!L$2:L1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!L$2:L1000,Grayana!L$2:L1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!L$2:L1000,Grayana!L$2:L1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!L$2:L1000,Grayana!L$2:L1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Grayana!L$2:L1000,Grayana!L$2:L1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(0.726) 0.726–3.423 (3.423) mm</v>
-      </c>
-      <c r="K46" t="str" cm="1">
-        <f t="array" ref="K46">"(" &amp; MIN(_xlfn._xlws.FILTER(Grayana!M$2:M1000,Grayana!M$2:M1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Grayana!M$2:M1000,(Grayana!M$2:M1000&lt;&gt;"")*(Grayana!M$2:M1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!M$2:M1000,Grayana!M$2:M1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!M$2:M1000,Grayana!M$2:M1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!M$2:M1000,Grayana!M$2:M1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Grayana!M$2:M1000,(Grayana!M$2:M1000&lt;&gt;"")*(Grayana!M$2:M1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!M$2:M1000,Grayana!M$2:M1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!M$2:M1000,Grayana!M$2:M1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!M$2:M1000,Grayana!M$2:M1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Grayana!M$2:M1000,Grayana!M$2:M1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(1.737) 1.737–3.345 (3.345) mm</v>
-      </c>
-      <c r="L46" t="str" cm="1">
-        <f t="array" ref="L46">"(" &amp; MIN(_xlfn._xlws.FILTER(Grayana!N$2:N1000,Grayana!N$2:N1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Grayana!N$2:N1000,(Grayana!N$2:N1000&lt;&gt;"")*(Grayana!N$2:N1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!N$2:N1000,Grayana!N$2:N1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!N$2:N1000,Grayana!N$2:N1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!N$2:N1000,Grayana!N$2:N1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Grayana!N$2:N1000,(Grayana!N$2:N1000&lt;&gt;"")*(Grayana!N$2:N1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!N$2:N1000,Grayana!N$2:N1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!N$2:N1000,Grayana!N$2:N1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!N$2:N1000,Grayana!N$2:N1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Grayana!N$2:N1000,Grayana!N$2:N1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(1.126) 1.126–3.399 (4.268) mm</v>
-      </c>
-      <c r="M46" t="str" cm="1">
-        <f t="array" ref="M46">"(" &amp; MIN(_xlfn._xlws.FILTER(Grayana!O$2:O1000,Grayana!O$2:O1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Grayana!O$2:O1000,(Grayana!O$2:O1000&lt;&gt;"")*(Grayana!O$2:O1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!O$2:O1000,Grayana!O$2:O1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!O$2:O1000,Grayana!O$2:O1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!O$2:O1000,Grayana!O$2:O1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Grayana!O$2:O1000,(Grayana!O$2:O1000&lt;&gt;"")*(Grayana!O$2:O1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!O$2:O1000,Grayana!O$2:O1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!O$2:O1000,Grayana!O$2:O1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!O$2:O1000,Grayana!O$2:O1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Grayana!O$2:O1000,Grayana!O$2:O1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(0.81) 0.81–4.067 (4.067) mm</v>
-      </c>
-      <c r="N46" t="str" cm="1">
-        <f t="array" ref="N46">"(" &amp; MIN(_xlfn._xlws.FILTER(Grayana!P$2:P1000,Grayana!P$2:P1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Grayana!P$2:P1000,(Grayana!P$2:P1000&lt;&gt;"")*(Grayana!P$2:P1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!P$2:P1000,Grayana!P$2:P1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!P$2:P1000,Grayana!P$2:P1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!P$2:P1000,Grayana!P$2:P1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Grayana!P$2:P1000,(Grayana!P$2:P1000&lt;&gt;"")*(Grayana!P$2:P1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!P$2:P1000,Grayana!P$2:P1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!P$2:P1000,Grayana!P$2:P1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!P$2:P1000,Grayana!P$2:P1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Grayana!P$2:P1000,Grayana!P$2:P1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(0.855) 0.855–5.104 (7.715) mm</v>
-      </c>
-      <c r="O46" t="str" cm="1">
-        <f t="array" ref="O46">"(" &amp; MIN(_xlfn._xlws.FILTER(Grayana!Q$2:Q1000,Grayana!Q$2:Q1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Grayana!Q$2:Q1000,(Grayana!Q$2:Q1000&lt;&gt;"")*(Grayana!Q$2:Q1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!Q$2:Q1000,Grayana!Q$2:Q1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!Q$2:Q1000,Grayana!Q$2:Q1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!Q$2:Q1000,Grayana!Q$2:Q1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Grayana!Q$2:Q1000,(Grayana!Q$2:Q1000&lt;&gt;"")*(Grayana!Q$2:Q1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!Q$2:Q1000,Grayana!Q$2:Q1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!Q$2:Q1000,Grayana!Q$2:Q1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!Q$2:Q1000,Grayana!Q$2:Q1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Grayana!Q$2:Q1000,Grayana!Q$2:Q1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(2.506) 2.506–21.293 (25.578) mm</v>
-      </c>
-      <c r="P46" t="str" cm="1">
-        <f t="array" ref="P46">"(" &amp; MIN(_xlfn._xlws.FILTER(Grayana!R$2:R1000,Grayana!R$2:R1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Grayana!R$2:R1000,(Grayana!R$2:R1000&lt;&gt;"")*(Grayana!R$2:R1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!R$2:R1000,Grayana!R$2:R1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!R$2:R1000,Grayana!R$2:R1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!R$2:R1000,Grayana!R$2:R1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Grayana!R$2:R1000,(Grayana!R$2:R1000&lt;&gt;"")*(Grayana!R$2:R1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!R$2:R1000,Grayana!R$2:R1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!R$2:R1000,Grayana!R$2:R1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Grayana!R$2:R1000,Grayana!R$2:R1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Grayana!R$2:R1000,Grayana!R$2:R1000&lt;&gt;"")) &amp; ") mm"</f>
-        <v>(380.751) 380.751–874.667 (874.667) mm</v>
+      <c r="C46" t="str">
+        <f>"(" &amp; IF(MIN(Grayana!E$2:E$1000)&lt;_xlfn.QUARTILE.INC(Grayana!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Grayana!E$2:E$1000,1)),MIN(Grayana!E$2:E$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Grayana!E$2:E$1000, Grayana!E$2:E$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Grayana!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Grayana!E$2:E$1000,1)), Grayana!E$2:E$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Grayana!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Grayana!E$2:E$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Grayana!E$2:E$1000, Grayana!E$2:E$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Grayana!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Grayana!E$2:E$1000,1)), Grayana!E$2:E$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Grayana!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Grayana!E$2:E$1000,1))) &amp; " (" &amp; IF(MAX(Grayana!E$2:E$1000)&gt;_xlfn.QUARTILE.INC(Grayana!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Grayana!E$2:E$1000,1)),MAX(Grayana!E$2:E$1000),"") &amp; ") mm"</f>
+        <v>() 0.804–2.26 (2.361) mm</v>
+      </c>
+      <c r="D46" t="str">
+        <f>"(" &amp; IF(MIN(Grayana!F$2:F$1000)&lt;_xlfn.QUARTILE.INC(Grayana!F$2:F$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Grayana!F$2:F$1000,1)),MIN(Grayana!F$2:F$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Grayana!F$2:F$1000, Grayana!F$2:F$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Grayana!F$2:F$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Grayana!F$2:F$1000,1)), Grayana!F$2:F$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Grayana!F$2:F$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Grayana!F$2:F$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Grayana!F$2:F$1000, Grayana!F$2:F$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Grayana!F$2:F$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Grayana!F$2:F$1000,1)), Grayana!F$2:F$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Grayana!F$2:F$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Grayana!F$2:F$1000,1))) &amp; " (" &amp; IF(MAX(Grayana!F$2:F$1000)&gt;_xlfn.QUARTILE.INC(Grayana!F$2:F$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Grayana!F$2:F$1000,1)),MAX(Grayana!F$2:F$1000),"") &amp; ") mm"</f>
+        <v>() 0.514–1.19 (1.245) mm</v>
+      </c>
+      <c r="E46" t="str">
+        <f>"(" &amp; IF(MIN(Grayana!G$2:G$1000)&lt;_xlfn.QUARTILE.INC(Grayana!G$2:G$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Grayana!G$2:G$1000,1)),MIN(Grayana!G$2:G$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Grayana!G$2:G$1000, Grayana!G$2:G$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Grayana!G$2:G$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Grayana!G$2:G$1000,1)), Grayana!G$2:G$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Grayana!G$2:G$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Grayana!G$2:G$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Grayana!G$2:G$1000, Grayana!G$2:G$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Grayana!G$2:G$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Grayana!G$2:G$1000,1)), Grayana!G$2:G$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Grayana!G$2:G$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Grayana!G$2:G$1000,1))) &amp; " (" &amp; IF(MAX(Grayana!G$2:G$1000)&gt;_xlfn.QUARTILE.INC(Grayana!G$2:G$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Grayana!G$2:G$1000,1)),MAX(Grayana!G$2:G$1000),"") &amp; ") mm"</f>
+        <v>() 0–0 () mm</v>
+      </c>
+      <c r="F46" t="str">
+        <f>"(" &amp; IF(MIN(Grayana!H$2:H$1000)&lt;_xlfn.QUARTILE.INC(Grayana!H$2:H$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Grayana!H$2:H$1000,1)),MIN(Grayana!H$2:H$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Grayana!H$2:H$1000, Grayana!H$2:H$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Grayana!H$2:H$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Grayana!H$2:H$1000,1)), Grayana!H$2:H$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Grayana!H$2:H$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Grayana!H$2:H$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Grayana!H$2:H$1000, Grayana!H$2:H$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Grayana!H$2:H$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Grayana!H$2:H$1000,1)), Grayana!H$2:H$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Grayana!H$2:H$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Grayana!H$2:H$1000,1))) &amp; " (" &amp; IF(MAX(Grayana!H$2:H$1000)&gt;_xlfn.QUARTILE.INC(Grayana!H$2:H$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Grayana!H$2:H$1000,1)),MAX(Grayana!H$2:H$1000),"") &amp; ") mm"</f>
+        <v>() 2.483–9.211 (9.87) mm</v>
+      </c>
+      <c r="G46" t="str">
+        <f>"(" &amp; IF(MIN(Grayana!I$2:I$1000)&lt;_xlfn.QUARTILE.INC(Grayana!I$2:I$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Grayana!I$2:I$1000,1)),MIN(Grayana!I$2:I$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Grayana!I$2:I$1000, Grayana!I$2:I$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Grayana!I$2:I$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Grayana!I$2:I$1000,1)), Grayana!I$2:I$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Grayana!I$2:I$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Grayana!I$2:I$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Grayana!I$2:I$1000, Grayana!I$2:I$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Grayana!I$2:I$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Grayana!I$2:I$1000,1)), Grayana!I$2:I$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Grayana!I$2:I$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Grayana!I$2:I$1000,1))) &amp; " (" &amp; IF(MAX(Grayana!I$2:I$1000)&gt;_xlfn.QUARTILE.INC(Grayana!I$2:I$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Grayana!I$2:I$1000,1)),MAX(Grayana!I$2:I$1000),"") &amp; ") mm"</f>
+        <v>() 0.338–3.441 (6.625) mm</v>
+      </c>
+      <c r="H46" t="str">
+        <f>"(" &amp; IF(MIN(Grayana!J$2:J$1000)&lt;_xlfn.QUARTILE.INC(Grayana!J$2:J$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Grayana!J$2:J$1000,1)),MIN(Grayana!J$2:J$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Grayana!J$2:J$1000, Grayana!J$2:J$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Grayana!J$2:J$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Grayana!J$2:J$1000,1)), Grayana!J$2:J$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Grayana!J$2:J$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Grayana!J$2:J$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Grayana!J$2:J$1000, Grayana!J$2:J$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Grayana!J$2:J$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Grayana!J$2:J$1000,1)), Grayana!J$2:J$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Grayana!J$2:J$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Grayana!J$2:J$1000,1))) &amp; " (" &amp; IF(MAX(Grayana!J$2:J$1000)&gt;_xlfn.QUARTILE.INC(Grayana!J$2:J$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Grayana!J$2:J$1000,1)),MAX(Grayana!J$2:J$1000),"") &amp; ") mm"</f>
+        <v>() 4.171–9.812 () mm</v>
+      </c>
+      <c r="I46" t="str">
+        <f>"(" &amp; IF(MIN(Grayana!K$2:K$1000)&lt;_xlfn.QUARTILE.INC(Grayana!K$2:K$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Grayana!K$2:K$1000,1)),MIN(Grayana!K$2:K$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Grayana!K$2:K$1000, Grayana!K$2:K$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Grayana!K$2:K$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Grayana!K$2:K$1000,1)), Grayana!K$2:K$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Grayana!K$2:K$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Grayana!K$2:K$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Grayana!K$2:K$1000, Grayana!K$2:K$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Grayana!K$2:K$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Grayana!K$2:K$1000,1)), Grayana!K$2:K$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Grayana!K$2:K$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Grayana!K$2:K$1000,1))) &amp; " (" &amp; IF(MAX(Grayana!K$2:K$1000)&gt;_xlfn.QUARTILE.INC(Grayana!K$2:K$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Grayana!K$2:K$1000,1)),MAX(Grayana!K$2:K$1000),"") &amp; ") mm"</f>
+        <v>() 1.853–4.833 () mm</v>
+      </c>
+      <c r="J46" t="str">
+        <f>"(" &amp; IF(MIN(Grayana!L$2:L$1000)&lt;_xlfn.QUARTILE.INC(Grayana!L$2:L$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Grayana!L$2:L$1000,1)),MIN(Grayana!L$2:L$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Grayana!L$2:L$1000, Grayana!L$2:L$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Grayana!L$2:L$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Grayana!L$2:L$1000,1)), Grayana!L$2:L$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Grayana!L$2:L$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Grayana!L$2:L$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Grayana!L$2:L$1000, Grayana!L$2:L$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Grayana!L$2:L$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Grayana!L$2:L$1000,1)), Grayana!L$2:L$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Grayana!L$2:L$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Grayana!L$2:L$1000,1))) &amp; " (" &amp; IF(MAX(Grayana!L$2:L$1000)&gt;_xlfn.QUARTILE.INC(Grayana!L$2:L$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Grayana!L$2:L$1000,1)),MAX(Grayana!L$2:L$1000),"") &amp; ") mm"</f>
+        <v>() 0.726–3.423 () mm</v>
+      </c>
+      <c r="K46" t="str">
+        <f>"(" &amp; IF(MIN(Grayana!M$2:M$1000)&lt;_xlfn.QUARTILE.INC(Grayana!M$2:M$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Grayana!M$2:M$1000,1)),MIN(Grayana!M$2:M$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Grayana!M$2:M$1000, Grayana!M$2:M$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Grayana!M$2:M$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Grayana!M$2:M$1000,1)), Grayana!M$2:M$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Grayana!M$2:M$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Grayana!M$2:M$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Grayana!M$2:M$1000, Grayana!M$2:M$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Grayana!M$2:M$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Grayana!M$2:M$1000,1)), Grayana!M$2:M$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Grayana!M$2:M$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Grayana!M$2:M$1000,1))) &amp; " (" &amp; IF(MAX(Grayana!M$2:M$1000)&gt;_xlfn.QUARTILE.INC(Grayana!M$2:M$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Grayana!M$2:M$1000,1)),MAX(Grayana!M$2:M$1000),"") &amp; ") mm"</f>
+        <v>() 1.737–3.345 () mm</v>
+      </c>
+      <c r="L46" t="str">
+        <f>"(" &amp; IF(MIN(Grayana!N$2:N$1000)&lt;_xlfn.QUARTILE.INC(Grayana!N$2:N$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Grayana!N$2:N$1000,1)),MIN(Grayana!N$2:N$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Grayana!N$2:N$1000, Grayana!N$2:N$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Grayana!N$2:N$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Grayana!N$2:N$1000,1)), Grayana!N$2:N$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Grayana!N$2:N$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Grayana!N$2:N$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Grayana!N$2:N$1000, Grayana!N$2:N$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Grayana!N$2:N$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Grayana!N$2:N$1000,1)), Grayana!N$2:N$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Grayana!N$2:N$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Grayana!N$2:N$1000,1))) &amp; " (" &amp; IF(MAX(Grayana!N$2:N$1000)&gt;_xlfn.QUARTILE.INC(Grayana!N$2:N$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Grayana!N$2:N$1000,1)),MAX(Grayana!N$2:N$1000),"") &amp; ") mm"</f>
+        <v>() 1.126–3.399 (4.268) mm</v>
+      </c>
+      <c r="M46" t="str">
+        <f>"(" &amp; IF(MIN(Grayana!O$2:O$1000)&lt;_xlfn.QUARTILE.INC(Grayana!O$2:O$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Grayana!O$2:O$1000,1)),MIN(Grayana!O$2:O$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Grayana!O$2:O$1000, Grayana!O$2:O$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Grayana!O$2:O$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Grayana!O$2:O$1000,1)), Grayana!O$2:O$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Grayana!O$2:O$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Grayana!O$2:O$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Grayana!O$2:O$1000, Grayana!O$2:O$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Grayana!O$2:O$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Grayana!O$2:O$1000,1)), Grayana!O$2:O$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Grayana!O$2:O$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Grayana!O$2:O$1000,1))) &amp; " (" &amp; IF(MAX(Grayana!O$2:O$1000)&gt;_xlfn.QUARTILE.INC(Grayana!O$2:O$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Grayana!O$2:O$1000,1)),MAX(Grayana!O$2:O$1000),"") &amp; ") mm"</f>
+        <v>() 0.81–4.067 () mm</v>
+      </c>
+      <c r="N46" t="str">
+        <f>"(" &amp; IF(MIN(Grayana!P$2:P$1000)&lt;_xlfn.QUARTILE.INC(Grayana!P$2:P$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Grayana!P$2:P$1000,1)),MIN(Grayana!P$2:P$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Grayana!P$2:P$1000, Grayana!P$2:P$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Grayana!P$2:P$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Grayana!P$2:P$1000,1)), Grayana!P$2:P$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Grayana!P$2:P$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Grayana!P$2:P$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Grayana!P$2:P$1000, Grayana!P$2:P$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Grayana!P$2:P$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Grayana!P$2:P$1000,1)), Grayana!P$2:P$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Grayana!P$2:P$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Grayana!P$2:P$1000,1))) &amp; " (" &amp; IF(MAX(Grayana!P$2:P$1000)&gt;_xlfn.QUARTILE.INC(Grayana!P$2:P$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Grayana!P$2:P$1000,1)),MAX(Grayana!P$2:P$1000),"") &amp; ") mm"</f>
+        <v>() 0.855–5.104 (7.715) mm</v>
+      </c>
+      <c r="O46" t="str">
+        <f>"(" &amp; IF(MIN(Grayana!Q$2:Q$1000)&lt;_xlfn.QUARTILE.INC(Grayana!Q$2:Q$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Grayana!Q$2:Q$1000,1)),MIN(Grayana!Q$2:Q$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Grayana!Q$2:Q$1000, Grayana!Q$2:Q$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Grayana!Q$2:Q$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Grayana!Q$2:Q$1000,1)), Grayana!Q$2:Q$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Grayana!Q$2:Q$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Grayana!Q$2:Q$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Grayana!Q$2:Q$1000, Grayana!Q$2:Q$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Grayana!Q$2:Q$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Grayana!Q$2:Q$1000,1)), Grayana!Q$2:Q$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Grayana!Q$2:Q$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Grayana!Q$2:Q$1000,1))) &amp; " (" &amp; IF(MAX(Grayana!Q$2:Q$1000)&gt;_xlfn.QUARTILE.INC(Grayana!Q$2:Q$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Grayana!Q$2:Q$1000,1)),MAX(Grayana!Q$2:Q$1000),"") &amp; ") mm"</f>
+        <v>() 2.506–21.293 (25.578) mm</v>
+      </c>
+      <c r="P46" t="str">
+        <f>"(" &amp; IF(MIN(Grayana!R$2:R$1000)&lt;_xlfn.QUARTILE.INC(Grayana!R$2:R$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Grayana!R$2:R$1000,1)),MIN(Grayana!R$2:R$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Grayana!R$2:R$1000, Grayana!R$2:R$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Grayana!R$2:R$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Grayana!R$2:R$1000,1)), Grayana!R$2:R$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Grayana!R$2:R$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Grayana!R$2:R$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Grayana!R$2:R$1000, Grayana!R$2:R$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Grayana!R$2:R$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Grayana!R$2:R$1000,1)), Grayana!R$2:R$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Grayana!R$2:R$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Grayana!R$2:R$1000,1))) &amp; " (" &amp; IF(MAX(Grayana!R$2:R$1000)&gt;_xlfn.QUARTILE.INC(Grayana!R$2:R$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Grayana!R$2:R$1000,1)),MAX(Grayana!R$2:R$1000),"") &amp; ") mm"</f>
+        <v>() 380.751–874.667 () mm</v>
       </c>
     </row>
     <row r="47" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -5034,61 +5056,61 @@
       <c r="B55" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C55" s="2" t="str" cm="1">
-        <f t="array" ref="C55">"(" &amp; MIN(_xlfn._xlws.FILTER(Richardsonii!E$2:E1000,Richardsonii!E$2:E1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Richardsonii!E$2:E1000,(Richardsonii!E$2:E1000&lt;&gt;"")*(Richardsonii!E$2:E1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!E$2:E1000,Richardsonii!E$2:E1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!E$2:E1000,Richardsonii!E$2:E1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!E$2:E1000,Richardsonii!E$2:E1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Richardsonii!E$2:E1000,(Richardsonii!E$2:E1000&lt;&gt;"")*(Richardsonii!E$2:E1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!E$2:E1000,Richardsonii!E$2:E1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!E$2:E1000,Richardsonii!E$2:E1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!E$2:E1000,Richardsonii!E$2:E1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Richardsonii!E$2:E1000,Richardsonii!E$2:E1000&lt;&gt;"" )) &amp; ") mm"</f>
+      <c r="C55" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Richardsonii!E$2:E$1000)&lt;_xlfn.QUARTILE.INC(Richardsonii!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!E$2:E$1000,1)),MIN(Richardsonii!E$2:E$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Richardsonii!E$2:E$1000, Richardsonii!E$2:E$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!E$2:E$1000,1)), Richardsonii!E$2:E$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!E$2:E$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Richardsonii!E$2:E$1000, Richardsonii!E$2:E$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!E$2:E$1000,1)), Richardsonii!E$2:E$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!E$2:E$1000,1))) &amp; " (" &amp; IF(MAX(Richardsonii!E$2:E$1000)&gt;_xlfn.QUARTILE.INC(Richardsonii!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!E$2:E$1000,1)),MAX(Richardsonii!E$2:E$1000),"") &amp; ") mm"</f>
         <v>(0) 0.707–1.79 (2.57) mm</v>
       </c>
-      <c r="D55" s="2" t="str" cm="1">
-        <f t="array" ref="D55">"(" &amp; MIN(_xlfn._xlws.FILTER(Richardsonii!F$2:F1000,Richardsonii!F$2:F1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Richardsonii!F$2:F1000,(Richardsonii!F$2:F1000&lt;&gt;"")*(Richardsonii!F$2:F1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!F$2:F1000,Richardsonii!F$2:F1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!F$2:F1000,Richardsonii!F$2:F1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!F$2:F1000,Richardsonii!F$2:F1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Richardsonii!F$2:F1000,(Richardsonii!F$2:F1000&lt;&gt;"")*(Richardsonii!F$2:F1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!F$2:F1000,Richardsonii!F$2:F1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!F$2:F1000,Richardsonii!F$2:F1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!F$2:F1000,Richardsonii!F$2:F1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Richardsonii!F$2:F1000,Richardsonii!F$2:F1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(0) 0–1.22 (1.22) mm</v>
-      </c>
-      <c r="E55" s="2" t="str" cm="1">
-        <f t="array" ref="E55">"(" &amp; MIN(_xlfn._xlws.FILTER(Richardsonii!G$2:G1000,Richardsonii!G$2:G1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Richardsonii!G$2:G1000,(Richardsonii!G$2:G1000&lt;&gt;"")*(Richardsonii!G$2:G1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!G$2:G1000,Richardsonii!G$2:G1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!G$2:G1000,Richardsonii!G$2:G1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!G$2:G1000,Richardsonii!G$2:G1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Richardsonii!G$2:G1000,(Richardsonii!G$2:G1000&lt;&gt;"")*(Richardsonii!G$2:G1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!G$2:G1000,Richardsonii!G$2:G1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!G$2:G1000,Richardsonii!G$2:G1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!G$2:G1000,Richardsonii!G$2:G1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Richardsonii!G$2:G1000,Richardsonii!G$2:G1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(0) 0–0 (0.73) mm</v>
-      </c>
-      <c r="F55" s="2" t="str" cm="1">
-        <f t="array" ref="F55">"(" &amp; MIN(_xlfn._xlws.FILTER(Richardsonii!H$2:H1000,Richardsonii!H$2:H1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Richardsonii!H$2:H1000,(Richardsonii!H$2:H1000&lt;&gt;"")*(Richardsonii!H$2:H1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!H$2:H1000,Richardsonii!H$2:H1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!H$2:H1000,Richardsonii!H$2:H1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!H$2:H1000,Richardsonii!H$2:H1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Richardsonii!H$2:H1000,(Richardsonii!H$2:H1000&lt;&gt;"")*(Richardsonii!H$2:H1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!H$2:H1000,Richardsonii!H$2:H1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!H$2:H1000,Richardsonii!H$2:H1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!H$2:H1000,Richardsonii!H$2:H1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Richardsonii!H$2:H1000,Richardsonii!H$2:H1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(1.09) 1.09–6.228 (9.386) mm</v>
-      </c>
-      <c r="G55" s="2" t="str" cm="1">
-        <f t="array" ref="G55">"(" &amp; MIN(_xlfn._xlws.FILTER(Richardsonii!I$2:I1000,Richardsonii!I$2:I1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Richardsonii!I$2:I1000,(Richardsonii!I$2:I1000&lt;&gt;"")*(Richardsonii!I$2:I1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!I$2:I1000,Richardsonii!I$2:I1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!I$2:I1000,Richardsonii!I$2:I1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!I$2:I1000,Richardsonii!I$2:I1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Richardsonii!I$2:I1000,(Richardsonii!I$2:I1000&lt;&gt;"")*(Richardsonii!I$2:I1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!I$2:I1000,Richardsonii!I$2:I1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!I$2:I1000,Richardsonii!I$2:I1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!I$2:I1000,Richardsonii!I$2:I1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Richardsonii!I$2:I1000,Richardsonii!I$2:I1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(0.316) 0.316–3.372 (4.97) mm</v>
-      </c>
-      <c r="H55" s="2" t="str" cm="1">
-        <f t="array" ref="H55">"(" &amp; MIN(_xlfn._xlws.FILTER(Richardsonii!J$2:J1000,Richardsonii!J$2:J1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Richardsonii!J$2:J1000,(Richardsonii!J$2:J1000&lt;&gt;"")*(Richardsonii!J$2:J1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!J$2:J1000,Richardsonii!J$2:J1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!J$2:J1000,Richardsonii!J$2:J1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!J$2:J1000,Richardsonii!J$2:J1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Richardsonii!J$2:J1000,(Richardsonii!J$2:J1000&lt;&gt;"")*(Richardsonii!J$2:J1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!J$2:J1000,Richardsonii!J$2:J1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!J$2:J1000,Richardsonii!J$2:J1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!J$2:J1000,Richardsonii!J$2:J1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Richardsonii!J$2:J1000,Richardsonii!J$2:J1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(2.784) 2.784–10.104 (10.104) mm</v>
-      </c>
-      <c r="I55" s="2" t="str" cm="1">
-        <f t="array" ref="I55">"(" &amp; MIN(_xlfn._xlws.FILTER(Richardsonii!K$2:K1000,Richardsonii!K$2:K1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Richardsonii!K$2:K1000,(Richardsonii!K$2:K1000&lt;&gt;"")*(Richardsonii!K$2:K1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!K$2:K1000,Richardsonii!K$2:K1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!K$2:K1000,Richardsonii!K$2:K1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!K$2:K1000,Richardsonii!K$2:K1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Richardsonii!K$2:K1000,(Richardsonii!K$2:K1000&lt;&gt;"")*(Richardsonii!K$2:K1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!K$2:K1000,Richardsonii!K$2:K1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!K$2:K1000,Richardsonii!K$2:K1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!K$2:K1000,Richardsonii!K$2:K1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Richardsonii!K$2:K1000,Richardsonii!K$2:K1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(1.655) 1.8–5.289 (5.289) mm</v>
-      </c>
-      <c r="J55" s="2" t="str" cm="1">
-        <f t="array" ref="J55">"(" &amp; MIN(_xlfn._xlws.FILTER(Richardsonii!L$2:L1000,Richardsonii!L$2:L1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Richardsonii!L$2:L1000,(Richardsonii!L$2:L1000&lt;&gt;"")*(Richardsonii!L$2:L1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!L$2:L1000,Richardsonii!L$2:L1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!L$2:L1000,Richardsonii!L$2:L1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!L$2:L1000,Richardsonii!L$2:L1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Richardsonii!L$2:L1000,(Richardsonii!L$2:L1000&lt;&gt;"")*(Richardsonii!L$2:L1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!L$2:L1000,Richardsonii!L$2:L1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!L$2:L1000,Richardsonii!L$2:L1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!L$2:L1000,Richardsonii!L$2:L1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Richardsonii!L$2:L1000,Richardsonii!L$2:L1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(0.78) 0.78–3.949 (3.949) mm</v>
-      </c>
-      <c r="K55" s="2" t="str" cm="1">
-        <f t="array" ref="K55">"(" &amp; MIN(_xlfn._xlws.FILTER(Richardsonii!M$2:M1000,Richardsonii!M$2:M1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Richardsonii!M$2:M1000,(Richardsonii!M$2:M1000&lt;&gt;"")*(Richardsonii!M$2:M1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!M$2:M1000,Richardsonii!M$2:M1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!M$2:M1000,Richardsonii!M$2:M1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!M$2:M1000,Richardsonii!M$2:M1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Richardsonii!M$2:M1000,(Richardsonii!M$2:M1000&lt;&gt;"")*(Richardsonii!M$2:M1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!M$2:M1000,Richardsonii!M$2:M1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!M$2:M1000,Richardsonii!M$2:M1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!M$2:M1000,Richardsonii!M$2:M1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Richardsonii!M$2:M1000,Richardsonii!M$2:M1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(1.653) 1.653–5.562 (5.562) mm</v>
-      </c>
-      <c r="L55" s="2" t="str" cm="1">
-        <f t="array" ref="L55">"(" &amp; MIN(_xlfn._xlws.FILTER(Richardsonii!N$2:N1000,Richardsonii!N$2:N1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Richardsonii!N$2:N1000,(Richardsonii!N$2:N1000&lt;&gt;"")*(Richardsonii!N$2:N1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!N$2:N1000,Richardsonii!N$2:N1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!N$2:N1000,Richardsonii!N$2:N1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!N$2:N1000,Richardsonii!N$2:N1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Richardsonii!N$2:N1000,(Richardsonii!N$2:N1000&lt;&gt;"")*(Richardsonii!N$2:N1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!N$2:N1000,Richardsonii!N$2:N1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!N$2:N1000,Richardsonii!N$2:N1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!N$2:N1000,Richardsonii!N$2:N1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Richardsonii!N$2:N1000,Richardsonii!N$2:N1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(1.036) 1.036–3.001 (3.896) mm</v>
-      </c>
-      <c r="M55" s="2" t="str" cm="1">
-        <f t="array" ref="M55">"(" &amp; MIN(_xlfn._xlws.FILTER(Richardsonii!O$2:O1000,Richardsonii!O$2:O1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Richardsonii!O$2:O1000,(Richardsonii!O$2:O1000&lt;&gt;"")*(Richardsonii!O$2:O1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!O$2:O1000,Richardsonii!O$2:O1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!O$2:O1000,Richardsonii!O$2:O1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!O$2:O1000,Richardsonii!O$2:O1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Richardsonii!O$2:O1000,(Richardsonii!O$2:O1000&lt;&gt;"")*(Richardsonii!O$2:O1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!O$2:O1000,Richardsonii!O$2:O1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!O$2:O1000,Richardsonii!O$2:O1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!O$2:O1000,Richardsonii!O$2:O1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Richardsonii!O$2:O1000,Richardsonii!O$2:O1000&lt;&gt;"" )) &amp; ") mm"</f>
+      <c r="D55" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Richardsonii!F$2:F$1000)&lt;_xlfn.QUARTILE.INC(Richardsonii!F$2:F$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!F$2:F$1000,1)),MIN(Richardsonii!F$2:F$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Richardsonii!F$2:F$1000, Richardsonii!F$2:F$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!F$2:F$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!F$2:F$1000,1)), Richardsonii!F$2:F$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!F$2:F$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!F$2:F$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Richardsonii!F$2:F$1000, Richardsonii!F$2:F$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!F$2:F$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!F$2:F$1000,1)), Richardsonii!F$2:F$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!F$2:F$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!F$2:F$1000,1))) &amp; " (" &amp; IF(MAX(Richardsonii!F$2:F$1000)&gt;_xlfn.QUARTILE.INC(Richardsonii!F$2:F$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!F$2:F$1000,1)),MAX(Richardsonii!F$2:F$1000),"") &amp; ") mm"</f>
+        <v>() 0–1.22 () mm</v>
+      </c>
+      <c r="E55" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Richardsonii!G$2:G$1000)&lt;_xlfn.QUARTILE.INC(Richardsonii!G$2:G$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!G$2:G$1000,1)),MIN(Richardsonii!G$2:G$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Richardsonii!G$2:G$1000, Richardsonii!G$2:G$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!G$2:G$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!G$2:G$1000,1)), Richardsonii!G$2:G$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!G$2:G$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!G$2:G$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Richardsonii!G$2:G$1000, Richardsonii!G$2:G$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!G$2:G$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!G$2:G$1000,1)), Richardsonii!G$2:G$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!G$2:G$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!G$2:G$1000,1))) &amp; " (" &amp; IF(MAX(Richardsonii!G$2:G$1000)&gt;_xlfn.QUARTILE.INC(Richardsonii!G$2:G$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!G$2:G$1000,1)),MAX(Richardsonii!G$2:G$1000),"") &amp; ") mm"</f>
+        <v>() 0–0 (0.73) mm</v>
+      </c>
+      <c r="F55" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Richardsonii!H$2:H$1000)&lt;_xlfn.QUARTILE.INC(Richardsonii!H$2:H$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!H$2:H$1000,1)),MIN(Richardsonii!H$2:H$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Richardsonii!H$2:H$1000, Richardsonii!H$2:H$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!H$2:H$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!H$2:H$1000,1)), Richardsonii!H$2:H$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!H$2:H$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!H$2:H$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Richardsonii!H$2:H$1000, Richardsonii!H$2:H$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!H$2:H$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!H$2:H$1000,1)), Richardsonii!H$2:H$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!H$2:H$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!H$2:H$1000,1))) &amp; " (" &amp; IF(MAX(Richardsonii!H$2:H$1000)&gt;_xlfn.QUARTILE.INC(Richardsonii!H$2:H$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!H$2:H$1000,1)),MAX(Richardsonii!H$2:H$1000),"") &amp; ") mm"</f>
+        <v>() 1.09–6.228 (9.386) mm</v>
+      </c>
+      <c r="G55" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Richardsonii!I$2:I$1000)&lt;_xlfn.QUARTILE.INC(Richardsonii!I$2:I$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!I$2:I$1000,1)),MIN(Richardsonii!I$2:I$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Richardsonii!I$2:I$1000, Richardsonii!I$2:I$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!I$2:I$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!I$2:I$1000,1)), Richardsonii!I$2:I$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!I$2:I$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!I$2:I$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Richardsonii!I$2:I$1000, Richardsonii!I$2:I$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!I$2:I$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!I$2:I$1000,1)), Richardsonii!I$2:I$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!I$2:I$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!I$2:I$1000,1))) &amp; " (" &amp; IF(MAX(Richardsonii!I$2:I$1000)&gt;_xlfn.QUARTILE.INC(Richardsonii!I$2:I$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!I$2:I$1000,1)),MAX(Richardsonii!I$2:I$1000),"") &amp; ") mm"</f>
+        <v>() 0.316–3.372 (4.97) mm</v>
+      </c>
+      <c r="H55" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Richardsonii!J$2:J$1000)&lt;_xlfn.QUARTILE.INC(Richardsonii!J$2:J$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!J$2:J$1000,1)),MIN(Richardsonii!J$2:J$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Richardsonii!J$2:J$1000, Richardsonii!J$2:J$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!J$2:J$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!J$2:J$1000,1)), Richardsonii!J$2:J$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!J$2:J$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!J$2:J$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Richardsonii!J$2:J$1000, Richardsonii!J$2:J$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!J$2:J$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!J$2:J$1000,1)), Richardsonii!J$2:J$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!J$2:J$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!J$2:J$1000,1))) &amp; " (" &amp; IF(MAX(Richardsonii!J$2:J$1000)&gt;_xlfn.QUARTILE.INC(Richardsonii!J$2:J$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!J$2:J$1000,1)),MAX(Richardsonii!J$2:J$1000),"") &amp; ") mm"</f>
+        <v>() 2.784–10.104 () mm</v>
+      </c>
+      <c r="I55" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Richardsonii!K$2:K$1000)&lt;_xlfn.QUARTILE.INC(Richardsonii!K$2:K$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!K$2:K$1000,1)),MIN(Richardsonii!K$2:K$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Richardsonii!K$2:K$1000, Richardsonii!K$2:K$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!K$2:K$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!K$2:K$1000,1)), Richardsonii!K$2:K$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!K$2:K$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!K$2:K$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Richardsonii!K$2:K$1000, Richardsonii!K$2:K$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!K$2:K$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!K$2:K$1000,1)), Richardsonii!K$2:K$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!K$2:K$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!K$2:K$1000,1))) &amp; " (" &amp; IF(MAX(Richardsonii!K$2:K$1000)&gt;_xlfn.QUARTILE.INC(Richardsonii!K$2:K$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!K$2:K$1000,1)),MAX(Richardsonii!K$2:K$1000),"") &amp; ") mm"</f>
+        <v>(1.655) 1.8–5.289 () mm</v>
+      </c>
+      <c r="J55" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Richardsonii!L$2:L$1000)&lt;_xlfn.QUARTILE.INC(Richardsonii!L$2:L$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!L$2:L$1000,1)),MIN(Richardsonii!L$2:L$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Richardsonii!L$2:L$1000, Richardsonii!L$2:L$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!L$2:L$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!L$2:L$1000,1)), Richardsonii!L$2:L$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!L$2:L$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!L$2:L$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Richardsonii!L$2:L$1000, Richardsonii!L$2:L$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!L$2:L$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!L$2:L$1000,1)), Richardsonii!L$2:L$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!L$2:L$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!L$2:L$1000,1))) &amp; " (" &amp; IF(MAX(Richardsonii!L$2:L$1000)&gt;_xlfn.QUARTILE.INC(Richardsonii!L$2:L$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!L$2:L$1000,1)),MAX(Richardsonii!L$2:L$1000),"") &amp; ") mm"</f>
+        <v>() 0.78–3.949 () mm</v>
+      </c>
+      <c r="K55" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Richardsonii!M$2:M$1000)&lt;_xlfn.QUARTILE.INC(Richardsonii!M$2:M$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!M$2:M$1000,1)),MIN(Richardsonii!M$2:M$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Richardsonii!M$2:M$1000, Richardsonii!M$2:M$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!M$2:M$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!M$2:M$1000,1)), Richardsonii!M$2:M$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!M$2:M$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!M$2:M$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Richardsonii!M$2:M$1000, Richardsonii!M$2:M$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!M$2:M$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!M$2:M$1000,1)), Richardsonii!M$2:M$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!M$2:M$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!M$2:M$1000,1))) &amp; " (" &amp; IF(MAX(Richardsonii!M$2:M$1000)&gt;_xlfn.QUARTILE.INC(Richardsonii!M$2:M$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!M$2:M$1000,1)),MAX(Richardsonii!M$2:M$1000),"") &amp; ") mm"</f>
+        <v>() 1.653–5.562 () mm</v>
+      </c>
+      <c r="L55" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Richardsonii!N$2:N$1000)&lt;_xlfn.QUARTILE.INC(Richardsonii!N$2:N$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!N$2:N$1000,1)),MIN(Richardsonii!N$2:N$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Richardsonii!N$2:N$1000, Richardsonii!N$2:N$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!N$2:N$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!N$2:N$1000,1)), Richardsonii!N$2:N$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!N$2:N$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!N$2:N$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Richardsonii!N$2:N$1000, Richardsonii!N$2:N$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!N$2:N$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!N$2:N$1000,1)), Richardsonii!N$2:N$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!N$2:N$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!N$2:N$1000,1))) &amp; " (" &amp; IF(MAX(Richardsonii!N$2:N$1000)&gt;_xlfn.QUARTILE.INC(Richardsonii!N$2:N$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!N$2:N$1000,1)),MAX(Richardsonii!N$2:N$1000),"") &amp; ") mm"</f>
+        <v>() 1.036–3.001 (3.896) mm</v>
+      </c>
+      <c r="M55" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Richardsonii!O$2:O$1000)&lt;_xlfn.QUARTILE.INC(Richardsonii!O$2:O$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!O$2:O$1000,1)),MIN(Richardsonii!O$2:O$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Richardsonii!O$2:O$1000, Richardsonii!O$2:O$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!O$2:O$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!O$2:O$1000,1)), Richardsonii!O$2:O$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!O$2:O$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!O$2:O$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Richardsonii!O$2:O$1000, Richardsonii!O$2:O$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!O$2:O$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!O$2:O$1000,1)), Richardsonii!O$2:O$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!O$2:O$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!O$2:O$1000,1))) &amp; " (" &amp; IF(MAX(Richardsonii!O$2:O$1000)&gt;_xlfn.QUARTILE.INC(Richardsonii!O$2:O$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!O$2:O$1000,1)),MAX(Richardsonii!O$2:O$1000),"") &amp; ") mm"</f>
         <v>(0) 0.432–1.57 (2.683) mm</v>
       </c>
-      <c r="N55" s="2" t="str" cm="1">
-        <f t="array" ref="N55">"(" &amp; MIN(_xlfn._xlws.FILTER(Richardsonii!P$2:P1000,Richardsonii!P$2:P1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Richardsonii!P$2:P1000,(Richardsonii!P$2:P1000&lt;&gt;"")*(Richardsonii!P$2:P1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!P$2:P1000,Richardsonii!P$2:P1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!P$2:P1000,Richardsonii!P$2:P1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!P$2:P1000,Richardsonii!P$2:P1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Richardsonii!P$2:P1000,(Richardsonii!P$2:P1000&lt;&gt;"")*(Richardsonii!P$2:P1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!P$2:P1000,Richardsonii!P$2:P1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!P$2:P1000,Richardsonii!P$2:P1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!P$2:P1000,Richardsonii!P$2:P1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Richardsonii!P$2:P1000,Richardsonii!P$2:P1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(1.166) 1.166–3.84 (4.584) mm</v>
-      </c>
-      <c r="O55" s="2" t="str" cm="1">
-        <f t="array" ref="O55">"(" &amp; MIN(_xlfn._xlws.FILTER(Richardsonii!Q$2:Q1000,Richardsonii!Q$2:Q1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Richardsonii!Q$2:Q1000,(Richardsonii!Q$2:Q1000&lt;&gt;"")*(Richardsonii!Q$2:Q1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!Q$2:Q1000,Richardsonii!Q$2:Q1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!Q$2:Q1000,Richardsonii!Q$2:Q1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!Q$2:Q1000,Richardsonii!Q$2:Q1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Richardsonii!Q$2:Q1000,(Richardsonii!Q$2:Q1000&lt;&gt;"")*(Richardsonii!Q$2:Q1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!Q$2:Q1000,Richardsonii!Q$2:Q1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!Q$2:Q1000,Richardsonii!Q$2:Q1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!Q$2:Q1000,Richardsonii!Q$2:Q1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Richardsonii!Q$2:Q1000,Richardsonii!Q$2:Q1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(1.784) 1.784–14.27 (14.27) mm</v>
-      </c>
-      <c r="P55" s="2" t="str" cm="1">
-        <f t="array" ref="P55">"(" &amp; MIN(_xlfn._xlws.FILTER(Richardsonii!R$2:R1000,Richardsonii!R$2:R1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Richardsonii!R$2:R1000,(Richardsonii!R$2:R1000&lt;&gt;"")*(Richardsonii!R$2:R1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!R$2:R1000,Richardsonii!R$2:R1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!R$2:R1000,Richardsonii!R$2:R1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!R$2:R1000,Richardsonii!R$2:R1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Richardsonii!R$2:R1000,(Richardsonii!R$2:R1000&lt;&gt;"")*(Richardsonii!R$2:R1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!R$2:R1000,Richardsonii!R$2:R1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!R$2:R1000,Richardsonii!R$2:R1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Richardsonii!R$2:R1000,Richardsonii!R$2:R1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Richardsonii!R$2:R1000,Richardsonii!R$2:R1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(272.047) 272.047–609.68 (673.574) mm</v>
+      <c r="N55" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Richardsonii!P$2:P$1000)&lt;_xlfn.QUARTILE.INC(Richardsonii!P$2:P$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!P$2:P$1000,1)),MIN(Richardsonii!P$2:P$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Richardsonii!P$2:P$1000, Richardsonii!P$2:P$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!P$2:P$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!P$2:P$1000,1)), Richardsonii!P$2:P$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!P$2:P$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!P$2:P$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Richardsonii!P$2:P$1000, Richardsonii!P$2:P$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!P$2:P$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!P$2:P$1000,1)), Richardsonii!P$2:P$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!P$2:P$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!P$2:P$1000,1))) &amp; " (" &amp; IF(MAX(Richardsonii!P$2:P$1000)&gt;_xlfn.QUARTILE.INC(Richardsonii!P$2:P$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!P$2:P$1000,1)),MAX(Richardsonii!P$2:P$1000),"") &amp; ") mm"</f>
+        <v>() 1.166–3.84 (4.584) mm</v>
+      </c>
+      <c r="O55" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Richardsonii!Q$2:Q$1000)&lt;_xlfn.QUARTILE.INC(Richardsonii!Q$2:Q$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!Q$2:Q$1000,1)),MIN(Richardsonii!Q$2:Q$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Richardsonii!Q$2:Q$1000, Richardsonii!Q$2:Q$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!Q$2:Q$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!Q$2:Q$1000,1)), Richardsonii!Q$2:Q$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!Q$2:Q$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!Q$2:Q$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Richardsonii!Q$2:Q$1000, Richardsonii!Q$2:Q$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!Q$2:Q$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!Q$2:Q$1000,1)), Richardsonii!Q$2:Q$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!Q$2:Q$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!Q$2:Q$1000,1))) &amp; " (" &amp; IF(MAX(Richardsonii!Q$2:Q$1000)&gt;_xlfn.QUARTILE.INC(Richardsonii!Q$2:Q$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!Q$2:Q$1000,1)),MAX(Richardsonii!Q$2:Q$1000),"") &amp; ") mm"</f>
+        <v>() 1.784–14.27 () mm</v>
+      </c>
+      <c r="P55" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Richardsonii!R$2:R$1000)&lt;_xlfn.QUARTILE.INC(Richardsonii!R$2:R$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!R$2:R$1000,1)),MIN(Richardsonii!R$2:R$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Richardsonii!R$2:R$1000, Richardsonii!R$2:R$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!R$2:R$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!R$2:R$1000,1)), Richardsonii!R$2:R$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!R$2:R$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!R$2:R$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Richardsonii!R$2:R$1000, Richardsonii!R$2:R$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!R$2:R$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!R$2:R$1000,1)), Richardsonii!R$2:R$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!R$2:R$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!R$2:R$1000,1))) &amp; " (" &amp; IF(MAX(Richardsonii!R$2:R$1000)&gt;_xlfn.QUARTILE.INC(Richardsonii!R$2:R$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!R$2:R$1000,1)),MAX(Richardsonii!R$2:R$1000),"") &amp; ") mm"</f>
+        <v>() 272.047–609.68 (673.574) mm</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.2">
@@ -5603,68 +5625,68 @@
         <v>1052.3879999999999</v>
       </c>
     </row>
-    <row r="64" spans="1:16" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.25">
-      <c r="A64" s="2" t="s">
+    <row r="64" spans="1:16" s="3" customFormat="1" ht="17" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B64" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C64" s="2" t="str" cm="1">
-        <f t="array" ref="C64">"(" &amp; MIN(_xlfn._xlws.FILTER(Hirsuticaulis!E$2:E1000,Hirsuticaulis!E$2:E1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Hirsuticaulis!E$2:E1000,(Hirsuticaulis!E$2:E1000&lt;&gt;"")*(Hirsuticaulis!E$2:E1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!E$2:E1000,Hirsuticaulis!E$2:E1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!E$2:E1000,Hirsuticaulis!E$2:E1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!E$2:E1000,Hirsuticaulis!E$2:E1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Hirsuticaulis!E$2:E1000,(Hirsuticaulis!E$2:E1000&lt;&gt;"")*(Hirsuticaulis!E$2:E1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!E$2:E1000,Hirsuticaulis!E$2:E1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!E$2:E1000,Hirsuticaulis!E$2:E1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!E$2:E1000,Hirsuticaulis!E$2:E1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Hirsuticaulis!E$2:E1000,Hirsuticaulis!E$2:E1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(0.609) 0.609–2.76 (3.542) mm</v>
-      </c>
-      <c r="D64" s="2" t="str" cm="1">
-        <f t="array" ref="D64">"(" &amp; MIN(_xlfn._xlws.FILTER(Hirsuticaulis!F$2:F1000,Hirsuticaulis!F$2:F1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Hirsuticaulis!F$2:F1000,(Hirsuticaulis!F$2:F1000&lt;&gt;"")*(Hirsuticaulis!F$2:F1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!F$2:F1000,Hirsuticaulis!F$2:F1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!F$2:F1000,Hirsuticaulis!F$2:F1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!F$2:F1000,Hirsuticaulis!F$2:F1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Hirsuticaulis!F$2:F1000,(Hirsuticaulis!F$2:F1000&lt;&gt;"")*(Hirsuticaulis!F$2:F1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!F$2:F1000,Hirsuticaulis!F$2:F1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!F$2:F1000,Hirsuticaulis!F$2:F1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!F$2:F1000,Hirsuticaulis!F$2:F1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Hirsuticaulis!F$2:F1000,Hirsuticaulis!F$2:F1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(0.323) 0.323–1.603 (1.972) mm</v>
-      </c>
-      <c r="E64" s="2" t="str" cm="1">
-        <f t="array" ref="E64">"(" &amp; MIN(_xlfn._xlws.FILTER(Hirsuticaulis!G$2:G1000,Hirsuticaulis!G$2:G1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Hirsuticaulis!G$2:G1000,(Hirsuticaulis!G$2:G1000&lt;&gt;"")*(Hirsuticaulis!G$2:G1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!G$2:G1000,Hirsuticaulis!G$2:G1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!G$2:G1000,Hirsuticaulis!G$2:G1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!G$2:G1000,Hirsuticaulis!G$2:G1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Hirsuticaulis!G$2:G1000,(Hirsuticaulis!G$2:G1000&lt;&gt;"")*(Hirsuticaulis!G$2:G1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!G$2:G1000,Hirsuticaulis!G$2:G1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!G$2:G1000,Hirsuticaulis!G$2:G1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!G$2:G1000,Hirsuticaulis!G$2:G1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Hirsuticaulis!G$2:G1000,Hirsuticaulis!G$2:G1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(0) 0–1.575 (1.575) mm</v>
-      </c>
-      <c r="F64" s="2" t="str" cm="1">
-        <f t="array" ref="F64">"(" &amp; MIN(_xlfn._xlws.FILTER(Hirsuticaulis!H$2:H1000,Hirsuticaulis!H$2:H1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Hirsuticaulis!H$2:H1000,(Hirsuticaulis!H$2:H1000&lt;&gt;"")*(Hirsuticaulis!H$2:H1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!H$2:H1000,Hirsuticaulis!H$2:H1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!H$2:H1000,Hirsuticaulis!H$2:H1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!H$2:H1000,Hirsuticaulis!H$2:H1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Hirsuticaulis!H$2:H1000,(Hirsuticaulis!H$2:H1000&lt;&gt;"")*(Hirsuticaulis!H$2:H1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!H$2:H1000,Hirsuticaulis!H$2:H1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!H$2:H1000,Hirsuticaulis!H$2:H1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!H$2:H1000,Hirsuticaulis!H$2:H1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Hirsuticaulis!H$2:H1000,Hirsuticaulis!H$2:H1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(0.958) 0.958–8.605 (9.633) mm</v>
-      </c>
-      <c r="G64" s="2" t="str" cm="1">
-        <f t="array" ref="G64">"(" &amp; MIN(_xlfn._xlws.FILTER(Hirsuticaulis!I$2:I1000,Hirsuticaulis!I$2:I1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Hirsuticaulis!I$2:I1000,(Hirsuticaulis!I$2:I1000&lt;&gt;"")*(Hirsuticaulis!I$2:I1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!I$2:I1000,Hirsuticaulis!I$2:I1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!I$2:I1000,Hirsuticaulis!I$2:I1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!I$2:I1000,Hirsuticaulis!I$2:I1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Hirsuticaulis!I$2:I1000,(Hirsuticaulis!I$2:I1000&lt;&gt;"")*(Hirsuticaulis!I$2:I1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!I$2:I1000,Hirsuticaulis!I$2:I1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!I$2:I1000,Hirsuticaulis!I$2:I1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!I$2:I1000,Hirsuticaulis!I$2:I1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Hirsuticaulis!I$2:I1000,Hirsuticaulis!I$2:I1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(0.114) 0.114–3.458 (4.044) mm</v>
-      </c>
-      <c r="H64" s="2" t="str" cm="1">
-        <f t="array" ref="H64">"(" &amp; MIN(_xlfn._xlws.FILTER(Hirsuticaulis!J$2:J1000,Hirsuticaulis!J$2:J1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Hirsuticaulis!J$2:J1000,(Hirsuticaulis!J$2:J1000&lt;&gt;"")*(Hirsuticaulis!J$2:J1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!J$2:J1000,Hirsuticaulis!J$2:J1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!J$2:J1000,Hirsuticaulis!J$2:J1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!J$2:J1000,Hirsuticaulis!J$2:J1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Hirsuticaulis!J$2:J1000,(Hirsuticaulis!J$2:J1000&lt;&gt;"")*(Hirsuticaulis!J$2:J1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!J$2:J1000,Hirsuticaulis!J$2:J1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!J$2:J1000,Hirsuticaulis!J$2:J1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!J$2:J1000,Hirsuticaulis!J$2:J1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Hirsuticaulis!J$2:J1000,Hirsuticaulis!J$2:J1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(2.34) 2.34–5.299 (6.612) mm</v>
-      </c>
-      <c r="I64" s="2" t="str" cm="1">
-        <f t="array" ref="I64">"(" &amp; MIN(_xlfn._xlws.FILTER(Hirsuticaulis!K$2:K1000,Hirsuticaulis!K$2:K1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Hirsuticaulis!K$2:K1000,(Hirsuticaulis!K$2:K1000&lt;&gt;"")*(Hirsuticaulis!K$2:K1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!K$2:K1000,Hirsuticaulis!K$2:K1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!K$2:K1000,Hirsuticaulis!K$2:K1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!K$2:K1000,Hirsuticaulis!K$2:K1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Hirsuticaulis!K$2:K1000,(Hirsuticaulis!K$2:K1000&lt;&gt;"")*(Hirsuticaulis!K$2:K1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!K$2:K1000,Hirsuticaulis!K$2:K1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!K$2:K1000,Hirsuticaulis!K$2:K1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!K$2:K1000,Hirsuticaulis!K$2:K1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Hirsuticaulis!K$2:K1000,Hirsuticaulis!K$2:K1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(0.695) 0.695–2.194 (3.356) mm</v>
-      </c>
-      <c r="J64" s="2" t="str" cm="1">
-        <f t="array" ref="J64">"(" &amp; MIN(_xlfn._xlws.FILTER(Hirsuticaulis!L$2:L1000,Hirsuticaulis!L$2:L1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Hirsuticaulis!L$2:L1000,(Hirsuticaulis!L$2:L1000&lt;&gt;"")*(Hirsuticaulis!L$2:L1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!L$2:L1000,Hirsuticaulis!L$2:L1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!L$2:L1000,Hirsuticaulis!L$2:L1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!L$2:L1000,Hirsuticaulis!L$2:L1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Hirsuticaulis!L$2:L1000,(Hirsuticaulis!L$2:L1000&lt;&gt;"")*(Hirsuticaulis!L$2:L1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!L$2:L1000,Hirsuticaulis!L$2:L1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!L$2:L1000,Hirsuticaulis!L$2:L1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!L$2:L1000,Hirsuticaulis!L$2:L1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Hirsuticaulis!L$2:L1000,Hirsuticaulis!L$2:L1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(0.444) 0.444–2.158 (2.87) mm</v>
-      </c>
-      <c r="K64" s="2" t="str" cm="1">
-        <f t="array" ref="K64">"(" &amp; MIN(_xlfn._xlws.FILTER(Hirsuticaulis!M$2:M1000,Hirsuticaulis!M$2:M1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Hirsuticaulis!M$2:M1000,(Hirsuticaulis!M$2:M1000&lt;&gt;"")*(Hirsuticaulis!M$2:M1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!M$2:M1000,Hirsuticaulis!M$2:M1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!M$2:M1000,Hirsuticaulis!M$2:M1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!M$2:M1000,Hirsuticaulis!M$2:M1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Hirsuticaulis!M$2:M1000,(Hirsuticaulis!M$2:M1000&lt;&gt;"")*(Hirsuticaulis!M$2:M1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!M$2:M1000,Hirsuticaulis!M$2:M1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!M$2:M1000,Hirsuticaulis!M$2:M1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!M$2:M1000,Hirsuticaulis!M$2:M1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Hirsuticaulis!M$2:M1000,Hirsuticaulis!M$2:M1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(1.159) 1.159–3.46 (4.287) mm</v>
-      </c>
-      <c r="L64" s="2" t="str" cm="1">
-        <f t="array" ref="L64">"(" &amp; MIN(_xlfn._xlws.FILTER(Hirsuticaulis!N$2:N1000,Hirsuticaulis!N$2:N1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Hirsuticaulis!N$2:N1000,(Hirsuticaulis!N$2:N1000&lt;&gt;"")*(Hirsuticaulis!N$2:N1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!N$2:N1000,Hirsuticaulis!N$2:N1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!N$2:N1000,Hirsuticaulis!N$2:N1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!N$2:N1000,Hirsuticaulis!N$2:N1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Hirsuticaulis!N$2:N1000,(Hirsuticaulis!N$2:N1000&lt;&gt;"")*(Hirsuticaulis!N$2:N1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!N$2:N1000,Hirsuticaulis!N$2:N1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!N$2:N1000,Hirsuticaulis!N$2:N1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!N$2:N1000,Hirsuticaulis!N$2:N1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Hirsuticaulis!N$2:N1000,Hirsuticaulis!N$2:N1000&lt;&gt;"" )) &amp; ") mm"</f>
+      <c r="C64" s="3" t="str">
+        <f>"(" &amp; IF(MIN(Hirsuticaulis!E$2:E$1000)&lt;_xlfn.QUARTILE.INC(Hirsuticaulis!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!E$2:E$1000,1)),MIN(Hirsuticaulis!E$2:E$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Hirsuticaulis!E$2:E$1000, Hirsuticaulis!E$2:E$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!E$2:E$1000,1)), Hirsuticaulis!E$2:E$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!E$2:E$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Hirsuticaulis!E$2:E$1000, Hirsuticaulis!E$2:E$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!E$2:E$1000,1)), Hirsuticaulis!E$2:E$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!E$2:E$1000,1))) &amp; " (" &amp; IF(MAX(Hirsuticaulis!E$2:E$1000)&gt;_xlfn.QUARTILE.INC(Hirsuticaulis!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!E$2:E$1000,1)),MAX(Hirsuticaulis!E$2:E$1000),"") &amp; ") mm"</f>
+        <v>() 0.609–2.76 (3.542) mm</v>
+      </c>
+      <c r="D64" s="3" t="str">
+        <f>"(" &amp; IF(MIN(Hirsuticaulis!F$2:F$1000)&lt;_xlfn.QUARTILE.INC(Hirsuticaulis!F$2:F$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!F$2:F$1000,1)),MIN(Hirsuticaulis!F$2:F$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Hirsuticaulis!F$2:F$1000, Hirsuticaulis!F$2:F$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!F$2:F$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!F$2:F$1000,1)), Hirsuticaulis!F$2:F$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!F$2:F$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!F$2:F$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Hirsuticaulis!F$2:F$1000, Hirsuticaulis!F$2:F$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!F$2:F$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!F$2:F$1000,1)), Hirsuticaulis!F$2:F$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!F$2:F$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!F$2:F$1000,1))) &amp; " (" &amp; IF(MAX(Hirsuticaulis!F$2:F$1000)&gt;_xlfn.QUARTILE.INC(Hirsuticaulis!F$2:F$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!F$2:F$1000,1)),MAX(Hirsuticaulis!F$2:F$1000),"") &amp; ") mm"</f>
+        <v>() 0.323–1.603 (1.972) mm</v>
+      </c>
+      <c r="E64" s="3" t="str">
+        <f>"(" &amp; IF(MIN(Hirsuticaulis!G$2:G$1000)&lt;_xlfn.QUARTILE.INC(Hirsuticaulis!G$2:G$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!G$2:G$1000,1)),MIN(Hirsuticaulis!G$2:G$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Hirsuticaulis!G$2:G$1000, Hirsuticaulis!G$2:G$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!G$2:G$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!G$2:G$1000,1)), Hirsuticaulis!G$2:G$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!G$2:G$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!G$2:G$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Hirsuticaulis!G$2:G$1000, Hirsuticaulis!G$2:G$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!G$2:G$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!G$2:G$1000,1)), Hirsuticaulis!G$2:G$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!G$2:G$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!G$2:G$1000,1))) &amp; " (" &amp; IF(MAX(Hirsuticaulis!G$2:G$1000)&gt;_xlfn.QUARTILE.INC(Hirsuticaulis!G$2:G$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!G$2:G$1000,1)),MAX(Hirsuticaulis!G$2:G$1000),"") &amp; ") mm"</f>
+        <v>() 0–1.575 () mm</v>
+      </c>
+      <c r="F64" s="3" t="str">
+        <f>"(" &amp; IF(MIN(Hirsuticaulis!H$2:H$1000)&lt;_xlfn.QUARTILE.INC(Hirsuticaulis!H$2:H$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!H$2:H$1000,1)),MIN(Hirsuticaulis!H$2:H$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Hirsuticaulis!H$2:H$1000, Hirsuticaulis!H$2:H$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!H$2:H$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!H$2:H$1000,1)), Hirsuticaulis!H$2:H$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!H$2:H$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!H$2:H$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Hirsuticaulis!H$2:H$1000, Hirsuticaulis!H$2:H$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!H$2:H$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!H$2:H$1000,1)), Hirsuticaulis!H$2:H$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!H$2:H$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!H$2:H$1000,1))) &amp; " (" &amp; IF(MAX(Hirsuticaulis!H$2:H$1000)&gt;_xlfn.QUARTILE.INC(Hirsuticaulis!H$2:H$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!H$2:H$1000,1)),MAX(Hirsuticaulis!H$2:H$1000),"") &amp; ") mm"</f>
+        <v>() 0.958–8.605 (9.633) mm</v>
+      </c>
+      <c r="G64" s="3" t="str">
+        <f>"(" &amp; IF(MIN(Hirsuticaulis!I$2:I$1000)&lt;_xlfn.QUARTILE.INC(Hirsuticaulis!I$2:I$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!I$2:I$1000,1)),MIN(Hirsuticaulis!I$2:I$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Hirsuticaulis!I$2:I$1000, Hirsuticaulis!I$2:I$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!I$2:I$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!I$2:I$1000,1)), Hirsuticaulis!I$2:I$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!I$2:I$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!I$2:I$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Hirsuticaulis!I$2:I$1000, Hirsuticaulis!I$2:I$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!I$2:I$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!I$2:I$1000,1)), Hirsuticaulis!I$2:I$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!I$2:I$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!I$2:I$1000,1))) &amp; " (" &amp; IF(MAX(Hirsuticaulis!I$2:I$1000)&gt;_xlfn.QUARTILE.INC(Hirsuticaulis!I$2:I$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!I$2:I$1000,1)),MAX(Hirsuticaulis!I$2:I$1000),"") &amp; ") mm"</f>
+        <v>() 0.114–3.458 (4.044) mm</v>
+      </c>
+      <c r="H64" s="3" t="str">
+        <f>"(" &amp; IF(MIN(Hirsuticaulis!J$2:J$1000)&lt;_xlfn.QUARTILE.INC(Hirsuticaulis!J$2:J$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!J$2:J$1000,1)),MIN(Hirsuticaulis!J$2:J$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Hirsuticaulis!J$2:J$1000, Hirsuticaulis!J$2:J$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!J$2:J$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!J$2:J$1000,1)), Hirsuticaulis!J$2:J$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!J$2:J$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!J$2:J$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Hirsuticaulis!J$2:J$1000, Hirsuticaulis!J$2:J$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!J$2:J$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!J$2:J$1000,1)), Hirsuticaulis!J$2:J$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!J$2:J$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!J$2:J$1000,1))) &amp; " (" &amp; IF(MAX(Hirsuticaulis!J$2:J$1000)&gt;_xlfn.QUARTILE.INC(Hirsuticaulis!J$2:J$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!J$2:J$1000,1)),MAX(Hirsuticaulis!J$2:J$1000),"") &amp; ") mm"</f>
+        <v>() 2.34–5.299 (6.612) mm</v>
+      </c>
+      <c r="I64" s="3" t="str">
+        <f>"(" &amp; IF(MIN(Hirsuticaulis!K$2:K$1000)&lt;_xlfn.QUARTILE.INC(Hirsuticaulis!K$2:K$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!K$2:K$1000,1)),MIN(Hirsuticaulis!K$2:K$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Hirsuticaulis!K$2:K$1000, Hirsuticaulis!K$2:K$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!K$2:K$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!K$2:K$1000,1)), Hirsuticaulis!K$2:K$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!K$2:K$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!K$2:K$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Hirsuticaulis!K$2:K$1000, Hirsuticaulis!K$2:K$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!K$2:K$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!K$2:K$1000,1)), Hirsuticaulis!K$2:K$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!K$2:K$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!K$2:K$1000,1))) &amp; " (" &amp; IF(MAX(Hirsuticaulis!K$2:K$1000)&gt;_xlfn.QUARTILE.INC(Hirsuticaulis!K$2:K$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!K$2:K$1000,1)),MAX(Hirsuticaulis!K$2:K$1000),"") &amp; ") mm"</f>
+        <v>() 0.695–2.194 (3.356) mm</v>
+      </c>
+      <c r="J64" s="3" t="str">
+        <f>"(" &amp; IF(MIN(Hirsuticaulis!L$2:L$1000)&lt;_xlfn.QUARTILE.INC(Hirsuticaulis!L$2:L$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!L$2:L$1000,1)),MIN(Hirsuticaulis!L$2:L$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Hirsuticaulis!L$2:L$1000, Hirsuticaulis!L$2:L$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!L$2:L$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!L$2:L$1000,1)), Hirsuticaulis!L$2:L$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!L$2:L$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!L$2:L$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Hirsuticaulis!L$2:L$1000, Hirsuticaulis!L$2:L$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!L$2:L$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!L$2:L$1000,1)), Hirsuticaulis!L$2:L$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!L$2:L$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!L$2:L$1000,1))) &amp; " (" &amp; IF(MAX(Hirsuticaulis!L$2:L$1000)&gt;_xlfn.QUARTILE.INC(Hirsuticaulis!L$2:L$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!L$2:L$1000,1)),MAX(Hirsuticaulis!L$2:L$1000),"") &amp; ") mm"</f>
+        <v>() 0.444–2.158 (2.87) mm</v>
+      </c>
+      <c r="K64" s="3" t="str">
+        <f>"(" &amp; IF(MIN(Hirsuticaulis!M$2:M$1000)&lt;_xlfn.QUARTILE.INC(Hirsuticaulis!M$2:M$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!M$2:M$1000,1)),MIN(Hirsuticaulis!M$2:M$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Hirsuticaulis!M$2:M$1000, Hirsuticaulis!M$2:M$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!M$2:M$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!M$2:M$1000,1)), Hirsuticaulis!M$2:M$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!M$2:M$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!M$2:M$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Hirsuticaulis!M$2:M$1000, Hirsuticaulis!M$2:M$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!M$2:M$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!M$2:M$1000,1)), Hirsuticaulis!M$2:M$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!M$2:M$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!M$2:M$1000,1))) &amp; " (" &amp; IF(MAX(Hirsuticaulis!M$2:M$1000)&gt;_xlfn.QUARTILE.INC(Hirsuticaulis!M$2:M$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!M$2:M$1000,1)),MAX(Hirsuticaulis!M$2:M$1000),"") &amp; ") mm"</f>
+        <v>() 1.159–3.46 (4.287) mm</v>
+      </c>
+      <c r="L64" s="3" t="str">
+        <f>"(" &amp; IF(MIN(Hirsuticaulis!N$2:N$1000)&lt;_xlfn.QUARTILE.INC(Hirsuticaulis!N$2:N$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!N$2:N$1000,1)),MIN(Hirsuticaulis!N$2:N$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Hirsuticaulis!N$2:N$1000, Hirsuticaulis!N$2:N$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!N$2:N$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!N$2:N$1000,1)), Hirsuticaulis!N$2:N$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!N$2:N$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!N$2:N$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Hirsuticaulis!N$2:N$1000, Hirsuticaulis!N$2:N$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!N$2:N$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!N$2:N$1000,1)), Hirsuticaulis!N$2:N$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!N$2:N$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!N$2:N$1000,1))) &amp; " (" &amp; IF(MAX(Hirsuticaulis!N$2:N$1000)&gt;_xlfn.QUARTILE.INC(Hirsuticaulis!N$2:N$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!N$2:N$1000,1)),MAX(Hirsuticaulis!N$2:N$1000),"") &amp; ") mm"</f>
         <v>(1.938) 2.207–5.112 (5.219) mm</v>
       </c>
-      <c r="M64" s="2" t="str" cm="1">
-        <f t="array" ref="M64">"(" &amp; MIN(_xlfn._xlws.FILTER(Hirsuticaulis!O$2:O1000,Hirsuticaulis!O$2:O1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Hirsuticaulis!O$2:O1000,(Hirsuticaulis!O$2:O1000&lt;&gt;"")*(Hirsuticaulis!O$2:O1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!O$2:O1000,Hirsuticaulis!O$2:O1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!O$2:O1000,Hirsuticaulis!O$2:O1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!O$2:O1000,Hirsuticaulis!O$2:O1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Hirsuticaulis!O$2:O1000,(Hirsuticaulis!O$2:O1000&lt;&gt;"")*(Hirsuticaulis!O$2:O1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!O$2:O1000,Hirsuticaulis!O$2:O1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!O$2:O1000,Hirsuticaulis!O$2:O1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!O$2:O1000,Hirsuticaulis!O$2:O1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Hirsuticaulis!O$2:O1000,Hirsuticaulis!O$2:O1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(1.333) 1.333–5.679 (5.679) mm</v>
-      </c>
-      <c r="N64" s="2" t="str" cm="1">
-        <f t="array" ref="N64">"(" &amp; MIN(_xlfn._xlws.FILTER(Hirsuticaulis!P$2:P1000,Hirsuticaulis!P$2:P1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Hirsuticaulis!P$2:P1000,(Hirsuticaulis!P$2:P1000&lt;&gt;"")*(Hirsuticaulis!P$2:P1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!P$2:P1000,Hirsuticaulis!P$2:P1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!P$2:P1000,Hirsuticaulis!P$2:P1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!P$2:P1000,Hirsuticaulis!P$2:P1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Hirsuticaulis!P$2:P1000,(Hirsuticaulis!P$2:P1000&lt;&gt;"")*(Hirsuticaulis!P$2:P1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!P$2:P1000,Hirsuticaulis!P$2:P1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!P$2:P1000,Hirsuticaulis!P$2:P1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!P$2:P1000,Hirsuticaulis!P$2:P1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Hirsuticaulis!P$2:P1000,Hirsuticaulis!P$2:P1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(0.889) 0.889–6.674 (12.105) mm</v>
-      </c>
-      <c r="O64" s="2" t="str" cm="1">
-        <f t="array" ref="O64">"(" &amp; MIN(_xlfn._xlws.FILTER(Hirsuticaulis!Q$2:Q1000,Hirsuticaulis!Q$2:Q1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Hirsuticaulis!Q$2:Q1000,(Hirsuticaulis!Q$2:Q1000&lt;&gt;"")*(Hirsuticaulis!Q$2:Q1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!Q$2:Q1000,Hirsuticaulis!Q$2:Q1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!Q$2:Q1000,Hirsuticaulis!Q$2:Q1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!Q$2:Q1000,Hirsuticaulis!Q$2:Q1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Hirsuticaulis!Q$2:Q1000,(Hirsuticaulis!Q$2:Q1000&lt;&gt;"")*(Hirsuticaulis!Q$2:Q1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!Q$2:Q1000,Hirsuticaulis!Q$2:Q1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!Q$2:Q1000,Hirsuticaulis!Q$2:Q1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!Q$2:Q1000,Hirsuticaulis!Q$2:Q1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Hirsuticaulis!Q$2:Q1000,Hirsuticaulis!Q$2:Q1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(1.155) 1.155–41.173 (49.824) mm</v>
-      </c>
-      <c r="P64" s="2" t="str" cm="1">
-        <f t="array" ref="P64">"(" &amp; MIN(_xlfn._xlws.FILTER(Hirsuticaulis!R$2:R1000,Hirsuticaulis!R$2:R1000&lt;&gt;"")) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Hirsuticaulis!R$2:R1000,(Hirsuticaulis!R$2:R1000&lt;&gt;"")*(Hirsuticaulis!R$2:R1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!R$2:R1000,Hirsuticaulis!R$2:R1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!R$2:R1000,Hirsuticaulis!R$2:R1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!R$2:R1000,Hirsuticaulis!R$2:R1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Hirsuticaulis!R$2:R1000,(Hirsuticaulis!R$2:R1000&lt;&gt;"")*(Hirsuticaulis!R$2:R1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!R$2:R1000,Hirsuticaulis!R$2:R1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!R$2:R1000,Hirsuticaulis!R$2:R1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hirsuticaulis!R$2:R1000,Hirsuticaulis!R$2:R1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Hirsuticaulis!R$2:R1000,Hirsuticaulis!R$2:R1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(173.565) 173.565–1052.388 (1052.388) mm</v>
+      <c r="M64" s="3" t="str">
+        <f>"(" &amp; IF(MIN(Hirsuticaulis!O$2:O$1000)&lt;_xlfn.QUARTILE.INC(Hirsuticaulis!O$2:O$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!O$2:O$1000,1)),MIN(Hirsuticaulis!O$2:O$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Hirsuticaulis!O$2:O$1000, Hirsuticaulis!O$2:O$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!O$2:O$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!O$2:O$1000,1)), Hirsuticaulis!O$2:O$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!O$2:O$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!O$2:O$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Hirsuticaulis!O$2:O$1000, Hirsuticaulis!O$2:O$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!O$2:O$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!O$2:O$1000,1)), Hirsuticaulis!O$2:O$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!O$2:O$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!O$2:O$1000,1))) &amp; " (" &amp; IF(MAX(Hirsuticaulis!O$2:O$1000)&gt;_xlfn.QUARTILE.INC(Hirsuticaulis!O$2:O$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!O$2:O$1000,1)),MAX(Hirsuticaulis!O$2:O$1000),"") &amp; ") mm"</f>
+        <v>() 1.333–5.679 () mm</v>
+      </c>
+      <c r="N64" s="3" t="str">
+        <f>"(" &amp; IF(MIN(Hirsuticaulis!P$2:P$1000)&lt;_xlfn.QUARTILE.INC(Hirsuticaulis!P$2:P$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!P$2:P$1000,1)),MIN(Hirsuticaulis!P$2:P$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Hirsuticaulis!P$2:P$1000, Hirsuticaulis!P$2:P$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!P$2:P$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!P$2:P$1000,1)), Hirsuticaulis!P$2:P$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!P$2:P$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!P$2:P$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Hirsuticaulis!P$2:P$1000, Hirsuticaulis!P$2:P$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!P$2:P$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!P$2:P$1000,1)), Hirsuticaulis!P$2:P$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!P$2:P$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!P$2:P$1000,1))) &amp; " (" &amp; IF(MAX(Hirsuticaulis!P$2:P$1000)&gt;_xlfn.QUARTILE.INC(Hirsuticaulis!P$2:P$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!P$2:P$1000,1)),MAX(Hirsuticaulis!P$2:P$1000),"") &amp; ") mm"</f>
+        <v>() 0.889–6.674 (12.105) mm</v>
+      </c>
+      <c r="O64" s="3" t="str">
+        <f>"(" &amp; IF(MIN(Hirsuticaulis!Q$2:Q$1000)&lt;_xlfn.QUARTILE.INC(Hirsuticaulis!Q$2:Q$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!Q$2:Q$1000,1)),MIN(Hirsuticaulis!Q$2:Q$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Hirsuticaulis!Q$2:Q$1000, Hirsuticaulis!Q$2:Q$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!Q$2:Q$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!Q$2:Q$1000,1)), Hirsuticaulis!Q$2:Q$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!Q$2:Q$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!Q$2:Q$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Hirsuticaulis!Q$2:Q$1000, Hirsuticaulis!Q$2:Q$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!Q$2:Q$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!Q$2:Q$1000,1)), Hirsuticaulis!Q$2:Q$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!Q$2:Q$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!Q$2:Q$1000,1))) &amp; " (" &amp; IF(MAX(Hirsuticaulis!Q$2:Q$1000)&gt;_xlfn.QUARTILE.INC(Hirsuticaulis!Q$2:Q$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!Q$2:Q$1000,1)),MAX(Hirsuticaulis!Q$2:Q$1000),"") &amp; ") mm"</f>
+        <v>() 1.155–41.173 (49.824) mm</v>
+      </c>
+      <c r="P64" s="3" t="str">
+        <f>"(" &amp; IF(MIN(Hirsuticaulis!R$2:R$1000)&lt;_xlfn.QUARTILE.INC(Hirsuticaulis!R$2:R$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!R$2:R$1000,1)),MIN(Hirsuticaulis!R$2:R$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Hirsuticaulis!R$2:R$1000, Hirsuticaulis!R$2:R$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!R$2:R$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!R$2:R$1000,1)), Hirsuticaulis!R$2:R$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!R$2:R$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!R$2:R$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Hirsuticaulis!R$2:R$1000, Hirsuticaulis!R$2:R$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!R$2:R$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!R$2:R$1000,1)), Hirsuticaulis!R$2:R$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!R$2:R$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!R$2:R$1000,1))) &amp; " (" &amp; IF(MAX(Hirsuticaulis!R$2:R$1000)&gt;_xlfn.QUARTILE.INC(Hirsuticaulis!R$2:R$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!R$2:R$1000,1)),MAX(Hirsuticaulis!R$2:R$1000),"") &amp; ") mm"</f>
+        <v>() 173.565–1052.388 () mm</v>
       </c>
     </row>
     <row r="65" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -6186,61 +6208,138 @@
       <c r="B73" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C73" s="2" t="str" cm="1">
-        <f t="array" ref="C73">"(" &amp; MIN(_xlfn._xlws.FILTER(Hispida!E$2:E1000,Hispida!E$2:E1000&lt;&gt;"" )) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Hispida!E$2:E1000,(Hispida!E$2:E1000&lt;&gt;"" )*(Hispida!E$2:E1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!E$2:E1000,Hispida!E$2:E1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!E$2:E1000,Hispida!E$2:E1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!E$2:E1000,Hispida!E$2:E1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Hispida!E$2:E1000,(Hispida!E$2:E1000&lt;&gt;"" )*(Hispida!E$2:E1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!E$2:E1000,Hispida!E$2:E1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!E$2:E1000,Hispida!E$2:E1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!E$2:E1000,Hispida!E$2:E1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Hispida!E$2:E1000,Hispida!E$2:E1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(0) 0–0 (0) mm</v>
-      </c>
-      <c r="D73" s="2" t="str" cm="1">
-        <f t="array" ref="D73">"(" &amp; MIN(_xlfn._xlws.FILTER(Hispida!F$2:F1000,Hispida!F$2:F1000&lt;&gt;"" )) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Hispida!F$2:F1000,(Hispida!F$2:F1000&lt;&gt;"" )*(Hispida!F$2:F1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!F$2:F1000,Hispida!F$2:F1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!F$2:F1000,Hispida!F$2:F1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!F$2:F1000,Hispida!F$2:F1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Hispida!F$2:F1000,(Hispida!F$2:F1000&lt;&gt;"" )*(Hispida!F$2:F1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!F$2:F1000,Hispida!F$2:F1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!F$2:F1000,Hispida!F$2:F1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!F$2:F1000,Hispida!F$2:F1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Hispida!F$2:F1000,Hispida!F$2:F1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(0) 0–0 (0) mm</v>
-      </c>
-      <c r="E73" s="2" t="str" cm="1">
-        <f t="array" ref="E73">"(" &amp; MIN(_xlfn._xlws.FILTER(Hispida!G$2:G1000,Hispida!G$2:G1000&lt;&gt;"" )) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Hispida!G$2:G1000,(Hispida!G$2:G1000&lt;&gt;"" )*(Hispida!G$2:G1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!G$2:G1000,Hispida!G$2:G1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!G$2:G1000,Hispida!G$2:G1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!G$2:G1000,Hispida!G$2:G1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Hispida!G$2:G1000,(Hispida!G$2:G1000&lt;&gt;"" )*(Hispida!G$2:G1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!G$2:G1000,Hispida!G$2:G1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!G$2:G1000,Hispida!G$2:G1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!G$2:G1000,Hispida!G$2:G1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Hispida!G$2:G1000,Hispida!G$2:G1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(0) 0–0 (0) mm</v>
-      </c>
-      <c r="F73" s="2" t="str" cm="1">
-        <f t="array" ref="F73">"(" &amp; MIN(_xlfn._xlws.FILTER(Hispida!H$2:H1000,Hispida!H$2:H1000&lt;&gt;"" )) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Hispida!H$2:H1000,(Hispida!H$2:H1000&lt;&gt;"" )*(Hispida!H$2:H1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!H$2:H1000,Hispida!H$2:H1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!H$2:H1000,Hispida!H$2:H1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!H$2:H1000,Hispida!H$2:H1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Hispida!H$2:H1000,(Hispida!H$2:H1000&lt;&gt;"" )*(Hispida!H$2:H1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!H$2:H1000,Hispida!H$2:H1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!H$2:H1000,Hispida!H$2:H1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!H$2:H1000,Hispida!H$2:H1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Hispida!H$2:H1000,Hispida!H$2:H1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(2.002) 2.002–10.963 (10.963) mm</v>
-      </c>
-      <c r="G73" s="2" t="str" cm="1">
-        <f t="array" ref="G73">"(" &amp; MIN(_xlfn._xlws.FILTER(Hispida!I$2:I1000,Hispida!I$2:I1000&lt;&gt;"" )) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Hispida!I$2:I1000,(Hispida!I$2:I1000&lt;&gt;"" )*(Hispida!I$2:I1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!I$2:I1000,Hispida!I$2:I1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!I$2:I1000,Hispida!I$2:I1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!I$2:I1000,Hispida!I$2:I1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Hispida!I$2:I1000,(Hispida!I$2:I1000&lt;&gt;"" )*(Hispida!I$2:I1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!I$2:I1000,Hispida!I$2:I1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!I$2:I1000,Hispida!I$2:I1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!I$2:I1000,Hispida!I$2:I1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Hispida!I$2:I1000,Hispida!I$2:I1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(0.93) 0.93–3.568 (5.41) mm</v>
-      </c>
-      <c r="H73" s="2" t="str" cm="1">
-        <f t="array" ref="H73">"(" &amp; MIN(_xlfn._xlws.FILTER(Hispida!J$2:J1000,Hispida!J$2:J1000&lt;&gt;"" )) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Hispida!J$2:J1000,(Hispida!J$2:J1000&lt;&gt;"" )*(Hispida!J$2:J1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!J$2:J1000,Hispida!J$2:J1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!J$2:J1000,Hispida!J$2:J1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!J$2:J1000,Hispida!J$2:J1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Hispida!J$2:J1000,(Hispida!J$2:J1000&lt;&gt;"" )*(Hispida!J$2:J1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!J$2:J1000,Hispida!J$2:J1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!J$2:J1000,Hispida!J$2:J1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!J$2:J1000,Hispida!J$2:J1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Hispida!J$2:J1000,Hispida!J$2:J1000&lt;&gt;"" )) &amp; ") mm"</f>
+      <c r="C73" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Hispida!E$2:E$1000)&lt;_xlfn.QUARTILE.INC(Hispida!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Hispida!E$2:E$1000,1)),MIN(Hispida!E$2:E$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Hispida!E$2:E$1000, Hispida!E$2:E$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hispida!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Hispida!E$2:E$1000,1)), Hispida!E$2:E$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hispida!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Hispida!E$2:E$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Hispida!E$2:E$1000, Hispida!E$2:E$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hispida!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Hispida!E$2:E$1000,1)), Hispida!E$2:E$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hispida!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Hispida!E$2:E$1000,1))) &amp; " (" &amp; IF(MAX(Hispida!E$2:E$1000)&gt;_xlfn.QUARTILE.INC(Hispida!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Hispida!E$2:E$1000,1)),MAX(Hispida!E$2:E$1000),"") &amp; ") mm"</f>
+        <v>() 0–0 () mm</v>
+      </c>
+      <c r="D73" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Hispida!F$2:F$1000)&lt;_xlfn.QUARTILE.INC(Hispida!F$2:F$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Hispida!F$2:F$1000,1)),MIN(Hispida!F$2:F$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Hispida!F$2:F$1000, Hispida!F$2:F$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hispida!F$2:F$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Hispida!F$2:F$1000,1)), Hispida!F$2:F$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hispida!F$2:F$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Hispida!F$2:F$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Hispida!F$2:F$1000, Hispida!F$2:F$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hispida!F$2:F$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Hispida!F$2:F$1000,1)), Hispida!F$2:F$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hispida!F$2:F$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Hispida!F$2:F$1000,1))) &amp; " (" &amp; IF(MAX(Hispida!F$2:F$1000)&gt;_xlfn.QUARTILE.INC(Hispida!F$2:F$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!F$2:F$1000,3)-_xlfn.QUARTILE.INC(Hispida!F$2:F$1000,1)),MAX(Hispida!F$2:F$1000),"") &amp; ") mm"</f>
+        <v>() 0–0 () mm</v>
+      </c>
+      <c r="E73" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Hispida!G$2:G$1000)&lt;_xlfn.QUARTILE.INC(Hispida!G$2:G$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Hispida!G$2:G$1000,1)),MIN(Hispida!G$2:G$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Hispida!G$2:G$1000, Hispida!G$2:G$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hispida!G$2:G$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Hispida!G$2:G$1000,1)), Hispida!G$2:G$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hispida!G$2:G$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Hispida!G$2:G$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Hispida!G$2:G$1000, Hispida!G$2:G$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hispida!G$2:G$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Hispida!G$2:G$1000,1)), Hispida!G$2:G$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hispida!G$2:G$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Hispida!G$2:G$1000,1))) &amp; " (" &amp; IF(MAX(Hispida!G$2:G$1000)&gt;_xlfn.QUARTILE.INC(Hispida!G$2:G$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!G$2:G$1000,3)-_xlfn.QUARTILE.INC(Hispida!G$2:G$1000,1)),MAX(Hispida!G$2:G$1000),"") &amp; ") mm"</f>
+        <v>() 0–0 () mm</v>
+      </c>
+      <c r="F73" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Hispida!H$2:H$1000)&lt;_xlfn.QUARTILE.INC(Hispida!H$2:H$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Hispida!H$2:H$1000,1)),MIN(Hispida!H$2:H$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Hispida!H$2:H$1000, Hispida!H$2:H$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hispida!H$2:H$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Hispida!H$2:H$1000,1)), Hispida!H$2:H$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hispida!H$2:H$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Hispida!H$2:H$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Hispida!H$2:H$1000, Hispida!H$2:H$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hispida!H$2:H$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Hispida!H$2:H$1000,1)), Hispida!H$2:H$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hispida!H$2:H$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Hispida!H$2:H$1000,1))) &amp; " (" &amp; IF(MAX(Hispida!H$2:H$1000)&gt;_xlfn.QUARTILE.INC(Hispida!H$2:H$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!H$2:H$1000,3)-_xlfn.QUARTILE.INC(Hispida!H$2:H$1000,1)),MAX(Hispida!H$2:H$1000),"") &amp; ") mm"</f>
+        <v>() 2.002–10.963 () mm</v>
+      </c>
+      <c r="G73" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Hispida!I$2:I$1000)&lt;_xlfn.QUARTILE.INC(Hispida!I$2:I$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Hispida!I$2:I$1000,1)),MIN(Hispida!I$2:I$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Hispida!I$2:I$1000, Hispida!I$2:I$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hispida!I$2:I$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Hispida!I$2:I$1000,1)), Hispida!I$2:I$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hispida!I$2:I$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Hispida!I$2:I$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Hispida!I$2:I$1000, Hispida!I$2:I$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hispida!I$2:I$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Hispida!I$2:I$1000,1)), Hispida!I$2:I$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hispida!I$2:I$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Hispida!I$2:I$1000,1))) &amp; " (" &amp; IF(MAX(Hispida!I$2:I$1000)&gt;_xlfn.QUARTILE.INC(Hispida!I$2:I$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!I$2:I$1000,3)-_xlfn.QUARTILE.INC(Hispida!I$2:I$1000,1)),MAX(Hispida!I$2:I$1000),"") &amp; ") mm"</f>
+        <v>() 0.93–3.568 (5.41) mm</v>
+      </c>
+      <c r="H73" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Hispida!J$2:J$1000)&lt;_xlfn.QUARTILE.INC(Hispida!J$2:J$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Hispida!J$2:J$1000,1)),MIN(Hispida!J$2:J$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Hispida!J$2:J$1000, Hispida!J$2:J$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hispida!J$2:J$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Hispida!J$2:J$1000,1)), Hispida!J$2:J$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hispida!J$2:J$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Hispida!J$2:J$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Hispida!J$2:J$1000, Hispida!J$2:J$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hispida!J$2:J$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Hispida!J$2:J$1000,1)), Hispida!J$2:J$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hispida!J$2:J$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Hispida!J$2:J$1000,1))) &amp; " (" &amp; IF(MAX(Hispida!J$2:J$1000)&gt;_xlfn.QUARTILE.INC(Hispida!J$2:J$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!J$2:J$1000,3)-_xlfn.QUARTILE.INC(Hispida!J$2:J$1000,1)),MAX(Hispida!J$2:J$1000),"") &amp; ") mm"</f>
         <v>(3.182) 3.875–6.041 (7.08) mm</v>
       </c>
-      <c r="I73" s="2" t="str" cm="1">
-        <f t="array" ref="I73">"(" &amp; MIN(_xlfn._xlws.FILTER(Hispida!K$2:K1000,Hispida!K$2:K1000&lt;&gt;"" )) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Hispida!K$2:K1000,(Hispida!K$2:K1000&lt;&gt;"" )*(Hispida!K$2:K1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!K$2:K1000,Hispida!K$2:K1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!K$2:K1000,Hispida!K$2:K1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!K$2:K1000,Hispida!K$2:K1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Hispida!K$2:K1000,(Hispida!K$2:K1000&lt;&gt;"" )*(Hispida!K$2:K1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!K$2:K1000,Hispida!K$2:K1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!K$2:K1000,Hispida!K$2:K1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!K$2:K1000,Hispida!K$2:K1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Hispida!K$2:K1000,Hispida!K$2:K1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(0.792) 0.792–2.593 (2.846) mm</v>
-      </c>
-      <c r="J73" s="2" t="str" cm="1">
-        <f t="array" ref="J73">"(" &amp; MIN(_xlfn._xlws.FILTER(Hispida!L$2:L1000,Hispida!L$2:L1000&lt;&gt;"" )) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Hispida!L$2:L1000,(Hispida!L$2:L1000&lt;&gt;"" )*(Hispida!L$2:L1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!L$2:L1000,Hispida!L$2:L1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!L$2:L1000,Hispida!L$2:L1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!L$2:L1000,Hispida!L$2:L1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Hispida!L$2:L1000,(Hispida!L$2:L1000&lt;&gt;"" )*(Hispida!L$2:L1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!L$2:L1000,Hispida!L$2:L1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!L$2:L1000,Hispida!L$2:L1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!L$2:L1000,Hispida!L$2:L1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Hispida!L$2:L1000,Hispida!L$2:L1000&lt;&gt;"" )) &amp; ") mm"</f>
+      <c r="I73" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Hispida!K$2:K$1000)&lt;_xlfn.QUARTILE.INC(Hispida!K$2:K$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Hispida!K$2:K$1000,1)),MIN(Hispida!K$2:K$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Hispida!K$2:K$1000, Hispida!K$2:K$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hispida!K$2:K$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Hispida!K$2:K$1000,1)), Hispida!K$2:K$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hispida!K$2:K$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Hispida!K$2:K$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Hispida!K$2:K$1000, Hispida!K$2:K$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hispida!K$2:K$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Hispida!K$2:K$1000,1)), Hispida!K$2:K$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hispida!K$2:K$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Hispida!K$2:K$1000,1))) &amp; " (" &amp; IF(MAX(Hispida!K$2:K$1000)&gt;_xlfn.QUARTILE.INC(Hispida!K$2:K$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!K$2:K$1000,3)-_xlfn.QUARTILE.INC(Hispida!K$2:K$1000,1)),MAX(Hispida!K$2:K$1000),"") &amp; ") mm"</f>
+        <v>() 0.792–2.593 (2.846) mm</v>
+      </c>
+      <c r="J73" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Hispida!L$2:L$1000)&lt;_xlfn.QUARTILE.INC(Hispida!L$2:L$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Hispida!L$2:L$1000,1)),MIN(Hispida!L$2:L$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Hispida!L$2:L$1000, Hispida!L$2:L$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hispida!L$2:L$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Hispida!L$2:L$1000,1)), Hispida!L$2:L$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hispida!L$2:L$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Hispida!L$2:L$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Hispida!L$2:L$1000, Hispida!L$2:L$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hispida!L$2:L$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Hispida!L$2:L$1000,1)), Hispida!L$2:L$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hispida!L$2:L$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Hispida!L$2:L$1000,1))) &amp; " (" &amp; IF(MAX(Hispida!L$2:L$1000)&gt;_xlfn.QUARTILE.INC(Hispida!L$2:L$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!L$2:L$1000,3)-_xlfn.QUARTILE.INC(Hispida!L$2:L$1000,1)),MAX(Hispida!L$2:L$1000),"") &amp; ") mm"</f>
         <v>(0.364) 0.71–1.547 (2.346) mm</v>
       </c>
-      <c r="K73" s="2" t="str" cm="1">
-        <f t="array" ref="K73">"(" &amp; MIN(_xlfn._xlws.FILTER(Hispida!M$2:M1000,Hispida!M$2:M1000&lt;&gt;"" )) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Hispida!M$2:M1000,(Hispida!M$2:M1000&lt;&gt;"" )*(Hispida!M$2:M1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!M$2:M1000,Hispida!M$2:M1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!M$2:M1000,Hispida!M$2:M1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!M$2:M1000,Hispida!M$2:M1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Hispida!M$2:M1000,(Hispida!M$2:M1000&lt;&gt;"" )*(Hispida!M$2:M1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!M$2:M1000,Hispida!M$2:M1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!M$2:M1000,Hispida!M$2:M1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!M$2:M1000,Hispida!M$2:M1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Hispida!M$2:M1000,Hispida!M$2:M1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(2.091) 2.091–3.511 (4.262) mm</v>
-      </c>
-      <c r="L73" s="2" t="str" cm="1">
-        <f t="array" ref="L73">"(" &amp; MIN(_xlfn._xlws.FILTER(Hispida!N$2:N1000,Hispida!N$2:N1000&lt;&gt;"" )) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Hispida!N$2:N1000,(Hispida!N$2:N1000&lt;&gt;"" )*(Hispida!N$2:N1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!N$2:N1000,Hispida!N$2:N1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!N$2:N1000,Hispida!N$2:N1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!N$2:N1000,Hispida!N$2:N1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Hispida!N$2:N1000,(Hispida!N$2:N1000&lt;&gt;"" )*(Hispida!N$2:N1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!N$2:N1000,Hispida!N$2:N1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!N$2:N1000,Hispida!N$2:N1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!N$2:N1000,Hispida!N$2:N1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Hispida!N$2:N1000,Hispida!N$2:N1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(1.939) 1.939–5.275 (5.275) mm</v>
-      </c>
-      <c r="M73" s="2" t="str" cm="1">
-        <f t="array" ref="M73">"(" &amp; MIN(_xlfn._xlws.FILTER(Hispida!O$2:O1000,Hispida!O$2:O1000&lt;&gt;"" )) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Hispida!O$2:O1000,(Hispida!O$2:O1000&lt;&gt;"" )*(Hispida!O$2:O1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!O$2:O1000,Hispida!O$2:O1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!O$2:O1000,Hispida!O$2:O1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!O$2:O1000,Hispida!O$2:O1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Hispida!O$2:O1000,(Hispida!O$2:O1000&lt;&gt;"" )*(Hispida!O$2:O1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!O$2:O1000,Hispida!O$2:O1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!O$2:O1000,Hispida!O$2:O1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!O$2:O1000,Hispida!O$2:O1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Hispida!O$2:O1000,Hispida!O$2:O1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(1.601) 1.601–5.368 (5.368) mm</v>
-      </c>
-      <c r="N73" s="2" t="str" cm="1">
-        <f t="array" ref="N73">"(" &amp; MIN(_xlfn._xlws.FILTER(Hispida!P$2:P1000,Hispida!P$2:P1000&lt;&gt;"" )) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Hispida!P$2:P1000,(Hispida!P$2:P1000&lt;&gt;"" )*(Hispida!P$2:P1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!P$2:P1000,Hispida!P$2:P1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!P$2:P1000,Hispida!P$2:P1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!P$2:P1000,Hispida!P$2:P1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Hispida!P$2:P1000,(Hispida!P$2:P1000&lt;&gt;"" )*(Hispida!P$2:P1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!P$2:P1000,Hispida!P$2:P1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!P$2:P1000,Hispida!P$2:P1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!P$2:P1000,Hispida!P$2:P1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Hispida!P$2:P1000,Hispida!P$2:P1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(1.193) 1.193–5.5 (5.5) mm</v>
-      </c>
-      <c r="O73" s="2" t="str" cm="1">
-        <f t="array" ref="O73">"(" &amp; MIN(_xlfn._xlws.FILTER(Hispida!Q$2:Q1000,Hispida!Q$2:Q1000&lt;&gt;"" )) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Hispida!Q$2:Q1000,(Hispida!Q$2:Q1000&lt;&gt;"" )*(Hispida!Q$2:Q1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!Q$2:Q1000,Hispida!Q$2:Q1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!Q$2:Q1000,Hispida!Q$2:Q1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!Q$2:Q1000,Hispida!Q$2:Q1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Hispida!Q$2:Q1000,(Hispida!Q$2:Q1000&lt;&gt;"" )*(Hispida!Q$2:Q1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!Q$2:Q1000,Hispida!Q$2:Q1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!Q$2:Q1000,Hispida!Q$2:Q1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!Q$2:Q1000,Hispida!Q$2:Q1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Hispida!Q$2:Q1000,Hispida!Q$2:Q1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(5.314) 5.314–36.57 (36.57) mm</v>
-      </c>
-      <c r="P73" s="2" t="str" cm="1">
-        <f t="array" ref="P73">"(" &amp; MIN(_xlfn._xlws.FILTER(Hispida!R$2:R1000,Hispida!R$2:R1000&lt;&gt;"" )) &amp; ") " &amp; MIN(_xlfn._xlws.FILTER(Hispida!R$2:R1000,(Hispida!R$2:R1000&lt;&gt;"" )*(Hispida!R$2:R1000&gt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!R$2:R1000,Hispida!R$2:R1000&lt;&gt;""),1)-1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!R$2:R1000,Hispida!R$2:R1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!R$2:R1000,Hispida!R$2:R1000&lt;&gt;""),1))))) &amp; "–" &amp; MAX(_xlfn._xlws.FILTER(Hispida!R$2:R1000,(Hispida!R$2:R1000&lt;&gt;"" )*(Hispida!R$2:R1000&lt;=_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!R$2:R1000,Hispida!R$2:R1000&lt;&gt;""),3)+1.5*(_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!R$2:R1000,Hispida!R$2:R1000&lt;&gt;""),3)-_xlfn.QUARTILE.INC(_xlfn._xlws.FILTER(Hispida!R$2:R1000,Hispida!R$2:R1000&lt;&gt;""),1))))) &amp; " (" &amp; MAX(_xlfn._xlws.FILTER(Hispida!R$2:R1000,Hispida!R$2:R1000&lt;&gt;"" )) &amp; ") mm"</f>
-        <v>(403.991) 466.159–976.656 (976.656) mm</v>
+      <c r="K73" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Hispida!M$2:M$1000)&lt;_xlfn.QUARTILE.INC(Hispida!M$2:M$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Hispida!M$2:M$1000,1)),MIN(Hispida!M$2:M$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Hispida!M$2:M$1000, Hispida!M$2:M$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hispida!M$2:M$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Hispida!M$2:M$1000,1)), Hispida!M$2:M$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hispida!M$2:M$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Hispida!M$2:M$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Hispida!M$2:M$1000, Hispida!M$2:M$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hispida!M$2:M$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Hispida!M$2:M$1000,1)), Hispida!M$2:M$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hispida!M$2:M$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Hispida!M$2:M$1000,1))) &amp; " (" &amp; IF(MAX(Hispida!M$2:M$1000)&gt;_xlfn.QUARTILE.INC(Hispida!M$2:M$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!M$2:M$1000,3)-_xlfn.QUARTILE.INC(Hispida!M$2:M$1000,1)),MAX(Hispida!M$2:M$1000),"") &amp; ") mm"</f>
+        <v>() 2.091–3.511 (4.262) mm</v>
+      </c>
+      <c r="L73" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Hispida!N$2:N$1000)&lt;_xlfn.QUARTILE.INC(Hispida!N$2:N$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Hispida!N$2:N$1000,1)),MIN(Hispida!N$2:N$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Hispida!N$2:N$1000, Hispida!N$2:N$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hispida!N$2:N$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Hispida!N$2:N$1000,1)), Hispida!N$2:N$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hispida!N$2:N$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Hispida!N$2:N$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Hispida!N$2:N$1000, Hispida!N$2:N$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hispida!N$2:N$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Hispida!N$2:N$1000,1)), Hispida!N$2:N$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hispida!N$2:N$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Hispida!N$2:N$1000,1))) &amp; " (" &amp; IF(MAX(Hispida!N$2:N$1000)&gt;_xlfn.QUARTILE.INC(Hispida!N$2:N$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!N$2:N$1000,3)-_xlfn.QUARTILE.INC(Hispida!N$2:N$1000,1)),MAX(Hispida!N$2:N$1000),"") &amp; ") mm"</f>
+        <v>() 1.939–5.275 () mm</v>
+      </c>
+      <c r="M73" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Hispida!O$2:O$1000)&lt;_xlfn.QUARTILE.INC(Hispida!O$2:O$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Hispida!O$2:O$1000,1)),MIN(Hispida!O$2:O$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Hispida!O$2:O$1000, Hispida!O$2:O$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hispida!O$2:O$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Hispida!O$2:O$1000,1)), Hispida!O$2:O$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hispida!O$2:O$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Hispida!O$2:O$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Hispida!O$2:O$1000, Hispida!O$2:O$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hispida!O$2:O$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Hispida!O$2:O$1000,1)), Hispida!O$2:O$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hispida!O$2:O$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Hispida!O$2:O$1000,1))) &amp; " (" &amp; IF(MAX(Hispida!O$2:O$1000)&gt;_xlfn.QUARTILE.INC(Hispida!O$2:O$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!O$2:O$1000,3)-_xlfn.QUARTILE.INC(Hispida!O$2:O$1000,1)),MAX(Hispida!O$2:O$1000),"") &amp; ") mm"</f>
+        <v>() 1.601–5.368 () mm</v>
+      </c>
+      <c r="N73" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Hispida!P$2:P$1000)&lt;_xlfn.QUARTILE.INC(Hispida!P$2:P$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Hispida!P$2:P$1000,1)),MIN(Hispida!P$2:P$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Hispida!P$2:P$1000, Hispida!P$2:P$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hispida!P$2:P$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Hispida!P$2:P$1000,1)), Hispida!P$2:P$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hispida!P$2:P$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Hispida!P$2:P$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Hispida!P$2:P$1000, Hispida!P$2:P$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hispida!P$2:P$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Hispida!P$2:P$1000,1)), Hispida!P$2:P$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hispida!P$2:P$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Hispida!P$2:P$1000,1))) &amp; " (" &amp; IF(MAX(Hispida!P$2:P$1000)&gt;_xlfn.QUARTILE.INC(Hispida!P$2:P$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!P$2:P$1000,3)-_xlfn.QUARTILE.INC(Hispida!P$2:P$1000,1)),MAX(Hispida!P$2:P$1000),"") &amp; ") mm"</f>
+        <v>() 1.193–5.5 () mm</v>
+      </c>
+      <c r="O73" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Hispida!Q$2:Q$1000)&lt;_xlfn.QUARTILE.INC(Hispida!Q$2:Q$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Hispida!Q$2:Q$1000,1)),MIN(Hispida!Q$2:Q$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Hispida!Q$2:Q$1000, Hispida!Q$2:Q$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hispida!Q$2:Q$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Hispida!Q$2:Q$1000,1)), Hispida!Q$2:Q$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hispida!Q$2:Q$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Hispida!Q$2:Q$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Hispida!Q$2:Q$1000, Hispida!Q$2:Q$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hispida!Q$2:Q$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Hispida!Q$2:Q$1000,1)), Hispida!Q$2:Q$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hispida!Q$2:Q$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Hispida!Q$2:Q$1000,1))) &amp; " (" &amp; IF(MAX(Hispida!Q$2:Q$1000)&gt;_xlfn.QUARTILE.INC(Hispida!Q$2:Q$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!Q$2:Q$1000,3)-_xlfn.QUARTILE.INC(Hispida!Q$2:Q$1000,1)),MAX(Hispida!Q$2:Q$1000),"") &amp; ") mm"</f>
+        <v>() 5.314–36.57 () mm</v>
+      </c>
+      <c r="P73" s="2" t="str">
+        <f>"(" &amp; IF(MIN(Hispida!R$2:R$1000)&lt;_xlfn.QUARTILE.INC(Hispida!R$2:R$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Hispida!R$2:R$1000,1)),MIN(Hispida!R$2:R$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Hispida!R$2:R$1000, Hispida!R$2:R$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hispida!R$2:R$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Hispida!R$2:R$1000,1)), Hispida!R$2:R$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hispida!R$2:R$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Hispida!R$2:R$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Hispida!R$2:R$1000, Hispida!R$2:R$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hispida!R$2:R$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Hispida!R$2:R$1000,1)), Hispida!R$2:R$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hispida!R$2:R$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Hispida!R$2:R$1000,1))) &amp; " (" &amp; IF(MAX(Hispida!R$2:R$1000)&gt;_xlfn.QUARTILE.INC(Hispida!R$2:R$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!R$2:R$1000,3)-_xlfn.QUARTILE.INC(Hispida!R$2:R$1000,1)),MAX(Hispida!R$2:R$1000),"") &amp; ") mm"</f>
+        <v>(403.991) 466.159–976.656 () mm</v>
+      </c>
+    </row>
+    <row r="83" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I83" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="84" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I84" t="str">
+        <f>"(" &amp; IF(MIN(Americana!E$2:E$1000)&lt;_xlfn.QUARTILE.INC(Americana!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Americana!E$2:E$1000,1)),MIN(Americana!E$2:E$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Americana!E$2:E$1000, Americana!E$2:E$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Americana!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Americana!E$2:E$1000,1)), Americana!E$2:E$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Americana!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Americana!E$2:E$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Americana!E$2:E$1000, Americana!E$2:E$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Americana!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Americana!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Americana!E$2:E$1000,1)), Americana!E$2:E$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Americana!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Americana!E$2:E$1000,1))) &amp; " (" &amp; IF(MAX(Americana!E$2:E$1000)&gt;_xlfn.QUARTILE.INC(Americana!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Americana!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Americana!E$2:E$1000,1)),MAX(Americana!E$2:E$1000),"") &amp; ") mm"</f>
+        <v>() 0–0 (2.874) mm</v>
+      </c>
+    </row>
+    <row r="86" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I86" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="87" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I87" t="str">
+        <f>"(" &amp; IF(MIN(Calycosa!E$2:E$1000)&lt;_xlfn.QUARTILE.INC(Calycosa!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Calycosa!E$2:E$1000,1)),MIN(Calycosa!E$2:E$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Calycosa!E$2:E$1000, Calycosa!E$2:E$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Calycosa!E$2:E$1000,1)), Calycosa!E$2:E$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Calycosa!E$2:E$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Calycosa!E$2:E$1000, Calycosa!E$2:E$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Calycosa!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Calycosa!E$2:E$1000,1)), Calycosa!E$2:E$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Calycosa!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Calycosa!E$2:E$1000,1))) &amp; " (" &amp; IF(MAX(Calycosa!E$2:E$1000)&gt;_xlfn.QUARTILE.INC(Calycosa!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Calycosa!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Calycosa!E$2:E$1000,1)),MAX(Calycosa!E$2:E$1000),"") &amp; ") mm"</f>
+        <v>() 0–0 (0.871) mm</v>
+      </c>
+    </row>
+    <row r="89" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I89" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="90" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I90" t="str">
+        <f>"(" &amp; IF(MIN(Fumosimontana!E$2:E$1000)&lt;_xlfn.QUARTILE.INC(Fumosimontana!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!E$2:E$1000,1)),MIN(Fumosimontana!E$2:E$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Fumosimontana!E$2:E$1000, Fumosimontana!E$2:E$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!E$2:E$1000,1)), Fumosimontana!E$2:E$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!E$2:E$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Fumosimontana!E$2:E$1000, Fumosimontana!E$2:E$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Fumosimontana!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!E$2:E$1000,1)), Fumosimontana!E$2:E$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Fumosimontana!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!E$2:E$1000,1))) &amp; " (" &amp; IF(MAX(Fumosimontana!E$2:E$1000)&gt;_xlfn.QUARTILE.INC(Fumosimontana!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Fumosimontana!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Fumosimontana!E$2:E$1000,1)),MAX(Fumosimontana!E$2:E$1000),"") &amp; ") mm"</f>
+        <v>() 0.98–2.76 () mm</v>
+      </c>
+    </row>
+    <row r="92" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I92" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="93" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I93" t="str">
+        <f>"(" &amp; IF(MIN(Grayana!E$2:E$1000)&lt;_xlfn.QUARTILE.INC(Grayana!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Grayana!E$2:E$1000,1)),MIN(Grayana!E$2:E$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Grayana!E$2:E$1000, Grayana!E$2:E$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Grayana!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Grayana!E$2:E$1000,1)), Grayana!E$2:E$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Grayana!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Grayana!E$2:E$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Grayana!E$2:E$1000, Grayana!E$2:E$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Grayana!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Grayana!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Grayana!E$2:E$1000,1)), Grayana!E$2:E$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Grayana!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Grayana!E$2:E$1000,1))) &amp; " (" &amp; IF(MAX(Grayana!E$2:E$1000)&gt;_xlfn.QUARTILE.INC(Grayana!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Grayana!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Grayana!E$2:E$1000,1)),MAX(Grayana!E$2:E$1000),"") &amp; ") mm"</f>
+        <v>() 0.804–2.26 (2.361) mm</v>
+      </c>
+    </row>
+    <row r="95" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I95" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="96" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I96" t="str">
+        <f>"(" &amp; IF(MIN(Richardsonii!E$2:E$1000)&lt;_xlfn.QUARTILE.INC(Richardsonii!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!E$2:E$1000,1)),MIN(Richardsonii!E$2:E$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Richardsonii!E$2:E$1000, Richardsonii!E$2:E$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!E$2:E$1000,1)), Richardsonii!E$2:E$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!E$2:E$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Richardsonii!E$2:E$1000, Richardsonii!E$2:E$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Richardsonii!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!E$2:E$1000,1)), Richardsonii!E$2:E$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Richardsonii!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!E$2:E$1000,1))) &amp; " (" &amp; IF(MAX(Richardsonii!E$2:E$1000)&gt;_xlfn.QUARTILE.INC(Richardsonii!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Richardsonii!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Richardsonii!E$2:E$1000,1)),MAX(Richardsonii!E$2:E$1000),"") &amp; ") mm"</f>
+        <v>(0) 0.707–1.79 (2.57) mm</v>
+      </c>
+    </row>
+    <row r="98" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I98" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="99" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I99" t="str">
+        <f>"(" &amp; IF(MIN(Hirsuticaulis!E$2:E$1000)&lt;_xlfn.QUARTILE.INC(Hirsuticaulis!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!E$2:E$1000,1)),MIN(Hirsuticaulis!E$2:E$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Hirsuticaulis!E$2:E$1000, Hirsuticaulis!E$2:E$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!E$2:E$1000,1)), Hirsuticaulis!E$2:E$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!E$2:E$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Hirsuticaulis!E$2:E$1000, Hirsuticaulis!E$2:E$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!E$2:E$1000,1)), Hirsuticaulis!E$2:E$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hirsuticaulis!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!E$2:E$1000,1))) &amp; " (" &amp; IF(MAX(Hirsuticaulis!E$2:E$1000)&gt;_xlfn.QUARTILE.INC(Hirsuticaulis!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hirsuticaulis!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Hirsuticaulis!E$2:E$1000,1)),MAX(Hirsuticaulis!E$2:E$1000),"") &amp; ") mm"</f>
+        <v>() 0.609–2.76 (3.542) mm</v>
+      </c>
+    </row>
+    <row r="101" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I101" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="102" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I102" t="str">
+        <f>"(" &amp; IF(MIN(Hispida!E$2:E$1000)&lt;_xlfn.QUARTILE.INC(Hispida!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Hispida!E$2:E$1000,1)),MIN(Hispida!E$2:E$1000),"") &amp; ") " &amp; _xlfn.MINIFS(Hispida!E$2:E$1000, Hispida!E$2:E$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hispida!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Hispida!E$2:E$1000,1)), Hispida!E$2:E$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hispida!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Hispida!E$2:E$1000,1))) &amp; "–" &amp; _xlfn.MAXIFS(Hispida!E$2:E$1000, Hispida!E$2:E$1000, "&gt;=" &amp; _xlfn.QUARTILE.INC(Hispida!E$2:E$1000,1)-1.5*(_xlfn.QUARTILE.INC(Hispida!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Hispida!E$2:E$1000,1)), Hispida!E$2:E$1000, "&lt;=" &amp; _xlfn.QUARTILE.INC(Hispida!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Hispida!E$2:E$1000,1))) &amp; " (" &amp; IF(MAX(Hispida!E$2:E$1000)&gt;_xlfn.QUARTILE.INC(Hispida!E$2:E$1000,3)+1.5*(_xlfn.QUARTILE.INC(Hispida!E$2:E$1000,3)-_xlfn.QUARTILE.INC(Hispida!E$2:E$1000,1)),MAX(Hispida!E$2:E$1000),"") &amp; ") mm"</f>
+        <v>() 0–0 () mm</v>
       </c>
     </row>
   </sheetData>
@@ -43025,52 +43124,43 @@
         <v>36</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>1.645</v>
       </c>
       <c r="I2">
-        <v>1.25</v>
+        <v>0.34599999999999997</v>
       </c>
       <c r="J2">
-        <v>2.6709999999999998</v>
+        <v>2.3719999999999999</v>
       </c>
       <c r="K2">
-        <v>1.18</v>
+        <v>1.413</v>
       </c>
       <c r="L2">
-        <v>1.0189999999999999</v>
+        <v>1.0049999999999999</v>
       </c>
       <c r="M2">
-        <v>1.74</v>
+        <v>1.302</v>
       </c>
       <c r="N2">
-        <v>3.6619999999999999</v>
+        <v>3.4460000000000002</v>
       </c>
       <c r="O2">
-        <v>3.5590000000000002</v>
+        <v>2.976</v>
       </c>
       <c r="P2">
-        <v>4.5869999999999997</v>
+        <v>2.37</v>
       </c>
       <c r="Q2">
-        <v>16.036999999999999</v>
+        <v>17.329999999999998</v>
       </c>
       <c r="R2">
-        <v>781.36699999999996</v>
+        <v>497.98599999999999</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
@@ -43078,52 +43168,43 @@
         <v>36</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H3">
-        <v>7.4989999999999997</v>
+        <v>2.129</v>
       </c>
       <c r="I3">
-        <v>1.675</v>
+        <v>1.256</v>
       </c>
       <c r="J3">
-        <v>3.03</v>
+        <v>2.2450000000000001</v>
       </c>
       <c r="K3">
-        <v>1.0640000000000001</v>
+        <v>1.1850000000000001</v>
       </c>
       <c r="L3">
-        <v>0.97199999999999998</v>
+        <v>0.98299999999999998</v>
       </c>
       <c r="M3">
-        <v>1.99</v>
+        <v>1.2749999999999999</v>
       </c>
       <c r="N3">
-        <v>2.5819999999999999</v>
+        <v>2.96</v>
       </c>
       <c r="O3">
-        <v>2.9129999999999998</v>
+        <v>1.6319999999999999</v>
       </c>
       <c r="P3">
-        <v>5.7</v>
+        <v>4.2119999999999997</v>
       </c>
       <c r="Q3">
-        <v>56.378999999999998</v>
+        <v>11.595000000000001</v>
+      </c>
+      <c r="R3">
+        <v>590.78200000000004</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
@@ -43131,52 +43212,43 @@
         <v>36</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1.3049999999999999</v>
       </c>
       <c r="H4">
-        <v>5.7770000000000001</v>
+        <v>2.1960000000000002</v>
       </c>
       <c r="I4">
-        <v>1.194</v>
+        <v>0.36</v>
       </c>
       <c r="J4">
-        <v>3.0169999999999999</v>
+        <v>2.7829999999999999</v>
       </c>
       <c r="K4">
-        <v>1.0089999999999999</v>
+        <v>1.0569999999999999</v>
       </c>
       <c r="L4">
-        <v>0.94899999999999995</v>
+        <v>0.94099999999999995</v>
       </c>
       <c r="M4">
-        <v>1.6970000000000001</v>
+        <v>1.4339999999999999</v>
       </c>
       <c r="N4">
-        <v>3.375</v>
+        <v>4.0940000000000003</v>
       </c>
       <c r="O4">
-        <v>3.63</v>
+        <v>4.0490000000000004</v>
       </c>
       <c r="P4">
-        <v>8.7750000000000004</v>
+        <v>4.7919999999999998</v>
       </c>
       <c r="Q4">
-        <v>26.954999999999998</v>
+        <v>23.524999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
@@ -43184,55 +43256,40 @@
         <v>36</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H5">
-        <v>6.0350000000000001</v>
+        <v>2.2229999999999999</v>
       </c>
       <c r="I5">
-        <v>2.7789999999999999</v>
+        <v>0.63300000000000001</v>
       </c>
       <c r="J5">
-        <v>4.1890000000000001</v>
+        <v>2.6379999999999999</v>
       </c>
       <c r="K5">
-        <v>1.5920000000000001</v>
+        <v>1.4990000000000001</v>
       </c>
       <c r="L5">
-        <v>1.351</v>
+        <v>1.3280000000000001</v>
       </c>
       <c r="M5">
-        <v>1.91</v>
+        <v>1.8720000000000001</v>
       </c>
       <c r="N5">
-        <v>3.7</v>
+        <v>3.1869999999999998</v>
       </c>
       <c r="O5">
-        <v>5.5679999999999996</v>
+        <v>1.7290000000000001</v>
       </c>
       <c r="P5">
-        <v>5.8570000000000002</v>
+        <v>2.5939999999999999</v>
       </c>
       <c r="Q5">
-        <v>23.795000000000002</v>
-      </c>
-      <c r="R5">
-        <v>745.75599999999997</v>
+        <v>10.677</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
@@ -43240,14 +43297,11 @@
         <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
         <v>38</v>
       </c>
-      <c r="D6" t="s">
-        <v>25</v>
-      </c>
       <c r="E6">
         <v>0</v>
       </c>
@@ -43255,40 +43309,37 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>0.79500000000000004</v>
       </c>
       <c r="H6">
-        <v>4.7510000000000003</v>
+        <v>2.3580000000000001</v>
       </c>
       <c r="I6">
-        <v>2.75</v>
+        <v>0.37</v>
       </c>
       <c r="J6">
-        <v>3.91</v>
+        <v>2.5710000000000002</v>
       </c>
       <c r="K6">
-        <v>1.109</v>
+        <v>2.1269999999999998</v>
       </c>
       <c r="L6">
-        <v>0.79400000000000004</v>
+        <v>1.9790000000000001</v>
       </c>
       <c r="M6">
-        <v>2.3140000000000001</v>
+        <v>2.077</v>
       </c>
       <c r="N6">
-        <v>4.6900000000000004</v>
+        <v>3.6619999999999999</v>
       </c>
       <c r="O6">
-        <v>4.609</v>
+        <v>3.6850000000000001</v>
       </c>
       <c r="P6">
-        <v>6.7060000000000004</v>
+        <v>3.4620000000000002</v>
       </c>
       <c r="Q6">
-        <v>18.245999999999999</v>
-      </c>
-      <c r="R6">
-        <v>590.99900000000002</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
@@ -43296,14 +43347,11 @@
         <v>36</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
         <v>38</v>
       </c>
-      <c r="D7" t="s">
-        <v>24</v>
-      </c>
       <c r="E7">
         <v>0</v>
       </c>
@@ -43311,37 +43359,40 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1.1140000000000001</v>
       </c>
       <c r="H7">
-        <v>4.1139999999999999</v>
+        <v>2.3650000000000002</v>
       </c>
       <c r="I7">
-        <v>2.0470000000000002</v>
+        <v>0.57899999999999996</v>
       </c>
       <c r="J7">
-        <v>4.2009999999999996</v>
+        <v>3</v>
       </c>
       <c r="K7">
-        <v>1.661</v>
+        <v>0.60599999999999998</v>
       </c>
       <c r="L7">
-        <v>1.516</v>
+        <v>0.59499999999999997</v>
       </c>
       <c r="M7">
-        <v>2.2269999999999999</v>
+        <v>2.2879999999999998</v>
       </c>
       <c r="N7">
-        <v>4.1479999999999997</v>
+        <v>3.448</v>
       </c>
       <c r="O7">
-        <v>4.0750000000000002</v>
+        <v>2.887</v>
       </c>
       <c r="P7">
-        <v>5.0529999999999999</v>
+        <v>3.7949999999999999</v>
       </c>
       <c r="Q7">
-        <v>14.175000000000001</v>
+        <v>29.815999999999999</v>
+      </c>
+      <c r="R7">
+        <v>770.83900000000006</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
@@ -43349,34 +43400,40 @@
         <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H8">
-        <v>5.2009999999999996</v>
+        <v>2.4740000000000002</v>
       </c>
       <c r="I8">
-        <v>2.6779999999999999</v>
+        <v>0.26900000000000002</v>
+      </c>
+      <c r="J8">
+        <v>2.9580000000000002</v>
+      </c>
+      <c r="K8">
+        <v>1.0369999999999999</v>
+      </c>
+      <c r="L8">
+        <v>1.147</v>
+      </c>
+      <c r="M8">
+        <v>1.64</v>
+      </c>
+      <c r="N8">
+        <v>3.87</v>
+      </c>
+      <c r="O8">
+        <v>2.468</v>
       </c>
       <c r="P8">
-        <v>12.923</v>
+        <v>1.1859999999999999</v>
       </c>
       <c r="Q8">
-        <v>18.338000000000001</v>
+        <v>10.564</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
@@ -43384,13 +43441,10 @@
         <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -43398,20 +43452,20 @@
       <c r="F9">
         <v>0</v>
       </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
       <c r="H9">
-        <v>3.2320000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="I9">
-        <v>1.55</v>
+        <v>0.60299999999999998</v>
       </c>
       <c r="P9">
-        <v>7.7320000000000002</v>
+        <v>2.2160000000000002</v>
       </c>
       <c r="Q9">
-        <v>17.463999999999999</v>
+        <v>14.59</v>
+      </c>
+      <c r="R9">
+        <v>725.89599999999996</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
@@ -43419,13 +43473,10 @@
         <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -43434,22 +43485,19 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>0.84599999999999997</v>
       </c>
       <c r="H10">
-        <v>6.2919999999999998</v>
+        <v>2.653</v>
       </c>
       <c r="I10">
-        <v>3.339</v>
+        <v>0.87</v>
       </c>
       <c r="P10">
-        <v>5.7670000000000003</v>
+        <v>3.238</v>
       </c>
       <c r="Q10">
-        <v>13.625999999999999</v>
-      </c>
-      <c r="R10">
-        <v>754.33699999999999</v>
+        <v>14.788</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
@@ -43457,13 +43505,10 @@
         <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -43471,41 +43516,17 @@
       <c r="F11">
         <v>0</v>
       </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
       <c r="H11">
-        <v>7.657</v>
+        <v>2.6949999999999998</v>
       </c>
       <c r="I11">
-        <v>2.4550000000000001</v>
-      </c>
-      <c r="J11">
-        <v>4.1900000000000004</v>
-      </c>
-      <c r="K11">
-        <v>0.92500000000000004</v>
-      </c>
-      <c r="L11">
-        <v>0.79600000000000004</v>
-      </c>
-      <c r="M11">
-        <v>2.87</v>
-      </c>
-      <c r="N11">
-        <v>5.21</v>
-      </c>
-      <c r="O11">
-        <v>4.3330000000000002</v>
+        <v>0.73</v>
       </c>
       <c r="P11">
-        <v>4.2320000000000002</v>
+        <v>5.1840000000000002</v>
       </c>
       <c r="Q11">
-        <v>7.4290000000000003</v>
-      </c>
-      <c r="R11">
-        <v>579.62199999999996</v>
+        <v>16.916</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
@@ -43513,52 +43534,46 @@
         <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>0.84499999999999997</v>
       </c>
       <c r="H12">
-        <v>6.3959999999999999</v>
+        <v>2.7519999999999998</v>
       </c>
       <c r="I12">
-        <v>2.8149999999999999</v>
+        <v>0.66400000000000003</v>
       </c>
       <c r="J12">
-        <v>3.637</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="K12">
-        <v>1.341</v>
+        <v>0.45100000000000001</v>
       </c>
       <c r="L12">
-        <v>1.1879999999999999</v>
+        <v>0.38</v>
       </c>
       <c r="M12">
-        <v>1.7969999999999999</v>
+        <v>1.4259999999999999</v>
       </c>
       <c r="N12">
-        <v>4.734</v>
+        <v>4.2430000000000003</v>
       </c>
       <c r="O12">
-        <v>3.19</v>
+        <v>4.9790000000000001</v>
       </c>
       <c r="P12">
-        <v>2.3479999999999999</v>
+        <v>5.7290000000000001</v>
       </c>
       <c r="Q12">
-        <v>10.004</v>
+        <v>7.4320000000000004</v>
       </c>
       <c r="R12">
-        <v>590.68600000000004</v>
+        <v>845.24</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
@@ -43566,10 +43581,13 @@
         <v>36</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>64</v>
+      </c>
+      <c r="D13" t="s">
+        <v>24</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -43580,32 +43598,11 @@
       <c r="G13">
         <v>0</v>
       </c>
-      <c r="J13">
-        <v>3.7160000000000002</v>
-      </c>
-      <c r="K13">
-        <v>1.6679999999999999</v>
-      </c>
-      <c r="L13">
-        <v>1.458</v>
-      </c>
-      <c r="M13">
-        <v>1.9650000000000001</v>
-      </c>
-      <c r="N13">
-        <v>4.766</v>
-      </c>
-      <c r="O13">
-        <v>3.915</v>
-      </c>
-      <c r="P13">
-        <v>3.4550000000000001</v>
-      </c>
-      <c r="Q13">
-        <v>18.951000000000001</v>
-      </c>
-      <c r="R13">
-        <v>539.70299999999997</v>
+      <c r="H13">
+        <v>3.008</v>
+      </c>
+      <c r="I13">
+        <v>1.0529999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
@@ -43613,10 +43610,10 @@
         <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
         <v>21</v>
@@ -43631,37 +43628,34 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>6.1920000000000002</v>
+        <v>3.1880000000000002</v>
       </c>
       <c r="I14">
-        <v>1.571</v>
+        <v>1.218</v>
       </c>
       <c r="J14">
-        <v>3.6640000000000001</v>
+        <v>2.6240000000000001</v>
       </c>
       <c r="K14">
-        <v>1.361</v>
+        <v>0.86899999999999999</v>
       </c>
       <c r="L14">
-        <v>1.036</v>
+        <v>0.61299999999999999</v>
       </c>
       <c r="M14">
-        <v>1.5</v>
+        <v>1.5960000000000001</v>
       </c>
       <c r="N14">
-        <v>4.2519999999999998</v>
-      </c>
-      <c r="O14">
-        <v>4.4740000000000002</v>
+        <v>3.83</v>
       </c>
       <c r="P14">
-        <v>5.0410000000000004</v>
+        <v>5.9210000000000003</v>
       </c>
       <c r="Q14">
-        <v>18.446000000000002</v>
+        <v>27.062000000000001</v>
       </c>
       <c r="R14">
-        <v>823.12199999999996</v>
+        <v>1012.704</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
@@ -43669,10 +43663,10 @@
         <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
         <v>21</v>
@@ -43687,37 +43681,37 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>6.149</v>
+        <v>3.2069999999999999</v>
       </c>
       <c r="I15">
-        <v>1.6890000000000001</v>
+        <v>2.1389999999999998</v>
       </c>
       <c r="J15">
-        <v>3.9049999999999998</v>
+        <v>2.593</v>
       </c>
       <c r="K15">
-        <v>0.99199999999999999</v>
+        <v>0.99299999999999999</v>
       </c>
       <c r="L15">
-        <v>0.92800000000000005</v>
+        <v>0.88600000000000001</v>
       </c>
       <c r="M15">
-        <v>1.841</v>
+        <v>1.524</v>
       </c>
       <c r="N15">
-        <v>4.3620000000000001</v>
+        <v>4.5149999999999997</v>
       </c>
       <c r="O15">
-        <v>3.1829999999999998</v>
+        <v>3.548</v>
       </c>
       <c r="P15">
-        <v>3.85</v>
+        <v>2.4</v>
       </c>
       <c r="Q15">
-        <v>36.018999999999998</v>
+        <v>12.63</v>
       </c>
       <c r="R15">
-        <v>732.04200000000003</v>
+        <v>847.38099999999997</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
@@ -43725,10 +43719,10 @@
         <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C16" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D16" t="s">
         <v>21</v>
@@ -43743,34 +43737,16 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>5.1769999999999996</v>
+        <v>3.2320000000000002</v>
       </c>
       <c r="I16">
-        <v>1.6259999999999999</v>
-      </c>
-      <c r="J16">
-        <v>4.0190000000000001</v>
-      </c>
-      <c r="K16">
-        <v>1.532</v>
-      </c>
-      <c r="L16">
-        <v>1.339</v>
-      </c>
-      <c r="M16">
-        <v>1.488</v>
-      </c>
-      <c r="N16">
-        <v>4.702</v>
-      </c>
-      <c r="O16">
-        <v>3.8580000000000001</v>
+        <v>1.55</v>
       </c>
       <c r="P16">
-        <v>6.7830000000000004</v>
+        <v>7.7320000000000002</v>
       </c>
       <c r="Q16">
-        <v>33.136000000000003</v>
+        <v>17.463999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
@@ -43778,13 +43754,10 @@
         <v>36</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s">
-        <v>46</v>
-      </c>
-      <c r="D17" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -43793,40 +43766,37 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>0.93700000000000006</v>
       </c>
       <c r="H17">
-        <v>4.57</v>
+        <v>3.2759999999999998</v>
       </c>
       <c r="I17">
-        <v>1.234</v>
+        <v>0.749</v>
       </c>
       <c r="J17">
-        <v>3.234</v>
+        <v>2.694</v>
       </c>
       <c r="K17">
-        <v>1.3959999999999999</v>
+        <v>1.2070000000000001</v>
       </c>
       <c r="L17">
-        <v>1.35</v>
+        <v>1.1080000000000001</v>
       </c>
       <c r="M17">
-        <v>2.5760000000000001</v>
+        <v>2.5270000000000001</v>
       </c>
       <c r="N17">
-        <v>3.11</v>
-      </c>
-      <c r="O17">
-        <v>2.7229999999999999</v>
+        <v>4.0540000000000003</v>
       </c>
       <c r="P17">
-        <v>4.8949999999999996</v>
+        <v>5.556</v>
       </c>
       <c r="Q17">
-        <v>18.914000000000001</v>
+        <v>17.588000000000001</v>
       </c>
       <c r="R17">
-        <v>743.88400000000001</v>
+        <v>692.99699999999996</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.2">
@@ -43834,13 +43804,10 @@
         <v>36</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -43849,40 +43816,34 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>0.998</v>
       </c>
       <c r="H18">
-        <v>5.1239999999999997</v>
+        <v>3.4609999999999999</v>
       </c>
       <c r="I18">
-        <v>1.2569999999999999</v>
+        <v>0.70599999999999996</v>
       </c>
       <c r="J18">
-        <v>3.3929999999999998</v>
+        <v>3.4220000000000002</v>
       </c>
       <c r="K18">
-        <v>1.081</v>
+        <v>1.488</v>
       </c>
       <c r="L18">
-        <v>1.0720000000000001</v>
+        <v>1.4550000000000001</v>
       </c>
       <c r="M18">
-        <v>1.387</v>
+        <v>2.5</v>
       </c>
       <c r="N18">
-        <v>3.7989999999999999</v>
-      </c>
-      <c r="O18">
-        <v>3.3069999999999999</v>
+        <v>3.4980000000000002</v>
       </c>
       <c r="P18">
-        <v>9.4019999999999992</v>
+        <v>5.1710000000000003</v>
       </c>
       <c r="Q18">
-        <v>19.684000000000001</v>
-      </c>
-      <c r="R18">
-        <v>880.28499999999997</v>
+        <v>23.29</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.2">
@@ -43890,13 +43851,10 @@
         <v>36</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>46</v>
-      </c>
-      <c r="D19" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -43904,38 +43862,35 @@
       <c r="F19">
         <v>0</v>
       </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
       <c r="H19">
-        <v>5.5259999999999998</v>
+        <v>3.492</v>
       </c>
       <c r="I19">
-        <v>1.3160000000000001</v>
+        <v>0.95799999999999996</v>
       </c>
       <c r="J19">
-        <v>3.0379999999999998</v>
+        <v>2.4430000000000001</v>
       </c>
       <c r="K19">
-        <v>1.587</v>
+        <v>1.161</v>
       </c>
       <c r="L19">
-        <v>1.544</v>
+        <v>0.80300000000000005</v>
       </c>
       <c r="M19">
-        <v>1.9450000000000001</v>
+        <v>1.8069999999999999</v>
       </c>
       <c r="N19">
-        <v>4.0869999999999997</v>
-      </c>
-      <c r="O19">
-        <v>3.5339999999999998</v>
+        <v>3.7639999999999998</v>
       </c>
       <c r="P19">
-        <v>6.1219999999999999</v>
+        <v>5.1680000000000001</v>
       </c>
       <c r="Q19">
-        <v>26.518999999999998</v>
+        <v>26.728999999999999</v>
+      </c>
+      <c r="R19">
+        <v>373.80900000000003</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.2">
@@ -43943,13 +43898,13 @@
         <v>36</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D20" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -43961,37 +43916,34 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>5.6310000000000002</v>
+        <v>3.5129999999999999</v>
       </c>
       <c r="I20">
-        <v>1.4730000000000001</v>
+        <v>1.2450000000000001</v>
       </c>
       <c r="J20">
-        <v>4.5999999999999996</v>
+        <v>4.032</v>
       </c>
       <c r="K20">
-        <v>1.6060000000000001</v>
+        <v>0.75900000000000001</v>
       </c>
       <c r="L20">
-        <v>1.2270000000000001</v>
+        <v>0.53100000000000003</v>
       </c>
       <c r="M20">
-        <v>2.109</v>
+        <v>2.8079999999999998</v>
       </c>
       <c r="N20">
-        <v>3.6040000000000001</v>
+        <v>4.5330000000000004</v>
       </c>
       <c r="O20">
-        <v>3.871</v>
+        <v>1.8620000000000001</v>
       </c>
       <c r="P20">
-        <v>8.1430000000000007</v>
+        <v>3.5960000000000001</v>
       </c>
       <c r="Q20">
-        <v>61.502000000000002</v>
-      </c>
-      <c r="R20">
-        <v>665.44399999999996</v>
+        <v>32.378999999999998</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.2">
@@ -43999,10 +43951,10 @@
         <v>36</v>
       </c>
       <c r="B21" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="D21" t="s">
         <v>21</v>
@@ -44013,14 +43965,38 @@
       <c r="F21">
         <v>0</v>
       </c>
-      <c r="G21">
-        <v>0</v>
+      <c r="H21">
+        <v>3.5979999999999999</v>
+      </c>
+      <c r="I21">
+        <v>1.4259999999999999</v>
+      </c>
+      <c r="J21">
+        <v>3.42</v>
+      </c>
+      <c r="K21">
+        <v>1.044</v>
+      </c>
+      <c r="L21">
+        <v>0.45600000000000002</v>
+      </c>
+      <c r="M21">
+        <v>2.3439999999999999</v>
+      </c>
+      <c r="N21">
+        <v>3.9940000000000002</v>
+      </c>
+      <c r="O21">
+        <v>3.7069999999999999</v>
       </c>
       <c r="P21">
-        <v>7.3390000000000004</v>
+        <v>4.1630000000000003</v>
       </c>
       <c r="Q21">
-        <v>43.118000000000002</v>
+        <v>23.713000000000001</v>
+      </c>
+      <c r="R21">
+        <v>791.32</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.2">
@@ -44028,10 +44004,10 @@
         <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="C22" t="s">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="D22" t="s">
         <v>21</v>
@@ -44042,14 +44018,35 @@
       <c r="F22">
         <v>0</v>
       </c>
-      <c r="G22">
-        <v>0</v>
+      <c r="H22">
+        <v>3.6040000000000001</v>
+      </c>
+      <c r="I22">
+        <v>0.89600000000000002</v>
+      </c>
+      <c r="J22">
+        <v>3.9529999999999998</v>
+      </c>
+      <c r="K22">
+        <v>1.381</v>
+      </c>
+      <c r="L22">
+        <v>1.2789999999999999</v>
+      </c>
+      <c r="M22">
+        <v>2.1579999999999999</v>
+      </c>
+      <c r="N22">
+        <v>3.7949999999999999</v>
+      </c>
+      <c r="O22">
+        <v>3.5129999999999999</v>
       </c>
       <c r="P22">
-        <v>7.62</v>
+        <v>3.956</v>
       </c>
       <c r="Q22">
-        <v>44.331000000000003</v>
+        <v>13.515000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.2">
@@ -44057,13 +44054,13 @@
         <v>36</v>
       </c>
       <c r="B23" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C23" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="D23" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -44075,37 +44072,37 @@
         <v>0</v>
       </c>
       <c r="H23">
-        <v>5.4550000000000001</v>
+        <v>3.6080000000000001</v>
       </c>
       <c r="I23">
-        <v>2.1739999999999999</v>
+        <v>1.196</v>
       </c>
       <c r="J23">
-        <v>3.8220000000000001</v>
+        <v>2.911</v>
       </c>
       <c r="K23">
-        <v>0.69399999999999995</v>
+        <v>0.88900000000000001</v>
       </c>
       <c r="L23">
-        <v>0.57299999999999995</v>
+        <v>0.88300000000000001</v>
       </c>
       <c r="M23">
-        <v>2.645</v>
+        <v>2.3959999999999999</v>
       </c>
       <c r="N23">
-        <v>4.75</v>
+        <v>3.4630000000000001</v>
       </c>
       <c r="O23">
-        <v>5.24</v>
+        <v>2.8519999999999999</v>
       </c>
       <c r="P23">
-        <v>2.4159999999999999</v>
+        <v>5.3890000000000002</v>
       </c>
       <c r="Q23">
-        <v>16.420999999999999</v>
+        <v>20.375</v>
       </c>
       <c r="R23">
-        <v>713.46799999999996</v>
+        <v>581.94899999999996</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.2">
@@ -44113,52 +44110,22 @@
         <v>36</v>
       </c>
       <c r="B24" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
         <v>50</v>
       </c>
-      <c r="D24" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
       <c r="H24">
-        <v>6.2229999999999999</v>
+        <v>3.6379999999999999</v>
       </c>
       <c r="I24">
-        <v>2.649</v>
-      </c>
-      <c r="J24">
-        <v>4.3929999999999998</v>
-      </c>
-      <c r="K24">
-        <v>1.2709999999999999</v>
-      </c>
-      <c r="L24">
-        <v>1.085</v>
-      </c>
-      <c r="M24">
-        <v>2.778</v>
-      </c>
-      <c r="N24">
-        <v>4.6079999999999997</v>
-      </c>
-      <c r="O24">
-        <v>4.6970000000000001</v>
+        <v>1.2569999999999999</v>
       </c>
       <c r="P24">
-        <v>3.218</v>
+        <v>4.9649999999999999</v>
       </c>
       <c r="Q24">
-        <v>24.195</v>
+        <v>7.5229999999999997</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.2">
@@ -44166,10 +44133,10 @@
         <v>36</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="C25" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D25" t="s">
         <v>21</v>
@@ -44184,34 +44151,37 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <v>4.9800000000000004</v>
+        <v>3.641</v>
       </c>
       <c r="I25">
-        <v>2.177</v>
+        <v>1.4630000000000001</v>
       </c>
       <c r="J25">
-        <v>3.722</v>
+        <v>4.1130000000000004</v>
       </c>
       <c r="K25">
-        <v>0.69699999999999995</v>
+        <v>1.079</v>
       </c>
       <c r="L25">
-        <v>0.48199999999999998</v>
+        <v>0.83699999999999997</v>
       </c>
       <c r="M25">
-        <v>2.5249999999999999</v>
+        <v>2.4260000000000002</v>
       </c>
       <c r="N25">
-        <v>4.5990000000000002</v>
+        <v>3.5110000000000001</v>
       </c>
       <c r="O25">
-        <v>4.1239999999999997</v>
+        <v>5.2480000000000002</v>
       </c>
       <c r="P25">
-        <v>3.1230000000000002</v>
+        <v>5.5609999999999999</v>
       </c>
       <c r="Q25">
-        <v>20.695</v>
+        <v>11.414999999999999</v>
+      </c>
+      <c r="R25">
+        <v>621.04100000000005</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.2">
@@ -44219,10 +44189,13 @@
         <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="C26" t="s">
-        <v>52</v>
+        <v>81</v>
+      </c>
+      <c r="D26" t="s">
+        <v>25</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -44231,37 +44204,37 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>0.89900000000000002</v>
       </c>
       <c r="H26">
-        <v>3.7759999999999998</v>
+        <v>3.7349999999999999</v>
       </c>
       <c r="I26">
-        <v>1.5669999999999999</v>
+        <v>0.59499999999999997</v>
       </c>
       <c r="J26">
-        <v>4.68</v>
+        <v>5.6589999999999998</v>
       </c>
       <c r="K26">
-        <v>1.3140000000000001</v>
+        <v>2.0110000000000001</v>
       </c>
       <c r="L26">
-        <v>1.2330000000000001</v>
+        <v>1.31</v>
       </c>
       <c r="M26">
-        <v>2.4910000000000001</v>
+        <v>2.9209999999999998</v>
       </c>
       <c r="N26">
-        <v>4.9189999999999996</v>
+        <v>4.83</v>
       </c>
       <c r="O26">
-        <v>4.8150000000000004</v>
+        <v>3.508</v>
       </c>
       <c r="P26">
-        <v>2.4729999999999999</v>
+        <v>2.1349999999999998</v>
       </c>
       <c r="Q26">
-        <v>15.706</v>
+        <v>4.9080000000000004</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.2">
@@ -44269,49 +44242,25 @@
         <v>36</v>
       </c>
       <c r="B27" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="C27" t="s">
-        <v>52</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-      <c r="F27">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>1.583</v>
       </c>
       <c r="H27">
-        <v>3.8780000000000001</v>
+        <v>3.7349999999999999</v>
       </c>
       <c r="I27">
-        <v>1.2150000000000001</v>
-      </c>
-      <c r="J27">
-        <v>4.6360000000000001</v>
-      </c>
-      <c r="K27">
-        <v>1.087</v>
-      </c>
-      <c r="L27">
-        <v>0.80800000000000005</v>
-      </c>
-      <c r="M27">
-        <v>2.5630000000000002</v>
-      </c>
-      <c r="N27">
-        <v>5.0410000000000004</v>
-      </c>
-      <c r="O27">
-        <v>4.2789999999999999</v>
+        <v>0.70499999999999996</v>
       </c>
       <c r="P27">
-        <v>6.4939999999999998</v>
+        <v>3.8220000000000001</v>
       </c>
       <c r="Q27">
-        <v>19.3</v>
+        <v>33.098999999999997</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.2">
@@ -44319,49 +44268,22 @@
         <v>36</v>
       </c>
       <c r="B28" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="C28" t="s">
-        <v>52</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-      <c r="F28">
-        <v>0</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H28">
-        <v>3.746</v>
+        <v>3.7360000000000002</v>
       </c>
       <c r="I28">
-        <v>1.4570000000000001</v>
-      </c>
-      <c r="J28">
-        <v>4.9660000000000002</v>
-      </c>
-      <c r="K28">
-        <v>1.7070000000000001</v>
-      </c>
-      <c r="L28">
-        <v>1.6180000000000001</v>
-      </c>
-      <c r="M28">
-        <v>2.859</v>
-      </c>
-      <c r="N28">
-        <v>4.9409999999999998</v>
-      </c>
-      <c r="O28">
-        <v>4.9610000000000003</v>
+        <v>0.39900000000000002</v>
       </c>
       <c r="P28">
-        <v>3.492</v>
+        <v>2.3820000000000001</v>
       </c>
       <c r="Q28">
-        <v>15.236000000000001</v>
+        <v>9.1880000000000006</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.2">
@@ -44369,13 +44291,13 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="C29" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="D29" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -44384,37 +44306,40 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>1.077</v>
       </c>
       <c r="H29">
-        <v>10.263999999999999</v>
+        <v>3.7440000000000002</v>
       </c>
       <c r="I29">
-        <v>4.327</v>
+        <v>0.371</v>
       </c>
       <c r="J29">
-        <v>3.4039999999999999</v>
+        <v>4.4240000000000004</v>
       </c>
       <c r="K29">
-        <v>1.1759999999999999</v>
+        <v>1.091</v>
       </c>
       <c r="L29">
-        <v>1.105</v>
+        <v>0.63</v>
       </c>
       <c r="M29">
-        <v>1.7450000000000001</v>
+        <v>3.0750000000000002</v>
       </c>
       <c r="N29">
-        <v>4.7569999999999997</v>
+        <v>4.4409999999999998</v>
+      </c>
+      <c r="O29">
+        <v>4.4279999999999999</v>
       </c>
       <c r="P29">
-        <v>3.593</v>
+        <v>1.573</v>
       </c>
       <c r="Q29">
-        <v>21.428999999999998</v>
+        <v>16.478000000000002</v>
       </c>
       <c r="R29">
-        <v>611.54600000000005</v>
+        <v>343.41500000000002</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.2">
@@ -44422,10 +44347,10 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C30" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -44437,37 +44362,34 @@
         <v>0</v>
       </c>
       <c r="H30">
-        <v>9.1129999999999995</v>
+        <v>3.746</v>
       </c>
       <c r="I30">
-        <v>3.8319999999999999</v>
+        <v>1.4570000000000001</v>
       </c>
       <c r="J30">
-        <v>3.54</v>
+        <v>4.9660000000000002</v>
       </c>
       <c r="K30">
-        <v>1.609</v>
+        <v>1.7070000000000001</v>
       </c>
       <c r="L30">
-        <v>1.476</v>
+        <v>1.6180000000000001</v>
       </c>
       <c r="M30">
-        <v>1.4490000000000001</v>
+        <v>2.859</v>
       </c>
       <c r="N30">
-        <v>4.2910000000000004</v>
+        <v>4.9409999999999998</v>
       </c>
       <c r="O30">
-        <v>3.8140000000000001</v>
+        <v>4.9610000000000003</v>
       </c>
       <c r="P30">
-        <v>2.4820000000000002</v>
+        <v>3.492</v>
       </c>
       <c r="Q30">
-        <v>16.744</v>
-      </c>
-      <c r="R30">
-        <v>655.952</v>
+        <v>15.236000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.2">
@@ -44475,10 +44397,10 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C31" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -44490,37 +44412,34 @@
         <v>0</v>
       </c>
       <c r="H31">
-        <v>10.68</v>
+        <v>3.7759999999999998</v>
       </c>
       <c r="I31">
-        <v>6.49</v>
+        <v>1.5669999999999999</v>
       </c>
       <c r="J31">
-        <v>4.0190000000000001</v>
+        <v>4.68</v>
       </c>
       <c r="K31">
-        <v>0.96</v>
+        <v>1.3140000000000001</v>
       </c>
       <c r="L31">
-        <v>0.91600000000000004</v>
+        <v>1.2330000000000001</v>
       </c>
       <c r="M31">
-        <v>3.5640000000000001</v>
+        <v>2.4910000000000001</v>
       </c>
       <c r="N31">
-        <v>4.1959999999999997</v>
+        <v>4.9189999999999996</v>
       </c>
       <c r="O31">
-        <v>3.8759999999999999</v>
+        <v>4.8150000000000004</v>
       </c>
       <c r="P31">
-        <v>3.8050000000000002</v>
+        <v>2.4729999999999999</v>
       </c>
       <c r="Q31">
-        <v>13.739000000000001</v>
-      </c>
-      <c r="R31">
-        <v>696.42700000000002</v>
+        <v>15.706</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.2">
@@ -44528,13 +44447,13 @@
         <v>36</v>
       </c>
       <c r="B32" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="C32" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D32" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -44543,40 +44462,13 @@
         <v>0</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>0.93899999999999995</v>
       </c>
       <c r="H32">
-        <v>7.423</v>
+        <v>3.823</v>
       </c>
       <c r="I32">
-        <v>2.5110000000000001</v>
-      </c>
-      <c r="J32">
-        <v>4.3499999999999996</v>
-      </c>
-      <c r="K32">
-        <v>1.7789999999999999</v>
-      </c>
-      <c r="L32">
-        <v>1.7450000000000001</v>
-      </c>
-      <c r="M32">
-        <v>2.6749999999999998</v>
-      </c>
-      <c r="N32">
-        <v>3.2160000000000002</v>
-      </c>
-      <c r="O32">
-        <v>3.29</v>
-      </c>
-      <c r="P32">
-        <v>2.6640000000000001</v>
-      </c>
-      <c r="Q32">
-        <v>18.071999999999999</v>
-      </c>
-      <c r="R32">
-        <v>709.48199999999997</v>
+        <v>1.5740000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.2">
@@ -44584,10 +44476,10 @@
         <v>36</v>
       </c>
       <c r="B33" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="C33" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -44596,37 +44488,22 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>0.95199999999999996</v>
       </c>
       <c r="H33">
-        <v>5.944</v>
+        <v>3.847</v>
       </c>
       <c r="I33">
-        <v>1.613</v>
-      </c>
-      <c r="J33">
-        <v>4.7300000000000004</v>
-      </c>
-      <c r="K33">
-        <v>1.611</v>
-      </c>
-      <c r="L33">
-        <v>1.399</v>
-      </c>
-      <c r="M33">
-        <v>2.806</v>
-      </c>
-      <c r="N33">
-        <v>2.9449999999999998</v>
-      </c>
-      <c r="O33">
-        <v>4.7119999999999997</v>
+        <v>1.468</v>
       </c>
       <c r="P33">
-        <v>2.5110000000000001</v>
+        <v>2.7330000000000001</v>
       </c>
       <c r="Q33">
-        <v>32.643000000000001</v>
+        <v>21.722000000000001</v>
+      </c>
+      <c r="R33">
+        <v>520.31100000000004</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.2">
@@ -44634,10 +44511,10 @@
         <v>36</v>
       </c>
       <c r="B34" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C34" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -44649,13 +44526,34 @@
         <v>0</v>
       </c>
       <c r="H34">
-        <v>7.2510000000000003</v>
+        <v>3.8780000000000001</v>
       </c>
       <c r="I34">
-        <v>1.913</v>
+        <v>1.2150000000000001</v>
+      </c>
+      <c r="J34">
+        <v>4.6360000000000001</v>
+      </c>
+      <c r="K34">
+        <v>1.087</v>
+      </c>
+      <c r="L34">
+        <v>0.80800000000000005</v>
+      </c>
+      <c r="M34">
+        <v>2.5630000000000002</v>
+      </c>
+      <c r="N34">
+        <v>5.0410000000000004</v>
+      </c>
+      <c r="O34">
+        <v>4.2789999999999999</v>
+      </c>
+      <c r="P34">
+        <v>6.4939999999999998</v>
       </c>
       <c r="Q34">
-        <v>12.417</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.2">
@@ -44663,10 +44561,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="C35" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="D35" t="s">
         <v>21</v>
@@ -44678,40 +44576,37 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>0.70099999999999996</v>
       </c>
       <c r="H35">
-        <v>5.524</v>
+        <v>3.9009999999999998</v>
       </c>
       <c r="I35">
-        <v>2.5750000000000002</v>
+        <v>1.431</v>
       </c>
       <c r="J35">
-        <v>3.411</v>
+        <v>2.5760000000000001</v>
       </c>
       <c r="K35">
-        <v>0.42299999999999999</v>
+        <v>0.78200000000000003</v>
       </c>
       <c r="L35">
-        <v>0.38600000000000001</v>
+        <v>0.76500000000000001</v>
       </c>
       <c r="M35">
-        <v>2.605</v>
+        <v>1.881</v>
       </c>
       <c r="N35">
-        <v>2.6850000000000001</v>
+        <v>4.0369999999999999</v>
       </c>
       <c r="O35">
-        <v>2.1269999999999998</v>
+        <v>2.9169999999999998</v>
       </c>
       <c r="P35">
-        <v>5.625</v>
+        <v>2.423</v>
       </c>
       <c r="Q35">
-        <v>13.702999999999999</v>
-      </c>
-      <c r="R35">
-        <v>662.31899999999996</v>
+        <v>9.3369999999999997</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.2">
@@ -44719,14 +44614,11 @@
         <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="C36" t="s">
         <v>38</v>
       </c>
-      <c r="D36" t="s">
-        <v>21</v>
-      </c>
       <c r="E36">
         <v>0</v>
       </c>
@@ -44734,40 +44626,40 @@
         <v>0</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>0.90200000000000002</v>
       </c>
       <c r="H36">
-        <v>3.6080000000000001</v>
+        <v>3.9129999999999998</v>
       </c>
       <c r="I36">
-        <v>1.196</v>
+        <v>0.92</v>
       </c>
       <c r="J36">
-        <v>2.911</v>
+        <v>3.9039999999999999</v>
       </c>
       <c r="K36">
-        <v>0.88900000000000001</v>
+        <v>0.56299999999999994</v>
       </c>
       <c r="L36">
-        <v>0.88300000000000001</v>
+        <v>0.42099999999999999</v>
       </c>
       <c r="M36">
-        <v>2.3959999999999999</v>
+        <v>2.57</v>
       </c>
       <c r="N36">
-        <v>3.4630000000000001</v>
+        <v>4.8630000000000004</v>
       </c>
       <c r="O36">
-        <v>2.8519999999999999</v>
+        <v>2.7770000000000001</v>
       </c>
       <c r="P36">
-        <v>5.3890000000000002</v>
+        <v>8.7370000000000001</v>
       </c>
       <c r="Q36">
-        <v>20.375</v>
+        <v>22.951000000000001</v>
       </c>
       <c r="R36">
-        <v>581.94899999999996</v>
+        <v>238.65199999999999</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.2">
@@ -44775,10 +44667,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C37" t="s">
-        <v>38</v>
+        <v>64</v>
+      </c>
+      <c r="D37" t="s">
+        <v>21</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -44790,34 +44685,31 @@
         <v>0</v>
       </c>
       <c r="H37">
-        <v>4.9320000000000004</v>
+        <v>4.1059999999999999</v>
       </c>
       <c r="I37">
-        <v>1.4930000000000001</v>
+        <v>1.405</v>
       </c>
       <c r="J37">
-        <v>2.96</v>
-      </c>
-      <c r="K37">
-        <v>0.89800000000000002</v>
-      </c>
-      <c r="L37">
-        <v>0.629</v>
+        <v>3.4169999999999998</v>
       </c>
       <c r="M37">
-        <v>2.238</v>
+        <v>2.952</v>
       </c>
       <c r="N37">
-        <v>4.2969999999999997</v>
+        <v>3.8130000000000002</v>
       </c>
       <c r="O37">
-        <v>3.327</v>
+        <v>3.5009999999999999</v>
       </c>
       <c r="P37">
-        <v>3.17</v>
+        <v>3.41</v>
       </c>
       <c r="Q37">
-        <v>12.349</v>
+        <v>13.284000000000001</v>
+      </c>
+      <c r="R37">
+        <v>702.21600000000001</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.2">
@@ -44825,13 +44717,13 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="C38" t="s">
         <v>38</v>
       </c>
       <c r="D38" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -44843,37 +44735,34 @@
         <v>0</v>
       </c>
       <c r="H38">
-        <v>5.5949999999999998</v>
+        <v>4.1139999999999999</v>
       </c>
       <c r="I38">
-        <v>1.5229999999999999</v>
+        <v>2.0470000000000002</v>
       </c>
       <c r="J38">
-        <v>3.6030000000000002</v>
+        <v>4.2009999999999996</v>
       </c>
       <c r="K38">
-        <v>1.907</v>
+        <v>1.661</v>
       </c>
       <c r="L38">
-        <v>1.905</v>
+        <v>1.516</v>
       </c>
       <c r="M38">
-        <v>1.454</v>
+        <v>2.2269999999999999</v>
       </c>
       <c r="N38">
-        <v>3.7080000000000002</v>
+        <v>4.1479999999999997</v>
       </c>
       <c r="O38">
-        <v>3.4489999999999998</v>
+        <v>4.0750000000000002</v>
       </c>
       <c r="P38">
-        <v>2.1989999999999998</v>
+        <v>5.0529999999999999</v>
       </c>
       <c r="Q38">
-        <v>26.12</v>
-      </c>
-      <c r="R38">
-        <v>792.803</v>
+        <v>14.175000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.2">
@@ -44881,13 +44770,13 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C39" t="s">
         <v>38</v>
       </c>
       <c r="D39" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -44899,31 +44788,37 @@
         <v>0</v>
       </c>
       <c r="H39">
-        <v>6.6230000000000002</v>
+        <v>4.2770000000000001</v>
       </c>
       <c r="I39">
-        <v>2.4950000000000001</v>
+        <v>1.302</v>
       </c>
       <c r="J39">
-        <v>3.3420000000000001</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="K39">
-        <v>1.179</v>
+        <v>1.845</v>
       </c>
       <c r="L39">
-        <v>0.95399999999999996</v>
+        <v>1.661</v>
       </c>
       <c r="M39">
-        <v>2.4900000000000002</v>
+        <v>2.7320000000000002</v>
       </c>
       <c r="N39">
-        <v>4.032</v>
+        <v>3.9860000000000002</v>
+      </c>
+      <c r="O39">
+        <v>4.2279999999999998</v>
       </c>
       <c r="P39">
-        <v>4.2030000000000003</v>
+        <v>4.4640000000000004</v>
       </c>
       <c r="Q39">
-        <v>15.401999999999999</v>
+        <v>5.7110000000000003</v>
+      </c>
+      <c r="R39">
+        <v>478.97</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.2">
@@ -44931,13 +44826,13 @@
         <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="C40" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D40" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -44946,22 +44841,40 @@
         <v>0</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>0.72299999999999998</v>
       </c>
       <c r="H40">
-        <v>4.38</v>
+        <v>4.335</v>
       </c>
       <c r="I40">
-        <v>1.325</v>
+        <v>1.163</v>
+      </c>
+      <c r="J40">
+        <v>3.7</v>
+      </c>
+      <c r="K40">
+        <v>0.95699999999999996</v>
+      </c>
+      <c r="L40">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="M40">
+        <v>2.2080000000000002</v>
       </c>
       <c r="N40">
-        <v>3.9380000000000002</v>
+        <v>3.4950000000000001</v>
+      </c>
+      <c r="O40">
+        <v>3.5019999999999998</v>
       </c>
       <c r="P40">
-        <v>3.3959999999999999</v>
+        <v>4.0129999999999999</v>
       </c>
       <c r="Q40">
-        <v>13.666</v>
+        <v>14.654</v>
+      </c>
+      <c r="R40">
+        <v>457.39600000000002</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.2">
@@ -44969,13 +44882,13 @@
         <v>36</v>
       </c>
       <c r="B41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C41" t="s">
         <v>38</v>
       </c>
       <c r="D41" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -44987,28 +44900,19 @@
         <v>0</v>
       </c>
       <c r="H41">
-        <v>7.8369999999999997</v>
+        <v>4.38</v>
       </c>
       <c r="I41">
-        <v>4.2949999999999999</v>
-      </c>
-      <c r="J41">
-        <v>4.1970000000000001</v>
-      </c>
-      <c r="M41">
-        <v>1.2729999999999999</v>
+        <v>1.325</v>
       </c>
       <c r="N41">
-        <v>3.177</v>
-      </c>
-      <c r="O41">
-        <v>4.2709999999999999</v>
+        <v>3.9380000000000002</v>
       </c>
       <c r="P41">
-        <v>3.6859999999999999</v>
+        <v>3.3959999999999999</v>
       </c>
       <c r="Q41">
-        <v>10.39</v>
+        <v>13.666</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.2">
@@ -45016,10 +44920,10 @@
         <v>36</v>
       </c>
       <c r="B42" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="C42" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D42" t="s">
         <v>21</v>
@@ -45034,34 +44938,34 @@
         <v>0</v>
       </c>
       <c r="H42">
-        <v>5.8940000000000001</v>
+        <v>4.399</v>
       </c>
       <c r="I42">
-        <v>3.6829999999999998</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="J42">
-        <v>4.8840000000000003</v>
+        <v>3.4740000000000002</v>
       </c>
       <c r="K42">
-        <v>1.4139999999999999</v>
-      </c>
-      <c r="L42">
-        <v>1.1759999999999999</v>
+        <v>0.96699999999999997</v>
       </c>
       <c r="M42">
-        <v>2.5310000000000001</v>
+        <v>1.55</v>
       </c>
       <c r="N42">
-        <v>4.1109999999999998</v>
+        <v>4.1070000000000002</v>
       </c>
       <c r="O42">
-        <v>3.9990000000000001</v>
+        <v>3.1120000000000001</v>
       </c>
       <c r="P42">
-        <v>6.633</v>
+        <v>3.677</v>
       </c>
       <c r="Q42">
-        <v>10.686999999999999</v>
+        <v>12.242000000000001</v>
+      </c>
+      <c r="R42">
+        <v>888.29399999999998</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.2">
@@ -45069,13 +44973,13 @@
         <v>36</v>
       </c>
       <c r="B43" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="C43" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="D43" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -45084,40 +44988,37 @@
         <v>0</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>0.876</v>
       </c>
       <c r="H43">
-        <v>4.2770000000000001</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="I43">
-        <v>1.302</v>
+        <v>1.534</v>
       </c>
       <c r="J43">
-        <v>4.3499999999999996</v>
+        <v>3.1859999999999999</v>
       </c>
       <c r="K43">
-        <v>1.845</v>
+        <v>1.36</v>
       </c>
       <c r="L43">
-        <v>1.661</v>
+        <v>0.69699999999999995</v>
       </c>
       <c r="M43">
-        <v>2.7320000000000002</v>
+        <v>1.9990000000000001</v>
       </c>
       <c r="N43">
-        <v>3.9860000000000002</v>
+        <v>3.3109999999999999</v>
       </c>
       <c r="O43">
-        <v>4.2279999999999998</v>
+        <v>3.847</v>
       </c>
       <c r="P43">
-        <v>4.4640000000000004</v>
+        <v>5.7759999999999998</v>
       </c>
       <c r="Q43">
-        <v>5.7110000000000003</v>
-      </c>
-      <c r="R43">
-        <v>478.97</v>
+        <v>15.307</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.2">
@@ -45125,10 +45026,10 @@
         <v>36</v>
       </c>
       <c r="B44" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="C44" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="D44" t="s">
         <v>21</v>
@@ -45139,38 +45040,35 @@
       <c r="F44">
         <v>0</v>
       </c>
-      <c r="G44">
-        <v>0</v>
-      </c>
       <c r="H44">
-        <v>5.585</v>
+        <v>4.4720000000000004</v>
       </c>
       <c r="I44">
-        <v>3.0939999999999999</v>
+        <v>1.077</v>
       </c>
       <c r="J44">
-        <v>4.077</v>
+        <v>2.649</v>
       </c>
       <c r="K44">
-        <v>1.2949999999999999</v>
+        <v>1.0960000000000001</v>
       </c>
       <c r="L44">
-        <v>1.0469999999999999</v>
+        <v>1.0669999999999999</v>
       </c>
       <c r="M44">
-        <v>2.2200000000000002</v>
+        <v>2.5329999999999999</v>
       </c>
       <c r="N44">
-        <v>3.7810000000000001</v>
+        <v>5.45</v>
       </c>
       <c r="O44">
-        <v>4.6390000000000002</v>
+        <v>5.4210000000000003</v>
       </c>
       <c r="P44">
-        <v>6.68</v>
+        <v>4.359</v>
       </c>
       <c r="Q44">
-        <v>8.9480000000000004</v>
+        <v>18.315000000000001</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.2">
@@ -45178,10 +45076,10 @@
         <v>36</v>
       </c>
       <c r="B45" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="C45" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="D45" t="s">
         <v>21</v>
@@ -45196,34 +45094,37 @@
         <v>0</v>
       </c>
       <c r="H45">
-        <v>6.8769999999999998</v>
+        <v>4.57</v>
       </c>
       <c r="I45">
-        <v>3.18</v>
+        <v>1.234</v>
       </c>
       <c r="J45">
-        <v>4.5990000000000002</v>
+        <v>3.234</v>
       </c>
       <c r="K45">
-        <v>2.3090000000000002</v>
+        <v>1.3959999999999999</v>
       </c>
       <c r="L45">
-        <v>1.663</v>
+        <v>1.35</v>
       </c>
       <c r="M45">
-        <v>1.492</v>
+        <v>2.5760000000000001</v>
       </c>
       <c r="N45">
-        <v>3.7959999999999998</v>
+        <v>3.11</v>
       </c>
       <c r="O45">
-        <v>2.391</v>
+        <v>2.7229999999999999</v>
       </c>
       <c r="P45">
-        <v>5.4109999999999996</v>
+        <v>4.8949999999999996</v>
       </c>
       <c r="Q45">
-        <v>7.7619999999999996</v>
+        <v>18.914000000000001</v>
+      </c>
+      <c r="R45">
+        <v>743.88400000000001</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.2">
@@ -45231,10 +45132,10 @@
         <v>36</v>
       </c>
       <c r="B46" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C46" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D46" t="s">
         <v>21</v>
@@ -45246,37 +45147,13 @@
         <v>0</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="H46">
-        <v>6.93</v>
+        <v>4.5819999999999999</v>
       </c>
       <c r="I46">
-        <v>2.923</v>
-      </c>
-      <c r="J46">
-        <v>3.7719999999999998</v>
-      </c>
-      <c r="K46">
-        <v>1.583</v>
-      </c>
-      <c r="L46">
-        <v>1.4259999999999999</v>
-      </c>
-      <c r="M46">
-        <v>1.522</v>
-      </c>
-      <c r="N46">
-        <v>3.3820000000000001</v>
-      </c>
-      <c r="P46">
-        <v>4.6139999999999999</v>
-      </c>
-      <c r="Q46">
-        <v>9.5039999999999996</v>
-      </c>
-      <c r="R46">
-        <v>586.10400000000004</v>
+        <v>1.518</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.2">
@@ -45284,10 +45161,10 @@
         <v>36</v>
       </c>
       <c r="B47" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C47" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D47" t="s">
         <v>21</v>
@@ -45302,37 +45179,31 @@
         <v>0</v>
       </c>
       <c r="H47">
-        <v>3.641</v>
+        <v>4.6029999999999998</v>
       </c>
       <c r="I47">
-        <v>1.4630000000000001</v>
+        <v>2.2570000000000001</v>
       </c>
       <c r="J47">
-        <v>4.1130000000000004</v>
+        <v>4.4729999999999999</v>
       </c>
       <c r="K47">
-        <v>1.079</v>
+        <v>1.76</v>
       </c>
       <c r="L47">
-        <v>0.83699999999999997</v>
+        <v>1.694</v>
       </c>
       <c r="M47">
-        <v>2.4260000000000002</v>
+        <v>2.0950000000000002</v>
       </c>
       <c r="N47">
-        <v>3.5110000000000001</v>
-      </c>
-      <c r="O47">
-        <v>5.2480000000000002</v>
+        <v>2.661</v>
       </c>
       <c r="P47">
-        <v>5.5609999999999999</v>
+        <v>4.63</v>
       </c>
       <c r="Q47">
-        <v>11.414999999999999</v>
-      </c>
-      <c r="R47">
-        <v>621.04100000000005</v>
+        <v>15.507</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.2">
@@ -45340,10 +45211,10 @@
         <v>36</v>
       </c>
       <c r="B48" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="C48" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="D48" t="s">
         <v>21</v>
@@ -45355,37 +45226,40 @@
         <v>0</v>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>0.83699999999999997</v>
       </c>
       <c r="H48">
-        <v>5.4320000000000004</v>
+        <v>4.6070000000000002</v>
       </c>
       <c r="I48">
-        <v>2.6629999999999998</v>
+        <v>1.7330000000000001</v>
       </c>
       <c r="J48">
-        <v>4.2549999999999999</v>
+        <v>3.5350000000000001</v>
       </c>
       <c r="K48">
-        <v>1.585</v>
+        <v>0.90900000000000003</v>
       </c>
       <c r="L48">
-        <v>1.2509999999999999</v>
+        <v>0.74099999999999999</v>
       </c>
       <c r="M48">
-        <v>2.6589999999999998</v>
+        <v>2.0819999999999999</v>
       </c>
       <c r="N48">
-        <v>5.5010000000000003</v>
+        <v>3.6040000000000001</v>
       </c>
       <c r="O48">
-        <v>4.7329999999999997</v>
-      </c>
-      <c r="P48" t="s">
-        <v>62</v>
+        <v>3.7440000000000002</v>
+      </c>
+      <c r="P48">
+        <v>4.18</v>
       </c>
       <c r="Q48">
-        <v>11.282</v>
+        <v>27.602</v>
+      </c>
+      <c r="R48">
+        <v>742.31299999999999</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.2">
@@ -45393,13 +45267,13 @@
         <v>36</v>
       </c>
       <c r="B49" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="C49" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="D49" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -45408,31 +45282,37 @@
         <v>0</v>
       </c>
       <c r="G49">
-        <v>0</v>
+        <v>0.63100000000000001</v>
+      </c>
+      <c r="H49">
+        <v>4.7249999999999996</v>
+      </c>
+      <c r="I49">
+        <v>1.595</v>
       </c>
       <c r="J49">
-        <v>3.9609999999999999</v>
+        <v>2.923</v>
       </c>
       <c r="K49">
-        <v>1.6419999999999999</v>
+        <v>0.93400000000000005</v>
       </c>
       <c r="L49">
-        <v>0.91900000000000004</v>
+        <v>0.79600000000000004</v>
       </c>
       <c r="M49">
-        <v>1.96</v>
+        <v>3.2309999999999999</v>
       </c>
       <c r="N49">
-        <v>4.0129999999999999</v>
+        <v>2.99</v>
       </c>
       <c r="O49">
-        <v>3.552</v>
+        <v>4.133</v>
       </c>
       <c r="P49">
-        <v>3.0619999999999998</v>
+        <v>5.6740000000000004</v>
       </c>
       <c r="Q49">
-        <v>10.647</v>
+        <v>17.510000000000002</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.2">
@@ -45440,10 +45320,10 @@
         <v>36</v>
       </c>
       <c r="B50" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C50" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="D50" t="s">
         <v>21</v>
@@ -45455,34 +45335,37 @@
         <v>0</v>
       </c>
       <c r="G50">
-        <v>0</v>
+        <v>1.2829999999999999</v>
       </c>
       <c r="H50">
-        <v>4.1059999999999999</v>
+        <v>4.7300000000000004</v>
       </c>
       <c r="I50">
-        <v>1.405</v>
+        <v>1.123</v>
       </c>
       <c r="J50">
-        <v>3.4169999999999998</v>
+        <v>3.7770000000000001</v>
+      </c>
+      <c r="K50">
+        <v>1.1639999999999999</v>
+      </c>
+      <c r="L50">
+        <v>1.0840000000000001</v>
       </c>
       <c r="M50">
-        <v>2.952</v>
+        <v>3.3540000000000001</v>
       </c>
       <c r="N50">
-        <v>3.8130000000000002</v>
+        <v>4.4909999999999997</v>
       </c>
       <c r="O50">
-        <v>3.5009999999999999</v>
+        <v>5.3280000000000003</v>
       </c>
       <c r="P50">
-        <v>3.41</v>
+        <v>4.7939999999999996</v>
       </c>
       <c r="Q50">
-        <v>13.284000000000001</v>
-      </c>
-      <c r="R50">
-        <v>702.21600000000001</v>
+        <v>15.36</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.2">
@@ -45490,13 +45373,13 @@
         <v>36</v>
       </c>
       <c r="B51" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="C51" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="D51" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -45508,10 +45391,37 @@
         <v>0</v>
       </c>
       <c r="H51">
-        <v>5.2519999999999998</v>
+        <v>4.7510000000000003</v>
       </c>
       <c r="I51">
-        <v>2.3620000000000001</v>
+        <v>2.75</v>
+      </c>
+      <c r="J51">
+        <v>3.91</v>
+      </c>
+      <c r="K51">
+        <v>1.109</v>
+      </c>
+      <c r="L51">
+        <v>0.79400000000000004</v>
+      </c>
+      <c r="M51">
+        <v>2.3140000000000001</v>
+      </c>
+      <c r="N51">
+        <v>4.6900000000000004</v>
+      </c>
+      <c r="O51">
+        <v>4.609</v>
+      </c>
+      <c r="P51">
+        <v>6.7060000000000004</v>
+      </c>
+      <c r="Q51">
+        <v>18.245999999999999</v>
+      </c>
+      <c r="R51">
+        <v>590.99900000000002</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.2">
@@ -45519,13 +45429,13 @@
         <v>36</v>
       </c>
       <c r="B52" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="C52" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="D52" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -45534,13 +45444,40 @@
         <v>0</v>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>1.4550000000000001</v>
       </c>
       <c r="H52">
-        <v>3.008</v>
+        <v>4.7640000000000002</v>
       </c>
       <c r="I52">
-        <v>1.0529999999999999</v>
+        <v>1.0820000000000001</v>
+      </c>
+      <c r="J52">
+        <v>3.6880000000000002</v>
+      </c>
+      <c r="K52">
+        <v>1.0429999999999999</v>
+      </c>
+      <c r="L52">
+        <v>0.68799999999999994</v>
+      </c>
+      <c r="M52">
+        <v>2.6859999999999999</v>
+      </c>
+      <c r="N52">
+        <v>4.4820000000000002</v>
+      </c>
+      <c r="O52">
+        <v>3.9249999999999998</v>
+      </c>
+      <c r="P52">
+        <v>2.3380000000000001</v>
+      </c>
+      <c r="Q52">
+        <v>6.633</v>
+      </c>
+      <c r="R52">
+        <v>438.92500000000001</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.2">
@@ -45548,7 +45485,7 @@
         <v>36</v>
       </c>
       <c r="B53" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C53" t="s">
         <v>50</v>
@@ -45562,41 +45499,35 @@
       <c r="F53">
         <v>0</v>
       </c>
-      <c r="G53">
-        <v>0</v>
-      </c>
       <c r="H53">
-        <v>7.4390000000000001</v>
+        <v>4.7770000000000001</v>
       </c>
       <c r="I53">
-        <v>3.4060000000000001</v>
+        <v>1.359</v>
       </c>
       <c r="J53">
-        <v>3.4870000000000001</v>
+        <v>3.01</v>
       </c>
       <c r="K53">
-        <v>1.0549999999999999</v>
+        <v>1.498</v>
       </c>
       <c r="L53">
-        <v>0.82099999999999995</v>
+        <v>1.264</v>
       </c>
       <c r="M53">
-        <v>2.1589999999999998</v>
+        <v>1.8620000000000001</v>
       </c>
       <c r="N53">
-        <v>4.069</v>
+        <v>3.8969999999999998</v>
       </c>
       <c r="O53">
-        <v>3.4689999999999999</v>
+        <v>2.8839999999999999</v>
       </c>
       <c r="P53">
-        <v>2.3660000000000001</v>
+        <v>3.8029999999999999</v>
       </c>
       <c r="Q53">
-        <v>23.082999999999998</v>
-      </c>
-      <c r="R53">
-        <v>401.69799999999998</v>
+        <v>14.914</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.2">
@@ -45604,13 +45535,10 @@
         <v>36</v>
       </c>
       <c r="B54" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="C54" t="s">
-        <v>50</v>
-      </c>
-      <c r="D54" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -45619,40 +45547,25 @@
         <v>0</v>
       </c>
       <c r="G54">
-        <v>0</v>
+        <v>0.34899999999999998</v>
       </c>
       <c r="H54">
-        <v>6.593</v>
+        <v>4.851</v>
       </c>
       <c r="I54">
-        <v>2.2210000000000001</v>
-      </c>
-      <c r="J54">
-        <v>2.7930000000000001</v>
-      </c>
-      <c r="K54">
-        <v>0.84</v>
-      </c>
-      <c r="L54">
-        <v>0.80400000000000005</v>
-      </c>
-      <c r="M54">
-        <v>2.4329999999999998</v>
+        <v>1.774</v>
       </c>
       <c r="N54">
-        <v>3.7709999999999999</v>
+        <v>3.9289999999999998</v>
       </c>
       <c r="O54">
-        <v>4.157</v>
+        <v>3.2690000000000001</v>
       </c>
       <c r="P54">
-        <v>2.6070000000000002</v>
+        <v>2.9089999999999998</v>
       </c>
       <c r="Q54">
-        <v>13.64</v>
-      </c>
-      <c r="R54">
-        <v>861.70899999999995</v>
+        <v>8.2349999999999994</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.2">
@@ -45660,10 +45573,10 @@
         <v>36</v>
       </c>
       <c r="B55" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="C55" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="D55" t="s">
         <v>21</v>
@@ -45675,40 +45588,40 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>0.58299999999999996</v>
       </c>
       <c r="H55">
-        <v>3.2069999999999999</v>
+        <v>4.8810000000000002</v>
       </c>
       <c r="I55">
-        <v>2.1389999999999998</v>
+        <v>1.1890000000000001</v>
       </c>
       <c r="J55">
-        <v>2.593</v>
+        <v>2.3919999999999999</v>
       </c>
       <c r="K55">
-        <v>0.99299999999999999</v>
+        <v>1.506</v>
       </c>
       <c r="L55">
-        <v>0.88600000000000001</v>
+        <v>0.79100000000000004</v>
       </c>
       <c r="M55">
-        <v>1.524</v>
+        <v>1.7250000000000001</v>
       </c>
       <c r="N55">
-        <v>4.5149999999999997</v>
+        <v>3.1339999999999999</v>
       </c>
       <c r="O55">
-        <v>3.548</v>
+        <v>3.6640000000000001</v>
       </c>
       <c r="P55">
-        <v>2.4</v>
+        <v>4.452</v>
       </c>
       <c r="Q55">
-        <v>12.63</v>
+        <v>11.879</v>
       </c>
       <c r="R55">
-        <v>847.38099999999997</v>
+        <v>834.19600000000003</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.2">
@@ -45716,13 +45629,10 @@
         <v>36</v>
       </c>
       <c r="B56" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C56" t="s">
-        <v>50</v>
-      </c>
-      <c r="D56" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -45733,29 +45643,35 @@
       <c r="G56">
         <v>0</v>
       </c>
+      <c r="H56">
+        <v>4.9320000000000004</v>
+      </c>
+      <c r="I56">
+        <v>1.4930000000000001</v>
+      </c>
       <c r="J56">
-        <v>3.7919999999999998</v>
+        <v>2.96</v>
       </c>
       <c r="K56">
-        <v>1.593</v>
+        <v>0.89800000000000002</v>
       </c>
       <c r="L56">
-        <v>1.3080000000000001</v>
+        <v>0.629</v>
       </c>
       <c r="M56">
-        <v>1.974</v>
+        <v>2.238</v>
       </c>
       <c r="N56">
-        <v>3.4209999999999998</v>
+        <v>4.2969999999999997</v>
       </c>
       <c r="O56">
-        <v>3.1120000000000001</v>
+        <v>3.327</v>
       </c>
       <c r="P56">
-        <v>3.6760000000000002</v>
+        <v>3.17</v>
       </c>
       <c r="Q56">
-        <v>11.606</v>
+        <v>12.349</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.2">
@@ -45763,7 +45679,7 @@
         <v>36</v>
       </c>
       <c r="B57" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="C57" t="s">
         <v>50</v>
@@ -45780,29 +45696,35 @@
       <c r="G57">
         <v>0</v>
       </c>
+      <c r="H57">
+        <v>4.9800000000000004</v>
+      </c>
+      <c r="I57">
+        <v>2.177</v>
+      </c>
       <c r="J57">
-        <v>3.01</v>
+        <v>3.722</v>
       </c>
       <c r="K57">
-        <v>0.72699999999999998</v>
+        <v>0.69699999999999995</v>
       </c>
       <c r="L57">
-        <v>0.71199999999999997</v>
+        <v>0.48199999999999998</v>
       </c>
       <c r="M57">
-        <v>2.492</v>
+        <v>2.5249999999999999</v>
       </c>
       <c r="N57">
-        <v>3.2549999999999999</v>
+        <v>4.5990000000000002</v>
       </c>
       <c r="O57">
-        <v>4.6130000000000004</v>
+        <v>4.1239999999999997</v>
       </c>
       <c r="P57">
-        <v>2.681</v>
+        <v>3.1230000000000002</v>
       </c>
       <c r="Q57">
-        <v>11.928000000000001</v>
+        <v>20.695</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.2">
@@ -45810,13 +45732,10 @@
         <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="C58" t="s">
-        <v>50</v>
-      </c>
-      <c r="D58" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -45827,32 +45746,38 @@
       <c r="G58">
         <v>0</v>
       </c>
+      <c r="H58">
+        <v>5</v>
+      </c>
+      <c r="I58">
+        <v>1.25</v>
+      </c>
       <c r="J58">
-        <v>2.992</v>
+        <v>2.6709999999999998</v>
       </c>
       <c r="K58">
-        <v>1.375</v>
+        <v>1.18</v>
       </c>
       <c r="L58">
-        <v>1.1919999999999999</v>
+        <v>1.0189999999999999</v>
       </c>
       <c r="M58">
-        <v>1.43</v>
+        <v>1.74</v>
       </c>
       <c r="N58">
-        <v>2.8820000000000001</v>
+        <v>3.6619999999999999</v>
       </c>
       <c r="O58">
-        <v>5.83</v>
+        <v>3.5590000000000002</v>
       </c>
       <c r="P58">
-        <v>4.1589999999999998</v>
+        <v>4.5869999999999997</v>
       </c>
       <c r="Q58">
-        <v>12.566000000000001</v>
+        <v>16.036999999999999</v>
       </c>
       <c r="R58">
-        <v>870.55700000000002</v>
+        <v>781.36699999999996</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.2">
@@ -45860,10 +45785,10 @@
         <v>36</v>
       </c>
       <c r="B59" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="C59" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D59" t="s">
         <v>21</v>
@@ -45875,13 +45800,40 @@
         <v>0</v>
       </c>
       <c r="G59">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="H59">
-        <v>4.5819999999999999</v>
+        <v>5.1239999999999997</v>
       </c>
       <c r="I59">
-        <v>1.518</v>
+        <v>1.2569999999999999</v>
+      </c>
+      <c r="J59">
+        <v>3.3929999999999998</v>
+      </c>
+      <c r="K59">
+        <v>1.081</v>
+      </c>
+      <c r="L59">
+        <v>1.0720000000000001</v>
+      </c>
+      <c r="M59">
+        <v>1.387</v>
+      </c>
+      <c r="N59">
+        <v>3.7989999999999999</v>
+      </c>
+      <c r="O59">
+        <v>3.3069999999999999</v>
+      </c>
+      <c r="P59">
+        <v>9.4019999999999992</v>
+      </c>
+      <c r="Q59">
+        <v>19.684000000000001</v>
+      </c>
+      <c r="R59">
+        <v>880.28499999999997</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.2">
@@ -45889,13 +45841,13 @@
         <v>36</v>
       </c>
       <c r="B60" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C60" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="D60" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -45904,13 +45856,40 @@
         <v>0</v>
       </c>
       <c r="G60">
-        <v>0.93899999999999995</v>
+        <v>1</v>
       </c>
       <c r="H60">
-        <v>3.823</v>
+        <v>5.1349999999999998</v>
       </c>
       <c r="I60">
-        <v>1.5740000000000001</v>
+        <v>1.6970000000000001</v>
+      </c>
+      <c r="J60">
+        <v>4.1840000000000002</v>
+      </c>
+      <c r="K60">
+        <v>1.1319999999999999</v>
+      </c>
+      <c r="L60">
+        <v>0.62</v>
+      </c>
+      <c r="M60">
+        <v>3.26</v>
+      </c>
+      <c r="N60">
+        <v>3.5710000000000002</v>
+      </c>
+      <c r="O60">
+        <v>4.1029999999999998</v>
+      </c>
+      <c r="P60">
+        <v>5.6920000000000002</v>
+      </c>
+      <c r="Q60">
+        <v>50.863</v>
+      </c>
+      <c r="R60">
+        <v>652.10299999999995</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.2">
@@ -45918,10 +45897,10 @@
         <v>36</v>
       </c>
       <c r="B61" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="C61" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D61" t="s">
         <v>21</v>
@@ -45933,13 +45912,37 @@
         <v>0</v>
       </c>
       <c r="G61">
-        <v>0.749</v>
+        <v>0</v>
       </c>
       <c r="H61">
-        <v>5.2590000000000003</v>
+        <v>5.1769999999999996</v>
       </c>
       <c r="I61">
-        <v>1.782</v>
+        <v>1.6259999999999999</v>
+      </c>
+      <c r="J61">
+        <v>4.0190000000000001</v>
+      </c>
+      <c r="K61">
+        <v>1.532</v>
+      </c>
+      <c r="L61">
+        <v>1.339</v>
+      </c>
+      <c r="M61">
+        <v>1.488</v>
+      </c>
+      <c r="N61">
+        <v>4.702</v>
+      </c>
+      <c r="O61">
+        <v>3.8580000000000001</v>
+      </c>
+      <c r="P61">
+        <v>6.7830000000000004</v>
+      </c>
+      <c r="Q61">
+        <v>33.136000000000003</v>
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.2">
@@ -45947,10 +45950,10 @@
         <v>36</v>
       </c>
       <c r="B62" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="C62" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D62" t="s">
         <v>21</v>
@@ -45961,35 +45964,20 @@
       <c r="F62">
         <v>0</v>
       </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
       <c r="H62">
-        <v>5.3470000000000004</v>
+        <v>5.2009999999999996</v>
       </c>
       <c r="I62">
-        <v>1.5469999999999999</v>
-      </c>
-      <c r="J62">
-        <v>3.024</v>
-      </c>
-      <c r="K62">
-        <v>1.0860000000000001</v>
-      </c>
-      <c r="L62">
-        <v>1.085</v>
-      </c>
-      <c r="M62">
-        <v>2.3769999999999998</v>
-      </c>
-      <c r="N62">
-        <v>3.456</v>
-      </c>
-      <c r="O62">
-        <v>2.6669999999999998</v>
+        <v>2.6779999999999999</v>
       </c>
       <c r="P62">
-        <v>2.222</v>
+        <v>12.923</v>
       </c>
       <c r="Q62">
-        <v>19.102</v>
+        <v>18.338000000000001</v>
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.2">
@@ -45997,13 +45985,13 @@
         <v>36</v>
       </c>
       <c r="B63" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C63" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D63" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -46011,35 +45999,14 @@
       <c r="F63">
         <v>0</v>
       </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
       <c r="H63">
-        <v>4.7770000000000001</v>
+        <v>5.2519999999999998</v>
       </c>
       <c r="I63">
-        <v>1.359</v>
-      </c>
-      <c r="J63">
-        <v>3.01</v>
-      </c>
-      <c r="K63">
-        <v>1.498</v>
-      </c>
-      <c r="L63">
-        <v>1.264</v>
-      </c>
-      <c r="M63">
-        <v>1.8620000000000001</v>
-      </c>
-      <c r="N63">
-        <v>3.8969999999999998</v>
-      </c>
-      <c r="O63">
-        <v>2.8839999999999999</v>
-      </c>
-      <c r="P63">
-        <v>3.8029999999999999</v>
-      </c>
-      <c r="Q63">
-        <v>14.914</v>
+        <v>2.3620000000000001</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.2">
@@ -46047,7 +46014,7 @@
         <v>36</v>
       </c>
       <c r="B64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C64" t="s">
         <v>50</v>
@@ -46061,35 +46028,14 @@
       <c r="F64">
         <v>0</v>
       </c>
+      <c r="G64">
+        <v>0.749</v>
+      </c>
       <c r="H64">
-        <v>5.6420000000000003</v>
+        <v>5.2590000000000003</v>
       </c>
       <c r="I64">
-        <v>1.256</v>
-      </c>
-      <c r="J64">
-        <v>3.7490000000000001</v>
-      </c>
-      <c r="K64">
-        <v>0.92</v>
-      </c>
-      <c r="L64">
-        <v>0.65400000000000003</v>
-      </c>
-      <c r="M64">
-        <v>2.8050000000000002</v>
-      </c>
-      <c r="N64">
-        <v>3.6920000000000002</v>
-      </c>
-      <c r="O64">
-        <v>2.85</v>
-      </c>
-      <c r="P64">
-        <v>2.2989999999999999</v>
-      </c>
-      <c r="Q64">
-        <v>12.202</v>
+        <v>1.782</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.2">
@@ -46097,10 +46043,10 @@
         <v>36</v>
       </c>
       <c r="B65" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C65" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D65" t="s">
         <v>21</v>
@@ -46115,37 +46061,34 @@
         <v>0</v>
       </c>
       <c r="H65">
-        <v>7.867</v>
+        <v>5.3140000000000001</v>
       </c>
       <c r="I65">
-        <v>3.2109999999999999</v>
+        <v>1.2010000000000001</v>
       </c>
       <c r="J65">
-        <v>3.8620000000000001</v>
+        <v>4.7789999999999999</v>
       </c>
       <c r="K65">
-        <v>1.2170000000000001</v>
+        <v>1.5549999999999999</v>
       </c>
       <c r="L65">
-        <v>0.751</v>
+        <v>1.016</v>
       </c>
       <c r="M65">
-        <v>2.831</v>
+        <v>4.2089999999999996</v>
       </c>
       <c r="N65">
-        <v>4.8099999999999996</v>
+        <v>2.75</v>
       </c>
       <c r="O65">
-        <v>4.2679999999999998</v>
+        <v>3.077</v>
       </c>
       <c r="P65">
-        <v>2.9119999999999999</v>
+        <v>4.952</v>
       </c>
       <c r="Q65">
-        <v>12.845000000000001</v>
-      </c>
-      <c r="R65">
-        <v>926.26900000000001</v>
+        <v>71.221999999999994</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.2">
@@ -46153,7 +46096,7 @@
         <v>36</v>
       </c>
       <c r="B66" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C66" t="s">
         <v>52</v>
@@ -46171,34 +46114,34 @@
         <v>0</v>
       </c>
       <c r="H66">
-        <v>6.2889999999999997</v>
+        <v>5.3170000000000002</v>
       </c>
       <c r="I66">
-        <v>1.919</v>
+        <v>2.7909999999999999</v>
       </c>
       <c r="J66">
-        <v>4.306</v>
+        <v>3.0459999999999998</v>
       </c>
       <c r="K66">
-        <v>1.889</v>
+        <v>1.516</v>
       </c>
       <c r="L66">
-        <v>1.847</v>
+        <v>1.2829999999999999</v>
       </c>
       <c r="M66">
-        <v>2.6240000000000001</v>
+        <v>1.8460000000000001</v>
       </c>
       <c r="N66">
-        <v>3.9119999999999999</v>
+        <v>3.4910000000000001</v>
       </c>
       <c r="O66">
-        <v>3.8759999999999999</v>
+        <v>2.6539999999999999</v>
       </c>
       <c r="P66">
-        <v>3.2480000000000002</v>
+        <v>4.1159999999999997</v>
       </c>
       <c r="Q66">
-        <v>13.007</v>
+        <v>18.538</v>
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.2">
@@ -46206,10 +46149,10 @@
         <v>36</v>
       </c>
       <c r="B67" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C67" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D67" t="s">
         <v>21</v>
@@ -46220,26 +46163,35 @@
       <c r="F67">
         <v>0</v>
       </c>
-      <c r="G67">
-        <v>0</v>
-      </c>
       <c r="H67">
-        <v>6.2880000000000003</v>
+        <v>5.3470000000000004</v>
       </c>
       <c r="I67">
-        <v>1.4670000000000001</v>
+        <v>1.5469999999999999</v>
+      </c>
+      <c r="J67">
+        <v>3.024</v>
+      </c>
+      <c r="K67">
+        <v>1.0860000000000001</v>
+      </c>
+      <c r="L67">
+        <v>1.085</v>
+      </c>
+      <c r="M67">
+        <v>2.3769999999999998</v>
       </c>
       <c r="N67">
-        <v>4.6120000000000001</v>
+        <v>3.456</v>
       </c>
       <c r="O67">
-        <v>4.6180000000000003</v>
+        <v>2.6669999999999998</v>
       </c>
       <c r="P67">
-        <v>3.7229999999999999</v>
+        <v>2.222</v>
       </c>
       <c r="Q67">
-        <v>12.891999999999999</v>
+        <v>19.102</v>
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.2">
@@ -46247,10 +46199,10 @@
         <v>36</v>
       </c>
       <c r="B68" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C68" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D68" t="s">
         <v>21</v>
@@ -46265,34 +46217,34 @@
         <v>0</v>
       </c>
       <c r="H68">
-        <v>5.3170000000000002</v>
+        <v>5.4320000000000004</v>
       </c>
       <c r="I68">
-        <v>2.7909999999999999</v>
+        <v>2.6629999999999998</v>
       </c>
       <c r="J68">
-        <v>3.0459999999999998</v>
+        <v>4.2549999999999999</v>
       </c>
       <c r="K68">
-        <v>1.516</v>
+        <v>1.585</v>
       </c>
       <c r="L68">
-        <v>1.2829999999999999</v>
+        <v>1.2509999999999999</v>
       </c>
       <c r="M68">
-        <v>1.8460000000000001</v>
+        <v>2.6589999999999998</v>
       </c>
       <c r="N68">
-        <v>3.4910000000000001</v>
+        <v>5.5010000000000003</v>
       </c>
       <c r="O68">
-        <v>2.6539999999999999</v>
-      </c>
-      <c r="P68">
-        <v>4.1159999999999997</v>
+        <v>4.7329999999999997</v>
+      </c>
+      <c r="P68" t="s">
+        <v>62</v>
       </c>
       <c r="Q68">
-        <v>18.538</v>
+        <v>11.282</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.2">
@@ -46300,13 +46252,13 @@
         <v>36</v>
       </c>
       <c r="B69" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="C69" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D69" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -46318,28 +46270,37 @@
         <v>0</v>
       </c>
       <c r="H69">
-        <v>6.3490000000000002</v>
+        <v>5.4550000000000001</v>
       </c>
       <c r="I69">
-        <v>2.504</v>
+        <v>2.1739999999999999</v>
       </c>
       <c r="J69">
-        <v>3.2469999999999999</v>
+        <v>3.8220000000000001</v>
+      </c>
+      <c r="K69">
+        <v>0.69399999999999995</v>
+      </c>
+      <c r="L69">
+        <v>0.57299999999999995</v>
       </c>
       <c r="M69">
-        <v>2.3130000000000002</v>
+        <v>2.645</v>
       </c>
       <c r="N69">
-        <v>2.996</v>
+        <v>4.75</v>
       </c>
       <c r="O69">
-        <v>2.6240000000000001</v>
+        <v>5.24</v>
       </c>
       <c r="P69">
-        <v>5.5460000000000003</v>
+        <v>2.4159999999999999</v>
       </c>
       <c r="Q69">
-        <v>17.846</v>
+        <v>16.420999999999999</v>
+      </c>
+      <c r="R69">
+        <v>713.46799999999996</v>
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.2">
@@ -46347,10 +46308,10 @@
         <v>36</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="C70" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D70" t="s">
         <v>21</v>
@@ -46365,31 +46326,37 @@
         <v>0</v>
       </c>
       <c r="H70">
-        <v>4.6029999999999998</v>
+        <v>5.524</v>
       </c>
       <c r="I70">
-        <v>2.2570000000000001</v>
+        <v>2.5750000000000002</v>
       </c>
       <c r="J70">
-        <v>4.4729999999999999</v>
+        <v>3.411</v>
       </c>
       <c r="K70">
-        <v>1.76</v>
+        <v>0.42299999999999999</v>
       </c>
       <c r="L70">
-        <v>1.694</v>
+        <v>0.38600000000000001</v>
       </c>
       <c r="M70">
-        <v>2.0950000000000002</v>
+        <v>2.605</v>
       </c>
       <c r="N70">
-        <v>2.661</v>
+        <v>2.6850000000000001</v>
+      </c>
+      <c r="O70">
+        <v>2.1269999999999998</v>
       </c>
       <c r="P70">
-        <v>4.63</v>
+        <v>5.625</v>
       </c>
       <c r="Q70">
-        <v>15.507</v>
+        <v>13.702999999999999</v>
+      </c>
+      <c r="R70">
+        <v>662.31899999999996</v>
       </c>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.2">
@@ -46397,10 +46364,10 @@
         <v>36</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="C71" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D71" t="s">
         <v>21</v>
@@ -46415,34 +46382,34 @@
         <v>0</v>
       </c>
       <c r="H71">
-        <v>4.399</v>
+        <v>5.5259999999999998</v>
       </c>
       <c r="I71">
-        <v>0.92500000000000004</v>
+        <v>1.3160000000000001</v>
       </c>
       <c r="J71">
-        <v>3.4740000000000002</v>
+        <v>3.0379999999999998</v>
       </c>
       <c r="K71">
-        <v>0.96699999999999997</v>
+        <v>1.587</v>
+      </c>
+      <c r="L71">
+        <v>1.544</v>
       </c>
       <c r="M71">
-        <v>1.55</v>
+        <v>1.9450000000000001</v>
       </c>
       <c r="N71">
-        <v>4.1070000000000002</v>
+        <v>4.0869999999999997</v>
       </c>
       <c r="O71">
-        <v>3.1120000000000001</v>
+        <v>3.5339999999999998</v>
       </c>
       <c r="P71">
-        <v>3.677</v>
+        <v>6.1219999999999999</v>
       </c>
       <c r="Q71">
-        <v>12.242000000000001</v>
-      </c>
-      <c r="R71">
-        <v>888.29399999999998</v>
+        <v>26.518999999999998</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.2">
@@ -46450,7 +46417,7 @@
         <v>36</v>
       </c>
       <c r="B72" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C72" t="s">
         <v>50</v>
@@ -46465,31 +46432,40 @@
         <v>0</v>
       </c>
       <c r="G72">
-        <v>0</v>
+        <v>0.56899999999999995</v>
+      </c>
+      <c r="H72">
+        <v>5.5659999999999998</v>
+      </c>
+      <c r="I72">
+        <v>1.1839999999999999</v>
       </c>
       <c r="J72">
-        <v>3.802</v>
+        <v>4.5030000000000001</v>
       </c>
       <c r="K72">
-        <v>1.173</v>
+        <v>0.88500000000000001</v>
       </c>
       <c r="L72">
-        <v>0.86899999999999999</v>
+        <v>0.77700000000000002</v>
       </c>
       <c r="M72">
-        <v>2.4039999999999999</v>
+        <v>2.0579999999999998</v>
       </c>
       <c r="N72">
-        <v>3.028</v>
+        <v>2.5920000000000001</v>
       </c>
       <c r="O72">
-        <v>3.0329999999999999</v>
+        <v>3.335</v>
       </c>
       <c r="P72">
-        <v>5.3360000000000003</v>
+        <v>4.532</v>
       </c>
       <c r="Q72">
-        <v>10.022</v>
+        <v>18.622</v>
+      </c>
+      <c r="R72">
+        <v>617.37099999999998</v>
       </c>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.2">
@@ -46497,10 +46473,13 @@
         <v>36</v>
       </c>
       <c r="B73" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C73" t="s">
-        <v>50</v>
+        <v>60</v>
+      </c>
+      <c r="D73" t="s">
+        <v>21</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -46511,29 +46490,35 @@
       <c r="G73">
         <v>0</v>
       </c>
+      <c r="H73">
+        <v>5.585</v>
+      </c>
+      <c r="I73">
+        <v>3.0939999999999999</v>
+      </c>
       <c r="J73">
-        <v>3.2559999999999998</v>
+        <v>4.077</v>
       </c>
       <c r="K73">
-        <v>0.80600000000000005</v>
+        <v>1.2949999999999999</v>
       </c>
       <c r="L73">
-        <v>0.69599999999999995</v>
+        <v>1.0469999999999999</v>
       </c>
       <c r="M73">
-        <v>2.5329999999999999</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="N73">
-        <v>2.5529999999999999</v>
+        <v>3.7810000000000001</v>
       </c>
       <c r="O73">
-        <v>3.9359999999999999</v>
+        <v>4.6390000000000002</v>
       </c>
       <c r="P73">
-        <v>3.9750000000000001</v>
+        <v>6.68</v>
       </c>
       <c r="Q73">
-        <v>16.29</v>
+        <v>8.9480000000000004</v>
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.2">
@@ -46541,13 +46526,13 @@
         <v>36</v>
       </c>
       <c r="B74" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="C74" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="D74" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -46559,34 +46544,37 @@
         <v>0</v>
       </c>
       <c r="H74">
-        <v>3.1880000000000002</v>
+        <v>5.5949999999999998</v>
       </c>
       <c r="I74">
-        <v>1.218</v>
+        <v>1.5229999999999999</v>
       </c>
       <c r="J74">
-        <v>2.6240000000000001</v>
+        <v>3.6030000000000002</v>
       </c>
       <c r="K74">
-        <v>0.86899999999999999</v>
+        <v>1.907</v>
       </c>
       <c r="L74">
-        <v>0.61299999999999999</v>
+        <v>1.905</v>
       </c>
       <c r="M74">
-        <v>1.5960000000000001</v>
+        <v>1.454</v>
       </c>
       <c r="N74">
-        <v>3.83</v>
+        <v>3.7080000000000002</v>
+      </c>
+      <c r="O74">
+        <v>3.4489999999999998</v>
       </c>
       <c r="P74">
-        <v>5.9210000000000003</v>
+        <v>2.1989999999999998</v>
       </c>
       <c r="Q74">
-        <v>27.062000000000001</v>
+        <v>26.12</v>
       </c>
       <c r="R74">
-        <v>1012.704</v>
+        <v>792.803</v>
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.2">
@@ -46647,13 +46635,13 @@
         <v>36</v>
       </c>
       <c r="B76" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C76" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D76" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -46665,34 +46653,37 @@
         <v>0</v>
       </c>
       <c r="H76">
-        <v>3.5129999999999999</v>
+        <v>5.6310000000000002</v>
       </c>
       <c r="I76">
-        <v>1.2450000000000001</v>
+        <v>1.4730000000000001</v>
       </c>
       <c r="J76">
-        <v>4.032</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="K76">
-        <v>0.75900000000000001</v>
+        <v>1.6060000000000001</v>
       </c>
       <c r="L76">
-        <v>0.53100000000000003</v>
+        <v>1.2270000000000001</v>
       </c>
       <c r="M76">
-        <v>2.8079999999999998</v>
+        <v>2.109</v>
       </c>
       <c r="N76">
-        <v>4.5330000000000004</v>
+        <v>3.6040000000000001</v>
       </c>
       <c r="O76">
-        <v>1.8620000000000001</v>
+        <v>3.871</v>
       </c>
       <c r="P76">
-        <v>3.5960000000000001</v>
+        <v>8.1430000000000007</v>
       </c>
       <c r="Q76">
-        <v>32.378999999999998</v>
+        <v>61.502000000000002</v>
+      </c>
+      <c r="R76">
+        <v>665.44399999999996</v>
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.2">
@@ -46700,10 +46691,10 @@
         <v>36</v>
       </c>
       <c r="B77" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C77" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D77" t="s">
         <v>21</v>
@@ -46714,41 +46705,35 @@
       <c r="F77">
         <v>0</v>
       </c>
-      <c r="G77">
-        <v>0</v>
-      </c>
       <c r="H77">
-        <v>5.6749999999999998</v>
+        <v>5.6420000000000003</v>
       </c>
       <c r="I77">
-        <v>1.619</v>
+        <v>1.256</v>
       </c>
       <c r="J77">
-        <v>4.0570000000000004</v>
+        <v>3.7490000000000001</v>
       </c>
       <c r="K77">
-        <v>1.5489999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="L77">
-        <v>0.28899999999999998</v>
+        <v>0.65400000000000003</v>
       </c>
       <c r="M77">
-        <v>2.9409999999999998</v>
+        <v>2.8050000000000002</v>
       </c>
       <c r="N77">
-        <v>4.1539999999999999</v>
+        <v>3.6920000000000002</v>
       </c>
       <c r="O77">
-        <v>5.125</v>
+        <v>2.85</v>
       </c>
       <c r="P77">
-        <v>3.15</v>
+        <v>2.2989999999999999</v>
       </c>
       <c r="Q77">
-        <v>69.971000000000004</v>
-      </c>
-      <c r="R77">
-        <v>753.43100000000004</v>
+        <v>12.202</v>
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.2">
@@ -46774,34 +46759,37 @@
         <v>0</v>
       </c>
       <c r="H78">
-        <v>5.3140000000000001</v>
+        <v>5.6749999999999998</v>
       </c>
       <c r="I78">
-        <v>1.2010000000000001</v>
+        <v>1.619</v>
       </c>
       <c r="J78">
-        <v>4.7789999999999999</v>
+        <v>4.0570000000000004</v>
       </c>
       <c r="K78">
-        <v>1.5549999999999999</v>
+        <v>1.5489999999999999</v>
       </c>
       <c r="L78">
-        <v>1.016</v>
+        <v>0.28899999999999998</v>
       </c>
       <c r="M78">
-        <v>4.2089999999999996</v>
+        <v>2.9409999999999998</v>
       </c>
       <c r="N78">
-        <v>2.75</v>
+        <v>4.1539999999999999</v>
       </c>
       <c r="O78">
-        <v>3.077</v>
+        <v>5.125</v>
       </c>
       <c r="P78">
-        <v>4.952</v>
+        <v>3.15</v>
       </c>
       <c r="Q78">
-        <v>71.221999999999994</v>
+        <v>69.971000000000004</v>
+      </c>
+      <c r="R78">
+        <v>753.43100000000004</v>
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.2">
@@ -46809,13 +46797,13 @@
         <v>36</v>
       </c>
       <c r="B79" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="C79" t="s">
         <v>38</v>
       </c>
       <c r="D79" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -46826,29 +46814,35 @@
       <c r="G79">
         <v>0</v>
       </c>
+      <c r="H79">
+        <v>5.7770000000000001</v>
+      </c>
+      <c r="I79">
+        <v>1.194</v>
+      </c>
       <c r="J79">
-        <v>3.8380000000000001</v>
+        <v>3.0169999999999999</v>
       </c>
       <c r="K79">
-        <v>1.595</v>
+        <v>1.0089999999999999</v>
       </c>
       <c r="L79">
-        <v>0.75900000000000001</v>
+        <v>0.94899999999999995</v>
       </c>
       <c r="M79">
-        <v>3.3359999999999999</v>
+        <v>1.6970000000000001</v>
       </c>
       <c r="N79">
-        <v>3.61</v>
+        <v>3.375</v>
       </c>
       <c r="O79">
-        <v>4.2240000000000002</v>
+        <v>3.63</v>
       </c>
       <c r="P79">
-        <v>4.1660000000000004</v>
+        <v>8.7750000000000004</v>
       </c>
       <c r="Q79">
-        <v>56.527000000000001</v>
+        <v>26.954999999999998</v>
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.2">
@@ -46861,9 +46855,6 @@
       <c r="C80" t="s">
         <v>38</v>
       </c>
-      <c r="D80" t="s">
-        <v>24</v>
-      </c>
       <c r="E80">
         <v>0</v>
       </c>
@@ -46871,40 +46862,37 @@
         <v>0</v>
       </c>
       <c r="G80">
-        <v>1</v>
+        <v>0.92900000000000005</v>
       </c>
       <c r="H80">
-        <v>5.1349999999999998</v>
+        <v>5.8819999999999997</v>
       </c>
       <c r="I80">
-        <v>1.6970000000000001</v>
+        <v>1.601</v>
       </c>
       <c r="J80">
-        <v>4.1840000000000002</v>
+        <v>4.8280000000000003</v>
       </c>
       <c r="K80">
-        <v>1.1319999999999999</v>
+        <v>0.63200000000000001</v>
       </c>
       <c r="L80">
-        <v>0.62</v>
+        <v>0.53500000000000003</v>
       </c>
       <c r="M80">
-        <v>3.26</v>
+        <v>3.5960000000000001</v>
       </c>
       <c r="N80">
-        <v>3.5710000000000002</v>
+        <v>3.9</v>
       </c>
       <c r="O80">
-        <v>4.1029999999999998</v>
+        <v>3.9660000000000002</v>
       </c>
       <c r="P80">
-        <v>5.6920000000000002</v>
+        <v>3.9289999999999998</v>
       </c>
       <c r="Q80">
-        <v>50.863</v>
-      </c>
-      <c r="R80">
-        <v>652.10299999999995</v>
+        <v>36.975000000000001</v>
       </c>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.2">
@@ -46912,11 +46900,14 @@
         <v>36</v>
       </c>
       <c r="B81" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="C81" t="s">
         <v>38</v>
       </c>
+      <c r="D81" t="s">
+        <v>21</v>
+      </c>
       <c r="E81">
         <v>0</v>
       </c>
@@ -46924,37 +46915,37 @@
         <v>0</v>
       </c>
       <c r="G81">
-        <v>0.92900000000000005</v>
+        <v>0</v>
       </c>
       <c r="H81">
-        <v>5.8819999999999997</v>
+        <v>5.8940000000000001</v>
       </c>
       <c r="I81">
-        <v>1.601</v>
+        <v>3.6829999999999998</v>
       </c>
       <c r="J81">
-        <v>4.8280000000000003</v>
+        <v>4.8840000000000003</v>
       </c>
       <c r="K81">
-        <v>0.63200000000000001</v>
+        <v>1.4139999999999999</v>
       </c>
       <c r="L81">
-        <v>0.53500000000000003</v>
+        <v>1.1759999999999999</v>
       </c>
       <c r="M81">
-        <v>3.5960000000000001</v>
+        <v>2.5310000000000001</v>
       </c>
       <c r="N81">
-        <v>3.9</v>
+        <v>4.1109999999999998</v>
       </c>
       <c r="O81">
-        <v>3.9660000000000002</v>
+        <v>3.9990000000000001</v>
       </c>
       <c r="P81">
-        <v>3.9289999999999998</v>
+        <v>6.633</v>
       </c>
       <c r="Q81">
-        <v>36.975000000000001</v>
+        <v>10.686999999999999</v>
       </c>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.2">
@@ -46962,10 +46953,10 @@
         <v>36</v>
       </c>
       <c r="B82" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="C82" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -46974,31 +46965,37 @@
         <v>0</v>
       </c>
       <c r="G82">
-        <v>1.006</v>
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <v>5.944</v>
+      </c>
+      <c r="I82">
+        <v>1.613</v>
       </c>
       <c r="J82">
-        <v>4.0199999999999996</v>
+        <v>4.7300000000000004</v>
       </c>
       <c r="K82">
-        <v>0.83699999999999997</v>
+        <v>1.611</v>
       </c>
       <c r="L82">
-        <v>0.745</v>
+        <v>1.399</v>
       </c>
       <c r="M82">
-        <v>2.5339999999999998</v>
+        <v>2.806</v>
       </c>
       <c r="N82">
-        <v>3.5329999999999999</v>
+        <v>2.9449999999999998</v>
       </c>
       <c r="O82">
-        <v>3.5720000000000001</v>
+        <v>4.7119999999999997</v>
       </c>
       <c r="P82">
-        <v>4.8570000000000002</v>
+        <v>2.5110000000000001</v>
       </c>
       <c r="Q82">
-        <v>51.710999999999999</v>
+        <v>32.643000000000001</v>
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.2">
@@ -47006,10 +47003,10 @@
         <v>36</v>
       </c>
       <c r="B83" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C83" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D83" t="s">
         <v>21</v>
@@ -47021,40 +47018,34 @@
         <v>0</v>
       </c>
       <c r="G83">
-        <v>1.0880000000000001</v>
+        <v>0.63100000000000001</v>
       </c>
       <c r="H83">
-        <v>6.1139999999999999</v>
+        <v>6.0229999999999997</v>
       </c>
       <c r="I83">
-        <v>1.258</v>
+        <v>1.339</v>
       </c>
       <c r="J83">
-        <v>4.5960000000000001</v>
+        <v>3.6150000000000002</v>
       </c>
       <c r="K83">
-        <v>1.327</v>
+        <v>1.0609999999999999</v>
       </c>
       <c r="L83">
-        <v>0.81799999999999995</v>
+        <v>0.80800000000000005</v>
       </c>
       <c r="M83">
-        <v>3.524</v>
+        <v>2.0019999999999998</v>
       </c>
       <c r="N83">
-        <v>3.86</v>
-      </c>
-      <c r="O83">
-        <v>3.7</v>
+        <v>4.3280000000000003</v>
       </c>
       <c r="P83">
-        <v>7.3159999999999998</v>
+        <v>7.141</v>
       </c>
       <c r="Q83">
-        <v>24.658999999999999</v>
-      </c>
-      <c r="R83">
-        <v>322.12</v>
+        <v>21.399000000000001</v>
       </c>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.2">
@@ -47062,11 +47053,14 @@
         <v>36</v>
       </c>
       <c r="B84" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="C84" t="s">
         <v>38</v>
       </c>
+      <c r="D84" t="s">
+        <v>25</v>
+      </c>
       <c r="E84">
         <v>0</v>
       </c>
@@ -47074,40 +47068,40 @@
         <v>0</v>
       </c>
       <c r="G84">
-        <v>0.90200000000000002</v>
+        <v>0</v>
       </c>
       <c r="H84">
-        <v>3.9129999999999998</v>
+        <v>6.0350000000000001</v>
       </c>
       <c r="I84">
-        <v>0.92</v>
+        <v>2.7789999999999999</v>
       </c>
       <c r="J84">
-        <v>3.9039999999999999</v>
+        <v>4.1890000000000001</v>
       </c>
       <c r="K84">
-        <v>0.56299999999999994</v>
+        <v>1.5920000000000001</v>
       </c>
       <c r="L84">
-        <v>0.42099999999999999</v>
+        <v>1.351</v>
       </c>
       <c r="M84">
-        <v>2.57</v>
+        <v>1.91</v>
       </c>
       <c r="N84">
-        <v>4.8630000000000004</v>
+        <v>3.7</v>
       </c>
       <c r="O84">
-        <v>2.7770000000000001</v>
+        <v>5.5679999999999996</v>
       </c>
       <c r="P84">
-        <v>8.7370000000000001</v>
+        <v>5.8570000000000002</v>
       </c>
       <c r="Q84">
-        <v>22.951000000000001</v>
+        <v>23.795000000000002</v>
       </c>
       <c r="R84">
-        <v>238.65199999999999</v>
+        <v>745.75599999999997</v>
       </c>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.2">
@@ -47120,6 +47114,9 @@
       <c r="C85" t="s">
         <v>38</v>
       </c>
+      <c r="D85" t="s">
+        <v>21</v>
+      </c>
       <c r="E85">
         <v>0</v>
       </c>
@@ -47127,28 +47124,40 @@
         <v>0</v>
       </c>
       <c r="G85">
-        <v>0.85399999999999998</v>
+        <v>1.0880000000000001</v>
+      </c>
+      <c r="H85">
+        <v>6.1139999999999999</v>
+      </c>
+      <c r="I85">
+        <v>1.258</v>
       </c>
       <c r="J85">
-        <v>3.609</v>
+        <v>4.5960000000000001</v>
+      </c>
+      <c r="K85">
+        <v>1.327</v>
+      </c>
+      <c r="L85">
+        <v>0.81799999999999995</v>
       </c>
       <c r="M85">
-        <v>2.605</v>
+        <v>3.524</v>
       </c>
       <c r="N85">
-        <v>3.7519999999999998</v>
+        <v>3.86</v>
       </c>
       <c r="O85">
-        <v>2.8769999999999998</v>
+        <v>3.7</v>
       </c>
       <c r="P85">
-        <v>7.0609999999999999</v>
+        <v>7.3159999999999998</v>
       </c>
       <c r="Q85">
-        <v>23.41</v>
+        <v>24.658999999999999</v>
       </c>
       <c r="R85">
-        <v>322.73</v>
+        <v>322.12</v>
       </c>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.2">
@@ -47156,10 +47165,10 @@
         <v>36</v>
       </c>
       <c r="B86" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="C86" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D86" t="s">
         <v>21</v>
@@ -47171,40 +47180,40 @@
         <v>0</v>
       </c>
       <c r="G86">
-        <v>0.56899999999999995</v>
+        <v>0</v>
       </c>
       <c r="H86">
-        <v>5.5659999999999998</v>
+        <v>6.149</v>
       </c>
       <c r="I86">
-        <v>1.1839999999999999</v>
+        <v>1.6890000000000001</v>
       </c>
       <c r="J86">
-        <v>4.5030000000000001</v>
+        <v>3.9049999999999998</v>
       </c>
       <c r="K86">
-        <v>0.88500000000000001</v>
+        <v>0.99199999999999999</v>
       </c>
       <c r="L86">
-        <v>0.77700000000000002</v>
+        <v>0.92800000000000005</v>
       </c>
       <c r="M86">
-        <v>2.0579999999999998</v>
+        <v>1.841</v>
       </c>
       <c r="N86">
-        <v>2.5920000000000001</v>
+        <v>4.3620000000000001</v>
       </c>
       <c r="O86">
-        <v>3.335</v>
+        <v>3.1829999999999998</v>
       </c>
       <c r="P86">
-        <v>4.532</v>
+        <v>3.85</v>
       </c>
       <c r="Q86">
-        <v>18.622</v>
+        <v>36.018999999999998</v>
       </c>
       <c r="R86">
-        <v>617.37099999999998</v>
+        <v>732.04200000000003</v>
       </c>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.2">
@@ -47212,10 +47221,10 @@
         <v>36</v>
       </c>
       <c r="B87" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="C87" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D87" t="s">
         <v>21</v>
@@ -47227,40 +47236,40 @@
         <v>0</v>
       </c>
       <c r="G87">
-        <v>0.72299999999999998</v>
+        <v>0</v>
       </c>
       <c r="H87">
-        <v>4.335</v>
+        <v>6.1920000000000002</v>
       </c>
       <c r="I87">
-        <v>1.163</v>
+        <v>1.571</v>
       </c>
       <c r="J87">
-        <v>3.7</v>
+        <v>3.6640000000000001</v>
       </c>
       <c r="K87">
-        <v>0.95699999999999996</v>
+        <v>1.361</v>
       </c>
       <c r="L87">
-        <v>0.56999999999999995</v>
+        <v>1.036</v>
       </c>
       <c r="M87">
-        <v>2.2080000000000002</v>
+        <v>1.5</v>
       </c>
       <c r="N87">
-        <v>3.4950000000000001</v>
+        <v>4.2519999999999998</v>
       </c>
       <c r="O87">
-        <v>3.5019999999999998</v>
+        <v>4.4740000000000002</v>
       </c>
       <c r="P87">
-        <v>4.0129999999999999</v>
+        <v>5.0410000000000004</v>
       </c>
       <c r="Q87">
-        <v>14.654</v>
+        <v>18.446000000000002</v>
       </c>
       <c r="R87">
-        <v>457.39600000000002</v>
+        <v>823.12199999999996</v>
       </c>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.2">
@@ -47268,13 +47277,13 @@
         <v>36</v>
       </c>
       <c r="B88" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="C88" t="s">
         <v>50</v>
       </c>
       <c r="D88" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -47283,34 +47292,37 @@
         <v>0</v>
       </c>
       <c r="G88">
-        <v>0.63100000000000001</v>
+        <v>0</v>
       </c>
       <c r="H88">
-        <v>6.0229999999999997</v>
+        <v>6.2229999999999999</v>
       </c>
       <c r="I88">
-        <v>1.339</v>
+        <v>2.649</v>
       </c>
       <c r="J88">
-        <v>3.6150000000000002</v>
+        <v>4.3929999999999998</v>
       </c>
       <c r="K88">
-        <v>1.0609999999999999</v>
+        <v>1.2709999999999999</v>
       </c>
       <c r="L88">
-        <v>0.80800000000000005</v>
+        <v>1.085</v>
       </c>
       <c r="M88">
-        <v>2.0019999999999998</v>
+        <v>2.778</v>
       </c>
       <c r="N88">
-        <v>4.3280000000000003</v>
+        <v>4.6079999999999997</v>
+      </c>
+      <c r="O88">
+        <v>4.6970000000000001</v>
       </c>
       <c r="P88">
-        <v>7.141</v>
+        <v>3.218</v>
       </c>
       <c r="Q88">
-        <v>21.399000000000001</v>
+        <v>24.195</v>
       </c>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.2">
@@ -47318,10 +47330,10 @@
         <v>36</v>
       </c>
       <c r="B89" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C89" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D89" t="s">
         <v>21</v>
@@ -47333,40 +47345,25 @@
         <v>0</v>
       </c>
       <c r="G89">
-        <v>0.92100000000000004</v>
+        <v>0</v>
       </c>
       <c r="H89">
-        <v>10.175000000000001</v>
+        <v>6.2880000000000003</v>
       </c>
       <c r="I89">
-        <v>3.774</v>
-      </c>
-      <c r="J89">
-        <v>3.74</v>
-      </c>
-      <c r="K89">
-        <v>0.85899999999999999</v>
-      </c>
-      <c r="L89">
-        <v>0.73699999999999999</v>
-      </c>
-      <c r="M89">
-        <v>3.0059999999999998</v>
+        <v>1.4670000000000001</v>
       </c>
       <c r="N89">
-        <v>3.8210000000000002</v>
+        <v>4.6120000000000001</v>
       </c>
       <c r="O89">
-        <v>5.0430000000000001</v>
+        <v>4.6180000000000003</v>
       </c>
       <c r="P89">
-        <v>5.6950000000000003</v>
+        <v>3.7229999999999999</v>
       </c>
       <c r="Q89">
-        <v>24.187999999999999</v>
-      </c>
-      <c r="R89">
-        <v>840.12</v>
+        <v>12.891999999999999</v>
       </c>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.2">
@@ -47374,10 +47371,10 @@
         <v>36</v>
       </c>
       <c r="B90" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C90" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D90" t="s">
         <v>21</v>
@@ -47389,37 +47386,37 @@
         <v>0</v>
       </c>
       <c r="G90">
-        <v>1.2829999999999999</v>
+        <v>0</v>
       </c>
       <c r="H90">
-        <v>4.7300000000000004</v>
+        <v>6.2889999999999997</v>
       </c>
       <c r="I90">
-        <v>1.123</v>
+        <v>1.919</v>
       </c>
       <c r="J90">
-        <v>3.7770000000000001</v>
+        <v>4.306</v>
       </c>
       <c r="K90">
-        <v>1.1639999999999999</v>
+        <v>1.889</v>
       </c>
       <c r="L90">
-        <v>1.0840000000000001</v>
+        <v>1.847</v>
       </c>
       <c r="M90">
-        <v>3.3540000000000001</v>
+        <v>2.6240000000000001</v>
       </c>
       <c r="N90">
-        <v>4.4909999999999997</v>
+        <v>3.9119999999999999</v>
       </c>
       <c r="O90">
-        <v>5.3280000000000003</v>
+        <v>3.8759999999999999</v>
       </c>
       <c r="P90">
-        <v>4.7939999999999996</v>
+        <v>3.2480000000000002</v>
       </c>
       <c r="Q90">
-        <v>15.36</v>
+        <v>13.007</v>
       </c>
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.2">
@@ -47427,10 +47424,10 @@
         <v>36</v>
       </c>
       <c r="B91" t="s">
-        <v>75</v>
+        <v>41</v>
       </c>
       <c r="C91" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D91" t="s">
         <v>21</v>
@@ -47442,37 +47439,22 @@
         <v>0</v>
       </c>
       <c r="G91">
-        <v>1.0129999999999999</v>
+        <v>0</v>
       </c>
       <c r="H91">
-        <v>6.6959999999999997</v>
+        <v>6.2919999999999998</v>
       </c>
       <c r="I91">
-        <v>2.5419999999999998</v>
-      </c>
-      <c r="J91">
-        <v>3.984</v>
-      </c>
-      <c r="K91">
-        <v>0.99099999999999999</v>
-      </c>
-      <c r="L91">
-        <v>0.85399999999999998</v>
-      </c>
-      <c r="M91">
-        <v>3.085</v>
-      </c>
-      <c r="N91">
-        <v>3.738</v>
-      </c>
-      <c r="O91">
-        <v>4.1159999999999997</v>
+        <v>3.339</v>
       </c>
       <c r="P91">
-        <v>4.819</v>
+        <v>5.7670000000000003</v>
       </c>
       <c r="Q91">
-        <v>12.592000000000001</v>
+        <v>13.625999999999999</v>
+      </c>
+      <c r="R91">
+        <v>754.33699999999999</v>
       </c>
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.2">
@@ -47480,10 +47462,10 @@
         <v>36</v>
       </c>
       <c r="B92" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C92" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="D92" t="s">
         <v>21</v>
@@ -47495,40 +47477,31 @@
         <v>0</v>
       </c>
       <c r="G92">
-        <v>0.58299999999999996</v>
+        <v>0</v>
       </c>
       <c r="H92">
-        <v>4.8810000000000002</v>
+        <v>6.3490000000000002</v>
       </c>
       <c r="I92">
-        <v>1.1890000000000001</v>
+        <v>2.504</v>
       </c>
       <c r="J92">
-        <v>2.3919999999999999</v>
-      </c>
-      <c r="K92">
-        <v>1.506</v>
-      </c>
-      <c r="L92">
-        <v>0.79100000000000004</v>
+        <v>3.2469999999999999</v>
       </c>
       <c r="M92">
-        <v>1.7250000000000001</v>
+        <v>2.3130000000000002</v>
       </c>
       <c r="N92">
-        <v>3.1339999999999999</v>
+        <v>2.996</v>
       </c>
       <c r="O92">
-        <v>3.6640000000000001</v>
+        <v>2.6240000000000001</v>
       </c>
       <c r="P92">
-        <v>4.452</v>
+        <v>5.5460000000000003</v>
       </c>
       <c r="Q92">
-        <v>11.879</v>
-      </c>
-      <c r="R92">
-        <v>834.19600000000003</v>
+        <v>17.846</v>
       </c>
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.2">
@@ -47536,13 +47509,10 @@
         <v>36</v>
       </c>
       <c r="B93" t="s">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="C93" t="s">
-        <v>77</v>
-      </c>
-      <c r="D93" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -47551,37 +47521,40 @@
         <v>0</v>
       </c>
       <c r="G93">
-        <v>0.70099999999999996</v>
+        <v>0</v>
       </c>
       <c r="H93">
-        <v>3.9009999999999998</v>
+        <v>6.3959999999999999</v>
       </c>
       <c r="I93">
-        <v>1.431</v>
+        <v>2.8149999999999999</v>
       </c>
       <c r="J93">
-        <v>2.5760000000000001</v>
+        <v>3.637</v>
       </c>
       <c r="K93">
-        <v>0.78200000000000003</v>
+        <v>1.341</v>
       </c>
       <c r="L93">
-        <v>0.76500000000000001</v>
+        <v>1.1879999999999999</v>
       </c>
       <c r="M93">
-        <v>1.881</v>
+        <v>1.7969999999999999</v>
       </c>
       <c r="N93">
-        <v>4.0369999999999999</v>
+        <v>4.734</v>
       </c>
       <c r="O93">
-        <v>2.9169999999999998</v>
+        <v>3.19</v>
       </c>
       <c r="P93">
-        <v>2.423</v>
+        <v>2.3479999999999999</v>
       </c>
       <c r="Q93">
-        <v>9.3369999999999997</v>
+        <v>10.004</v>
+      </c>
+      <c r="R93">
+        <v>590.68600000000004</v>
       </c>
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.2">
@@ -47589,10 +47562,13 @@
         <v>36</v>
       </c>
       <c r="B94" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C94" t="s">
-        <v>77</v>
+        <v>50</v>
+      </c>
+      <c r="D94" t="s">
+        <v>24</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -47601,25 +47577,40 @@
         <v>0</v>
       </c>
       <c r="G94">
-        <v>0.34899999999999998</v>
+        <v>0</v>
       </c>
       <c r="H94">
-        <v>4.851</v>
+        <v>6.593</v>
       </c>
       <c r="I94">
-        <v>1.774</v>
+        <v>2.2210000000000001</v>
+      </c>
+      <c r="J94">
+        <v>2.7930000000000001</v>
+      </c>
+      <c r="K94">
+        <v>0.84</v>
+      </c>
+      <c r="L94">
+        <v>0.80400000000000005</v>
+      </c>
+      <c r="M94">
+        <v>2.4329999999999998</v>
       </c>
       <c r="N94">
-        <v>3.9289999999999998</v>
+        <v>3.7709999999999999</v>
       </c>
       <c r="O94">
-        <v>3.2690000000000001</v>
+        <v>4.157</v>
       </c>
       <c r="P94">
-        <v>2.9089999999999998</v>
+        <v>2.6070000000000002</v>
       </c>
       <c r="Q94">
-        <v>8.2349999999999994</v>
+        <v>13.64</v>
+      </c>
+      <c r="R94">
+        <v>861.70899999999995</v>
       </c>
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.2">
@@ -47627,13 +47618,13 @@
         <v>36</v>
       </c>
       <c r="B95" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="C95" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
       <c r="D95" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -47641,38 +47632,35 @@
       <c r="F95">
         <v>0</v>
       </c>
+      <c r="G95">
+        <v>0</v>
+      </c>
       <c r="H95">
-        <v>3.5979999999999999</v>
+        <v>6.6230000000000002</v>
       </c>
       <c r="I95">
-        <v>1.4259999999999999</v>
+        <v>2.4950000000000001</v>
       </c>
       <c r="J95">
-        <v>3.42</v>
+        <v>3.3420000000000001</v>
       </c>
       <c r="K95">
-        <v>1.044</v>
+        <v>1.179</v>
       </c>
       <c r="L95">
-        <v>0.45600000000000002</v>
+        <v>0.95399999999999996</v>
       </c>
       <c r="M95">
-        <v>2.3439999999999999</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="N95">
-        <v>3.9940000000000002</v>
-      </c>
-      <c r="O95">
-        <v>3.7069999999999999</v>
+        <v>4.032</v>
       </c>
       <c r="P95">
-        <v>4.1630000000000003</v>
+        <v>4.2030000000000003</v>
       </c>
       <c r="Q95">
-        <v>23.713000000000001</v>
-      </c>
-      <c r="R95">
-        <v>791.32</v>
+        <v>15.401999999999999</v>
       </c>
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.2">
@@ -47680,10 +47668,10 @@
         <v>36</v>
       </c>
       <c r="B96" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C96" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="D96" t="s">
         <v>21</v>
@@ -47694,35 +47682,38 @@
       <c r="F96">
         <v>0</v>
       </c>
+      <c r="G96">
+        <v>1.0129999999999999</v>
+      </c>
       <c r="H96">
-        <v>3.6040000000000001</v>
+        <v>6.6959999999999997</v>
       </c>
       <c r="I96">
-        <v>0.89600000000000002</v>
+        <v>2.5419999999999998</v>
       </c>
       <c r="J96">
-        <v>3.9529999999999998</v>
+        <v>3.984</v>
       </c>
       <c r="K96">
-        <v>1.381</v>
+        <v>0.99099999999999999</v>
       </c>
       <c r="L96">
-        <v>1.2789999999999999</v>
+        <v>0.85399999999999998</v>
       </c>
       <c r="M96">
-        <v>2.1579999999999999</v>
+        <v>3.085</v>
       </c>
       <c r="N96">
-        <v>3.7949999999999999</v>
+        <v>3.738</v>
       </c>
       <c r="O96">
-        <v>3.5129999999999999</v>
+        <v>4.1159999999999997</v>
       </c>
       <c r="P96">
-        <v>3.956</v>
+        <v>4.819</v>
       </c>
       <c r="Q96">
-        <v>13.515000000000001</v>
+        <v>12.592000000000001</v>
       </c>
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.2">
@@ -47730,10 +47721,10 @@
         <v>36</v>
       </c>
       <c r="B97" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="C97" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="D97" t="s">
         <v>21</v>
@@ -47744,35 +47735,38 @@
       <c r="F97">
         <v>0</v>
       </c>
+      <c r="G97">
+        <v>0</v>
+      </c>
       <c r="H97">
-        <v>4.4720000000000004</v>
+        <v>6.8769999999999998</v>
       </c>
       <c r="I97">
-        <v>1.077</v>
+        <v>3.18</v>
       </c>
       <c r="J97">
-        <v>2.649</v>
+        <v>4.5990000000000002</v>
       </c>
       <c r="K97">
-        <v>1.0960000000000001</v>
+        <v>2.3090000000000002</v>
       </c>
       <c r="L97">
-        <v>1.0669999999999999</v>
+        <v>1.663</v>
       </c>
       <c r="M97">
-        <v>2.5329999999999999</v>
+        <v>1.492</v>
       </c>
       <c r="N97">
-        <v>5.45</v>
+        <v>3.7959999999999998</v>
       </c>
       <c r="O97">
-        <v>5.4210000000000003</v>
+        <v>2.391</v>
       </c>
       <c r="P97">
-        <v>4.359</v>
+        <v>5.4109999999999996</v>
       </c>
       <c r="Q97">
-        <v>18.315000000000001</v>
+        <v>7.7619999999999996</v>
       </c>
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.2">
@@ -47780,10 +47774,10 @@
         <v>36</v>
       </c>
       <c r="B98" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="C98" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="D98" t="s">
         <v>21</v>
@@ -47795,40 +47789,37 @@
         <v>0</v>
       </c>
       <c r="G98">
-        <v>0.83699999999999997</v>
+        <v>0</v>
       </c>
       <c r="H98">
-        <v>4.6070000000000002</v>
+        <v>6.93</v>
       </c>
       <c r="I98">
-        <v>1.7330000000000001</v>
+        <v>2.923</v>
       </c>
       <c r="J98">
-        <v>3.5350000000000001</v>
+        <v>3.7719999999999998</v>
       </c>
       <c r="K98">
-        <v>0.90900000000000003</v>
+        <v>1.583</v>
       </c>
       <c r="L98">
-        <v>0.74099999999999999</v>
+        <v>1.4259999999999999</v>
       </c>
       <c r="M98">
-        <v>2.0819999999999999</v>
+        <v>1.522</v>
       </c>
       <c r="N98">
-        <v>3.6040000000000001</v>
-      </c>
-      <c r="O98">
-        <v>3.7440000000000002</v>
+        <v>3.3820000000000001</v>
       </c>
       <c r="P98">
-        <v>4.18</v>
+        <v>4.6139999999999999</v>
       </c>
       <c r="Q98">
-        <v>27.602</v>
+        <v>9.5039999999999996</v>
       </c>
       <c r="R98">
-        <v>742.31299999999999</v>
+        <v>586.10400000000004</v>
       </c>
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.2">
@@ -47836,13 +47827,10 @@
         <v>36</v>
       </c>
       <c r="B99" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C99" t="s">
-        <v>77</v>
-      </c>
-      <c r="D99" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -47851,37 +47839,16 @@
         <v>0</v>
       </c>
       <c r="G99">
-        <v>0.63100000000000001</v>
+        <v>0</v>
       </c>
       <c r="H99">
-        <v>4.7249999999999996</v>
+        <v>7.2510000000000003</v>
       </c>
       <c r="I99">
-        <v>1.595</v>
-      </c>
-      <c r="J99">
-        <v>2.923</v>
-      </c>
-      <c r="K99">
-        <v>0.93400000000000005</v>
-      </c>
-      <c r="L99">
-        <v>0.79600000000000004</v>
-      </c>
-      <c r="M99">
-        <v>3.2309999999999999</v>
-      </c>
-      <c r="N99">
-        <v>2.99</v>
-      </c>
-      <c r="O99">
-        <v>4.133</v>
-      </c>
-      <c r="P99">
-        <v>5.6740000000000004</v>
+        <v>1.913</v>
       </c>
       <c r="Q99">
-        <v>17.510000000000002</v>
+        <v>12.417</v>
       </c>
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.2">
@@ -47889,13 +47856,13 @@
         <v>36</v>
       </c>
       <c r="B100" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C100" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="D100" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -47904,37 +47871,40 @@
         <v>0</v>
       </c>
       <c r="G100">
-        <v>0.876</v>
+        <v>0</v>
       </c>
       <c r="H100">
-        <v>4.4000000000000004</v>
+        <v>7.423</v>
       </c>
       <c r="I100">
-        <v>1.534</v>
+        <v>2.5110000000000001</v>
       </c>
       <c r="J100">
-        <v>3.1859999999999999</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="K100">
-        <v>1.36</v>
+        <v>1.7789999999999999</v>
       </c>
       <c r="L100">
-        <v>0.69699999999999995</v>
+        <v>1.7450000000000001</v>
       </c>
       <c r="M100">
-        <v>1.9990000000000001</v>
+        <v>2.6749999999999998</v>
       </c>
       <c r="N100">
-        <v>3.3109999999999999</v>
+        <v>3.2160000000000002</v>
       </c>
       <c r="O100">
-        <v>3.847</v>
+        <v>3.29</v>
       </c>
       <c r="P100">
-        <v>5.7759999999999998</v>
+        <v>2.6640000000000001</v>
       </c>
       <c r="Q100">
-        <v>15.307</v>
+        <v>18.071999999999999</v>
+      </c>
+      <c r="R100">
+        <v>709.48199999999997</v>
       </c>
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.2">
@@ -47942,13 +47912,13 @@
         <v>36</v>
       </c>
       <c r="B101" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C101" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="D101" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -47957,40 +47927,40 @@
         <v>0</v>
       </c>
       <c r="G101">
-        <v>1.4550000000000001</v>
+        <v>0</v>
       </c>
       <c r="H101">
-        <v>4.7640000000000002</v>
+        <v>7.4390000000000001</v>
       </c>
       <c r="I101">
-        <v>1.0820000000000001</v>
+        <v>3.4060000000000001</v>
       </c>
       <c r="J101">
-        <v>3.6880000000000002</v>
+        <v>3.4870000000000001</v>
       </c>
       <c r="K101">
-        <v>1.0429999999999999</v>
+        <v>1.0549999999999999</v>
       </c>
       <c r="L101">
-        <v>0.68799999999999994</v>
+        <v>0.82099999999999995</v>
       </c>
       <c r="M101">
-        <v>2.6859999999999999</v>
+        <v>2.1589999999999998</v>
       </c>
       <c r="N101">
-        <v>4.4820000000000002</v>
+        <v>4.069</v>
       </c>
       <c r="O101">
-        <v>3.9249999999999998</v>
+        <v>3.4689999999999999</v>
       </c>
       <c r="P101">
-        <v>2.3380000000000001</v>
+        <v>2.3660000000000001</v>
       </c>
       <c r="Q101">
-        <v>6.633</v>
+        <v>23.082999999999998</v>
       </c>
       <c r="R101">
-        <v>438.92500000000001</v>
+        <v>401.69799999999998</v>
       </c>
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.2">
@@ -47998,10 +47968,10 @@
         <v>36</v>
       </c>
       <c r="B102" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="C102" t="s">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="D102" t="s">
         <v>25</v>
@@ -48013,40 +47983,37 @@
         <v>0</v>
       </c>
       <c r="G102">
-        <v>1.077</v>
+        <v>0</v>
       </c>
       <c r="H102">
-        <v>3.7440000000000002</v>
+        <v>7.4989999999999997</v>
       </c>
       <c r="I102">
-        <v>0.371</v>
+        <v>1.675</v>
       </c>
       <c r="J102">
-        <v>4.4240000000000004</v>
+        <v>3.03</v>
       </c>
       <c r="K102">
-        <v>1.091</v>
+        <v>1.0640000000000001</v>
       </c>
       <c r="L102">
-        <v>0.63</v>
+        <v>0.97199999999999998</v>
       </c>
       <c r="M102">
-        <v>3.0750000000000002</v>
+        <v>1.99</v>
       </c>
       <c r="N102">
-        <v>4.4409999999999998</v>
+        <v>2.5819999999999999</v>
       </c>
       <c r="O102">
-        <v>4.4279999999999999</v>
+        <v>2.9129999999999998</v>
       </c>
       <c r="P102">
-        <v>1.573</v>
+        <v>5.7</v>
       </c>
       <c r="Q102">
-        <v>16.478000000000002</v>
-      </c>
-      <c r="R102">
-        <v>343.41500000000002</v>
+        <v>56.378999999999998</v>
       </c>
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.2">
@@ -48054,13 +48021,13 @@
         <v>36</v>
       </c>
       <c r="B103" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="C103" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="D103" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -48069,37 +48036,40 @@
         <v>0</v>
       </c>
       <c r="G103">
-        <v>0.89900000000000002</v>
+        <v>0</v>
       </c>
       <c r="H103">
-        <v>3.7349999999999999</v>
+        <v>7.657</v>
       </c>
       <c r="I103">
-        <v>0.59499999999999997</v>
+        <v>2.4550000000000001</v>
       </c>
       <c r="J103">
-        <v>5.6589999999999998</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="K103">
-        <v>2.0110000000000001</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="L103">
-        <v>1.31</v>
+        <v>0.79600000000000004</v>
       </c>
       <c r="M103">
-        <v>2.9209999999999998</v>
+        <v>2.87</v>
       </c>
       <c r="N103">
-        <v>4.83</v>
+        <v>5.21</v>
       </c>
       <c r="O103">
-        <v>3.508</v>
+        <v>4.3330000000000002</v>
       </c>
       <c r="P103">
-        <v>2.1349999999999998</v>
+        <v>4.2320000000000002</v>
       </c>
       <c r="Q103">
-        <v>4.9080000000000004</v>
+        <v>7.4290000000000003</v>
+      </c>
+      <c r="R103">
+        <v>579.62199999999996</v>
       </c>
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.2">
@@ -48107,10 +48077,13 @@
         <v>36</v>
       </c>
       <c r="B104" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="C104" t="s">
-        <v>77</v>
+        <v>38</v>
+      </c>
+      <c r="D104" t="s">
+        <v>21</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -48118,35 +48091,32 @@
       <c r="F104">
         <v>0</v>
       </c>
+      <c r="G104">
+        <v>0</v>
+      </c>
       <c r="H104">
-        <v>3.492</v>
+        <v>7.8369999999999997</v>
       </c>
       <c r="I104">
-        <v>0.95799999999999996</v>
+        <v>4.2949999999999999</v>
       </c>
       <c r="J104">
-        <v>2.4430000000000001</v>
-      </c>
-      <c r="K104">
-        <v>1.161</v>
-      </c>
-      <c r="L104">
-        <v>0.80300000000000005</v>
+        <v>4.1970000000000001</v>
       </c>
       <c r="M104">
-        <v>1.8069999999999999</v>
+        <v>1.2729999999999999</v>
       </c>
       <c r="N104">
-        <v>3.7639999999999998</v>
+        <v>3.177</v>
+      </c>
+      <c r="O104">
+        <v>4.2709999999999999</v>
       </c>
       <c r="P104">
-        <v>5.1680000000000001</v>
+        <v>3.6859999999999999</v>
       </c>
       <c r="Q104">
-        <v>26.728999999999999</v>
-      </c>
-      <c r="R104">
-        <v>373.80900000000003</v>
+        <v>10.39</v>
       </c>
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.2">
@@ -48154,10 +48124,13 @@
         <v>36</v>
       </c>
       <c r="B105" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C105" t="s">
-        <v>77</v>
+        <v>52</v>
+      </c>
+      <c r="D105" t="s">
+        <v>21</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -48165,20 +48138,41 @@
       <c r="F105">
         <v>0</v>
       </c>
+      <c r="G105">
+        <v>0</v>
+      </c>
       <c r="H105">
-        <v>2.48</v>
+        <v>7.867</v>
       </c>
       <c r="I105">
-        <v>0.60299999999999998</v>
+        <v>3.2109999999999999</v>
+      </c>
+      <c r="J105">
+        <v>3.8620000000000001</v>
+      </c>
+      <c r="K105">
+        <v>1.2170000000000001</v>
+      </c>
+      <c r="L105">
+        <v>0.751</v>
+      </c>
+      <c r="M105">
+        <v>2.831</v>
+      </c>
+      <c r="N105">
+        <v>4.8099999999999996</v>
+      </c>
+      <c r="O105">
+        <v>4.2679999999999998</v>
       </c>
       <c r="P105">
-        <v>2.2160000000000002</v>
+        <v>2.9119999999999999</v>
       </c>
       <c r="Q105">
-        <v>14.59</v>
+        <v>12.845000000000001</v>
       </c>
       <c r="R105">
-        <v>725.89599999999996</v>
+        <v>926.26900000000001</v>
       </c>
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.2">
@@ -48186,10 +48180,10 @@
         <v>36</v>
       </c>
       <c r="B106" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="C106" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -48197,17 +48191,41 @@
       <c r="F106">
         <v>0</v>
       </c>
+      <c r="G106">
+        <v>0</v>
+      </c>
       <c r="H106">
-        <v>2.6949999999999998</v>
+        <v>9.1129999999999995</v>
       </c>
       <c r="I106">
-        <v>0.73</v>
+        <v>3.8319999999999999</v>
+      </c>
+      <c r="J106">
+        <v>3.54</v>
+      </c>
+      <c r="K106">
+        <v>1.609</v>
+      </c>
+      <c r="L106">
+        <v>1.476</v>
+      </c>
+      <c r="M106">
+        <v>1.4490000000000001</v>
+      </c>
+      <c r="N106">
+        <v>4.2910000000000004</v>
+      </c>
+      <c r="O106">
+        <v>3.8140000000000001</v>
       </c>
       <c r="P106">
-        <v>5.1840000000000002</v>
+        <v>2.4820000000000002</v>
       </c>
       <c r="Q106">
-        <v>16.916</v>
+        <v>16.744</v>
+      </c>
+      <c r="R106">
+        <v>655.952</v>
       </c>
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.2">
@@ -48215,11 +48233,14 @@
         <v>36</v>
       </c>
       <c r="B107" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C107" t="s">
         <v>50</v>
       </c>
+      <c r="D107" t="s">
+        <v>21</v>
+      </c>
       <c r="E107">
         <v>0</v>
       </c>
@@ -48227,37 +48248,40 @@
         <v>0</v>
       </c>
       <c r="G107">
-        <v>0.93700000000000006</v>
+        <v>0.92100000000000004</v>
       </c>
       <c r="H107">
-        <v>3.2759999999999998</v>
+        <v>10.175000000000001</v>
       </c>
       <c r="I107">
-        <v>0.749</v>
+        <v>3.774</v>
       </c>
       <c r="J107">
-        <v>2.694</v>
+        <v>3.74</v>
       </c>
       <c r="K107">
-        <v>1.2070000000000001</v>
+        <v>0.85899999999999999</v>
       </c>
       <c r="L107">
-        <v>1.1080000000000001</v>
+        <v>0.73699999999999999</v>
       </c>
       <c r="M107">
-        <v>2.5270000000000001</v>
+        <v>3.0059999999999998</v>
       </c>
       <c r="N107">
-        <v>4.0540000000000003</v>
+        <v>3.8210000000000002</v>
+      </c>
+      <c r="O107">
+        <v>5.0430000000000001</v>
       </c>
       <c r="P107">
-        <v>5.556</v>
+        <v>5.6950000000000003</v>
       </c>
       <c r="Q107">
-        <v>17.588000000000001</v>
+        <v>24.187999999999999</v>
       </c>
       <c r="R107">
-        <v>692.99699999999996</v>
+        <v>840.12</v>
       </c>
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.2">
@@ -48265,10 +48289,13 @@
         <v>36</v>
       </c>
       <c r="B108" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="C108" t="s">
-        <v>50</v>
+        <v>54</v>
+      </c>
+      <c r="D108" t="s">
+        <v>21</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -48277,22 +48304,37 @@
         <v>0</v>
       </c>
       <c r="G108">
-        <v>0.95199999999999996</v>
+        <v>0</v>
       </c>
       <c r="H108">
-        <v>3.847</v>
+        <v>10.263999999999999</v>
       </c>
       <c r="I108">
-        <v>1.468</v>
+        <v>4.327</v>
+      </c>
+      <c r="J108">
+        <v>3.4039999999999999</v>
+      </c>
+      <c r="K108">
+        <v>1.1759999999999999</v>
+      </c>
+      <c r="L108">
+        <v>1.105</v>
+      </c>
+      <c r="M108">
+        <v>1.7450000000000001</v>
+      </c>
+      <c r="N108">
+        <v>4.7569999999999997</v>
       </c>
       <c r="P108">
-        <v>2.7330000000000001</v>
+        <v>3.593</v>
       </c>
       <c r="Q108">
-        <v>21.722000000000001</v>
+        <v>21.428999999999998</v>
       </c>
       <c r="R108">
-        <v>520.31100000000004</v>
+        <v>611.54600000000005</v>
       </c>
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.2">
@@ -48300,10 +48342,10 @@
         <v>36</v>
       </c>
       <c r="B109" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="C109" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -48312,19 +48354,40 @@
         <v>0</v>
       </c>
       <c r="G109">
-        <v>0.84599999999999997</v>
+        <v>0</v>
       </c>
       <c r="H109">
-        <v>2.653</v>
+        <v>10.68</v>
       </c>
       <c r="I109">
-        <v>0.87</v>
+        <v>6.49</v>
+      </c>
+      <c r="J109">
+        <v>4.0190000000000001</v>
+      </c>
+      <c r="K109">
+        <v>0.96</v>
+      </c>
+      <c r="L109">
+        <v>0.91600000000000004</v>
+      </c>
+      <c r="M109">
+        <v>3.5640000000000001</v>
+      </c>
+      <c r="N109">
+        <v>4.1959999999999997</v>
+      </c>
+      <c r="O109">
+        <v>3.8759999999999999</v>
       </c>
       <c r="P109">
-        <v>3.238</v>
+        <v>3.8050000000000002</v>
       </c>
       <c r="Q109">
-        <v>14.788</v>
+        <v>13.739000000000001</v>
+      </c>
+      <c r="R109">
+        <v>696.42700000000002</v>
       </c>
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.2">
@@ -48332,10 +48395,10 @@
         <v>36</v>
       </c>
       <c r="B110" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="C110" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -48344,40 +48407,34 @@
         <v>0</v>
       </c>
       <c r="G110">
-        <v>1.1140000000000001</v>
-      </c>
-      <c r="H110">
-        <v>2.3650000000000002</v>
-      </c>
-      <c r="I110">
-        <v>0.57899999999999996</v>
+        <v>0</v>
       </c>
       <c r="J110">
-        <v>3</v>
+        <v>3.7160000000000002</v>
       </c>
       <c r="K110">
-        <v>0.60599999999999998</v>
+        <v>1.6679999999999999</v>
       </c>
       <c r="L110">
-        <v>0.59499999999999997</v>
+        <v>1.458</v>
       </c>
       <c r="M110">
-        <v>2.2879999999999998</v>
+        <v>1.9650000000000001</v>
       </c>
       <c r="N110">
-        <v>3.448</v>
+        <v>4.766</v>
       </c>
       <c r="O110">
-        <v>2.887</v>
+        <v>3.915</v>
       </c>
       <c r="P110">
-        <v>3.7949999999999999</v>
+        <v>3.4550000000000001</v>
       </c>
       <c r="Q110">
-        <v>29.815999999999999</v>
+        <v>18.951000000000001</v>
       </c>
       <c r="R110">
-        <v>770.83900000000006</v>
+        <v>539.70299999999997</v>
       </c>
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.2">
@@ -48385,10 +48442,13 @@
         <v>36</v>
       </c>
       <c r="B111" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="C111" t="s">
-        <v>38</v>
+        <v>46</v>
+      </c>
+      <c r="D111" t="s">
+        <v>21</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -48397,37 +48457,13 @@
         <v>0</v>
       </c>
       <c r="G111">
-        <v>0.79500000000000004</v>
-      </c>
-      <c r="H111">
-        <v>2.3580000000000001</v>
-      </c>
-      <c r="I111">
-        <v>0.37</v>
-      </c>
-      <c r="J111">
-        <v>2.5710000000000002</v>
-      </c>
-      <c r="K111">
-        <v>2.1269999999999998</v>
-      </c>
-      <c r="L111">
-        <v>1.9790000000000001</v>
-      </c>
-      <c r="M111">
-        <v>2.077</v>
-      </c>
-      <c r="N111">
-        <v>3.6619999999999999</v>
-      </c>
-      <c r="O111">
-        <v>3.6850000000000001</v>
+        <v>0</v>
       </c>
       <c r="P111">
-        <v>3.4620000000000002</v>
+        <v>7.3390000000000004</v>
       </c>
       <c r="Q111">
-        <v>3.8</v>
+        <v>43.118000000000002</v>
       </c>
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.2">
@@ -48435,10 +48471,13 @@
         <v>36</v>
       </c>
       <c r="B112" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="C112" t="s">
-        <v>38</v>
+        <v>46</v>
+      </c>
+      <c r="D112" t="s">
+        <v>21</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -48447,34 +48486,13 @@
         <v>0</v>
       </c>
       <c r="G112">
-        <v>0.998</v>
-      </c>
-      <c r="H112">
-        <v>3.4609999999999999</v>
-      </c>
-      <c r="I112">
-        <v>0.70599999999999996</v>
-      </c>
-      <c r="J112">
-        <v>3.4220000000000002</v>
-      </c>
-      <c r="K112">
-        <v>1.488</v>
-      </c>
-      <c r="L112">
-        <v>1.4550000000000001</v>
-      </c>
-      <c r="M112">
-        <v>2.5</v>
-      </c>
-      <c r="N112">
-        <v>3.4980000000000002</v>
+        <v>0</v>
       </c>
       <c r="P112">
-        <v>5.1710000000000003</v>
+        <v>7.62</v>
       </c>
       <c r="Q112">
-        <v>23.29</v>
+        <v>44.331000000000003</v>
       </c>
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.2">
@@ -48482,7 +48500,46 @@
         <v>36</v>
       </c>
       <c r="B113" t="s">
-        <v>82</v>
+        <v>61</v>
+      </c>
+      <c r="C113" t="s">
+        <v>60</v>
+      </c>
+      <c r="D113" t="s">
+        <v>21</v>
+      </c>
+      <c r="E113">
+        <v>0</v>
+      </c>
+      <c r="F113">
+        <v>0</v>
+      </c>
+      <c r="G113">
+        <v>0</v>
+      </c>
+      <c r="J113">
+        <v>3.9609999999999999</v>
+      </c>
+      <c r="K113">
+        <v>1.6419999999999999</v>
+      </c>
+      <c r="L113">
+        <v>0.91900000000000004</v>
+      </c>
+      <c r="M113">
+        <v>1.96</v>
+      </c>
+      <c r="N113">
+        <v>4.0129999999999999</v>
+      </c>
+      <c r="O113">
+        <v>3.552</v>
+      </c>
+      <c r="P113">
+        <v>3.0619999999999998</v>
+      </c>
+      <c r="Q113">
+        <v>10.647</v>
       </c>
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.2">
@@ -48490,46 +48547,46 @@
         <v>36</v>
       </c>
       <c r="B114" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C114" t="s">
         <v>50</v>
       </c>
+      <c r="D114" t="s">
+        <v>21</v>
+      </c>
+      <c r="E114">
+        <v>0</v>
+      </c>
+      <c r="F114">
+        <v>0</v>
+      </c>
       <c r="G114">
-        <v>0.84499999999999997</v>
-      </c>
-      <c r="H114">
-        <v>2.7519999999999998</v>
-      </c>
-      <c r="I114">
-        <v>0.66400000000000003</v>
+        <v>0</v>
       </c>
       <c r="J114">
-        <v>2.0099999999999998</v>
+        <v>3.7919999999999998</v>
       </c>
       <c r="K114">
-        <v>0.45100000000000001</v>
+        <v>1.593</v>
       </c>
       <c r="L114">
-        <v>0.38</v>
+        <v>1.3080000000000001</v>
       </c>
       <c r="M114">
-        <v>1.4259999999999999</v>
+        <v>1.974</v>
       </c>
       <c r="N114">
-        <v>4.2430000000000003</v>
+        <v>3.4209999999999998</v>
       </c>
       <c r="O114">
-        <v>4.9790000000000001</v>
+        <v>3.1120000000000001</v>
       </c>
       <c r="P114">
-        <v>5.7290000000000001</v>
+        <v>3.6760000000000002</v>
       </c>
       <c r="Q114">
-        <v>7.4320000000000004</v>
-      </c>
-      <c r="R114">
-        <v>845.24</v>
+        <v>11.606</v>
       </c>
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.2">
@@ -48537,43 +48594,46 @@
         <v>36</v>
       </c>
       <c r="B115" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C115" t="s">
         <v>50</v>
       </c>
+      <c r="D115" t="s">
+        <v>21</v>
+      </c>
+      <c r="E115">
+        <v>0</v>
+      </c>
+      <c r="F115">
+        <v>0</v>
+      </c>
       <c r="G115">
-        <v>1.3049999999999999</v>
-      </c>
-      <c r="H115">
-        <v>2.1960000000000002</v>
-      </c>
-      <c r="I115">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="J115">
-        <v>2.7829999999999999</v>
+        <v>3.01</v>
       </c>
       <c r="K115">
-        <v>1.0569999999999999</v>
+        <v>0.72699999999999998</v>
       </c>
       <c r="L115">
-        <v>0.94099999999999995</v>
+        <v>0.71199999999999997</v>
       </c>
       <c r="M115">
-        <v>1.4339999999999999</v>
+        <v>2.492</v>
       </c>
       <c r="N115">
-        <v>4.0940000000000003</v>
+        <v>3.2549999999999999</v>
       </c>
       <c r="O115">
-        <v>4.0490000000000004</v>
+        <v>4.6130000000000004</v>
       </c>
       <c r="P115">
-        <v>4.7919999999999998</v>
+        <v>2.681</v>
       </c>
       <c r="Q115">
-        <v>23.524999999999999</v>
+        <v>11.928000000000001</v>
       </c>
     </row>
     <row r="116" spans="1:18" x14ac:dyDescent="0.2">
@@ -48581,25 +48641,49 @@
         <v>36</v>
       </c>
       <c r="B116" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C116" t="s">
         <v>50</v>
       </c>
+      <c r="D116" t="s">
+        <v>24</v>
+      </c>
+      <c r="E116">
+        <v>0</v>
+      </c>
+      <c r="F116">
+        <v>0</v>
+      </c>
       <c r="G116">
-        <v>1.583</v>
-      </c>
-      <c r="H116">
-        <v>3.7349999999999999</v>
-      </c>
-      <c r="I116">
-        <v>0.70499999999999996</v>
+        <v>0</v>
+      </c>
+      <c r="J116">
+        <v>2.992</v>
+      </c>
+      <c r="K116">
+        <v>1.375</v>
+      </c>
+      <c r="L116">
+        <v>1.1919999999999999</v>
+      </c>
+      <c r="M116">
+        <v>1.43</v>
+      </c>
+      <c r="N116">
+        <v>2.8820000000000001</v>
+      </c>
+      <c r="O116">
+        <v>5.83</v>
       </c>
       <c r="P116">
-        <v>3.8220000000000001</v>
+        <v>4.1589999999999998</v>
       </c>
       <c r="Q116">
-        <v>33.098999999999997</v>
+        <v>12.566000000000001</v>
+      </c>
+      <c r="R116">
+        <v>870.55700000000002</v>
       </c>
     </row>
     <row r="117" spans="1:18" x14ac:dyDescent="0.2">
@@ -48607,43 +48691,46 @@
         <v>36</v>
       </c>
       <c r="B117" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C117" t="s">
-        <v>77</v>
-      </c>
-      <c r="H117">
-        <v>1.645</v>
-      </c>
-      <c r="I117">
-        <v>0.34599999999999997</v>
+        <v>50</v>
+      </c>
+      <c r="D117" t="s">
+        <v>21</v>
+      </c>
+      <c r="E117">
+        <v>0</v>
+      </c>
+      <c r="F117">
+        <v>0</v>
+      </c>
+      <c r="G117">
+        <v>0</v>
       </c>
       <c r="J117">
-        <v>2.3719999999999999</v>
+        <v>3.802</v>
       </c>
       <c r="K117">
-        <v>1.413</v>
+        <v>1.173</v>
       </c>
       <c r="L117">
-        <v>1.0049999999999999</v>
+        <v>0.86899999999999999</v>
       </c>
       <c r="M117">
-        <v>1.302</v>
+        <v>2.4039999999999999</v>
       </c>
       <c r="N117">
-        <v>3.4460000000000002</v>
+        <v>3.028</v>
       </c>
       <c r="O117">
-        <v>2.976</v>
+        <v>3.0329999999999999</v>
       </c>
       <c r="P117">
-        <v>2.37</v>
+        <v>5.3360000000000003</v>
       </c>
       <c r="Q117">
-        <v>17.329999999999998</v>
-      </c>
-      <c r="R117">
-        <v>497.98599999999999</v>
+        <v>10.022</v>
       </c>
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.2">
@@ -48651,40 +48738,43 @@
         <v>36</v>
       </c>
       <c r="B118" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C118" t="s">
-        <v>77</v>
-      </c>
-      <c r="H118">
-        <v>2.4740000000000002</v>
-      </c>
-      <c r="I118">
-        <v>0.26900000000000002</v>
+        <v>50</v>
+      </c>
+      <c r="E118">
+        <v>0</v>
+      </c>
+      <c r="F118">
+        <v>0</v>
+      </c>
+      <c r="G118">
+        <v>0</v>
       </c>
       <c r="J118">
-        <v>2.9580000000000002</v>
+        <v>3.2559999999999998</v>
       </c>
       <c r="K118">
-        <v>1.0369999999999999</v>
+        <v>0.80600000000000005</v>
       </c>
       <c r="L118">
-        <v>1.147</v>
+        <v>0.69599999999999995</v>
       </c>
       <c r="M118">
-        <v>1.64</v>
+        <v>2.5329999999999999</v>
       </c>
       <c r="N118">
-        <v>3.87</v>
+        <v>2.5529999999999999</v>
       </c>
       <c r="O118">
-        <v>2.468</v>
+        <v>3.9359999999999999</v>
       </c>
       <c r="P118">
-        <v>1.1859999999999999</v>
+        <v>3.9750000000000001</v>
       </c>
       <c r="Q118">
-        <v>10.564</v>
+        <v>16.29</v>
       </c>
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.2">
@@ -48692,22 +48782,46 @@
         <v>36</v>
       </c>
       <c r="B119" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="C119" t="s">
-        <v>77</v>
-      </c>
-      <c r="H119">
-        <v>3.7360000000000002</v>
-      </c>
-      <c r="I119">
-        <v>0.39900000000000002</v>
+        <v>38</v>
+      </c>
+      <c r="D119" t="s">
+        <v>21</v>
+      </c>
+      <c r="E119">
+        <v>0</v>
+      </c>
+      <c r="F119">
+        <v>0</v>
+      </c>
+      <c r="G119">
+        <v>0</v>
+      </c>
+      <c r="J119">
+        <v>3.8380000000000001</v>
+      </c>
+      <c r="K119">
+        <v>1.595</v>
+      </c>
+      <c r="L119">
+        <v>0.75900000000000001</v>
+      </c>
+      <c r="M119">
+        <v>3.3359999999999999</v>
+      </c>
+      <c r="N119">
+        <v>3.61</v>
+      </c>
+      <c r="O119">
+        <v>4.2240000000000002</v>
       </c>
       <c r="P119">
-        <v>2.3820000000000001</v>
+        <v>4.1660000000000004</v>
       </c>
       <c r="Q119">
-        <v>9.1880000000000006</v>
+        <v>56.527000000000001</v>
       </c>
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.2">
@@ -48715,43 +48829,43 @@
         <v>36</v>
       </c>
       <c r="B120" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="C120" t="s">
-        <v>50</v>
-      </c>
-      <c r="H120">
-        <v>2.129</v>
-      </c>
-      <c r="I120">
-        <v>1.256</v>
+        <v>38</v>
+      </c>
+      <c r="E120">
+        <v>0</v>
+      </c>
+      <c r="F120">
+        <v>0</v>
+      </c>
+      <c r="G120">
+        <v>1.006</v>
       </c>
       <c r="J120">
-        <v>2.2450000000000001</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="K120">
-        <v>1.1850000000000001</v>
+        <v>0.83699999999999997</v>
       </c>
       <c r="L120">
-        <v>0.98299999999999998</v>
+        <v>0.745</v>
       </c>
       <c r="M120">
-        <v>1.2749999999999999</v>
+        <v>2.5339999999999998</v>
       </c>
       <c r="N120">
-        <v>2.96</v>
+        <v>3.5329999999999999</v>
       </c>
       <c r="O120">
-        <v>1.6319999999999999</v>
+        <v>3.5720000000000001</v>
       </c>
       <c r="P120">
-        <v>4.2119999999999997</v>
+        <v>4.8570000000000002</v>
       </c>
       <c r="Q120">
-        <v>11.595000000000001</v>
-      </c>
-      <c r="R120">
-        <v>590.78200000000004</v>
+        <v>51.710999999999999</v>
       </c>
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.2">
@@ -48759,40 +48873,40 @@
         <v>36</v>
       </c>
       <c r="B121" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="C121" t="s">
-        <v>50</v>
-      </c>
-      <c r="H121">
-        <v>2.2229999999999999</v>
-      </c>
-      <c r="I121">
-        <v>0.63300000000000001</v>
+        <v>38</v>
+      </c>
+      <c r="E121">
+        <v>0</v>
+      </c>
+      <c r="F121">
+        <v>0</v>
+      </c>
+      <c r="G121">
+        <v>0.85399999999999998</v>
       </c>
       <c r="J121">
-        <v>2.6379999999999999</v>
-      </c>
-      <c r="K121">
-        <v>1.4990000000000001</v>
-      </c>
-      <c r="L121">
-        <v>1.3280000000000001</v>
+        <v>3.609</v>
       </c>
       <c r="M121">
-        <v>1.8720000000000001</v>
+        <v>2.605</v>
       </c>
       <c r="N121">
-        <v>3.1869999999999998</v>
+        <v>3.7519999999999998</v>
       </c>
       <c r="O121">
-        <v>1.7290000000000001</v>
+        <v>2.8769999999999998</v>
       </c>
       <c r="P121">
-        <v>2.5939999999999999</v>
+        <v>7.0609999999999999</v>
       </c>
       <c r="Q121">
-        <v>10.677</v>
+        <v>23.41</v>
+      </c>
+      <c r="R121">
+        <v>322.73</v>
       </c>
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.2">
@@ -48800,25 +48914,13 @@
         <v>36</v>
       </c>
       <c r="B122" t="s">
-        <v>84</v>
-      </c>
-      <c r="C122" t="s">
-        <v>50</v>
-      </c>
-      <c r="H122">
-        <v>3.6379999999999999</v>
-      </c>
-      <c r="I122">
-        <v>1.2569999999999999</v>
-      </c>
-      <c r="P122">
-        <v>4.9649999999999999</v>
-      </c>
-      <c r="Q122">
-        <v>7.5229999999999997</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R122">
+    <sortCondition ref="H2:H122"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>